--- a/skills/functional-safety/hazard_analysis/references/hara_template.xlsx
+++ b/skills/functional-safety/hazard_analysis/references/hara_template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7008" tabRatio="933" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7008" tabRatio="933" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="版本管理" sheetId="1" r:id="rId1"/>
@@ -1830,12 +1830,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2052,6 +2046,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2101,21 +2098,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2123,21 +2130,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -2182,8 +2182,8 @@
       <xdr:rowOff>2117</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>133494</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2347776</xdr:colOff>
       <xdr:row>81</xdr:row>
       <xdr:rowOff>142109</xdr:rowOff>
     </xdr:to>
@@ -7013,30 +7013,30 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.21875" style="68" customWidth="1"/>
-    <col min="2" max="2" width="11" style="68" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="68" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="68" customWidth="1"/>
-    <col min="5" max="5" width="29.44140625" style="68" customWidth="1"/>
-    <col min="6" max="6" width="12" style="68" customWidth="1"/>
-    <col min="7" max="7" width="9" style="68" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="68"/>
+    <col min="1" max="1" width="9.88671875" style="66" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="66" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="66" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="66" customWidth="1"/>
+    <col min="5" max="5" width="49.77734375" style="66" customWidth="1"/>
+    <col min="6" max="6" width="12" style="66" customWidth="1"/>
+    <col min="7" max="7" width="9" style="66" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="66"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7051,769 +7051,769 @@
   <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="76" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="76" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="76" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" style="76" customWidth="1"/>
-    <col min="6" max="8" width="10" style="76" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" style="76" customWidth="1"/>
-    <col min="10" max="254" width="10" style="76" customWidth="1"/>
-    <col min="255" max="259" width="15.44140625" style="76" customWidth="1"/>
-    <col min="260" max="264" width="10" style="76" customWidth="1"/>
-    <col min="265" max="265" width="13.33203125" style="76" customWidth="1"/>
-    <col min="266" max="510" width="10" style="76" customWidth="1"/>
-    <col min="511" max="515" width="15.44140625" style="76" customWidth="1"/>
-    <col min="516" max="520" width="10" style="76" customWidth="1"/>
-    <col min="521" max="521" width="13.33203125" style="76" customWidth="1"/>
-    <col min="522" max="766" width="10" style="76" customWidth="1"/>
-    <col min="767" max="771" width="15.44140625" style="76" customWidth="1"/>
-    <col min="772" max="776" width="10" style="76" customWidth="1"/>
-    <col min="777" max="777" width="13.33203125" style="76" customWidth="1"/>
-    <col min="778" max="1022" width="10" style="76" customWidth="1"/>
-    <col min="1023" max="1027" width="15.44140625" style="76" customWidth="1"/>
-    <col min="1028" max="1032" width="10" style="76" customWidth="1"/>
-    <col min="1033" max="1033" width="13.33203125" style="76" customWidth="1"/>
-    <col min="1034" max="1278" width="10" style="76" customWidth="1"/>
-    <col min="1279" max="1283" width="15.44140625" style="76" customWidth="1"/>
-    <col min="1284" max="1288" width="10" style="76" customWidth="1"/>
-    <col min="1289" max="1289" width="13.33203125" style="76" customWidth="1"/>
-    <col min="1290" max="1534" width="10" style="76" customWidth="1"/>
-    <col min="1535" max="1539" width="15.44140625" style="76" customWidth="1"/>
-    <col min="1540" max="1544" width="10" style="76" customWidth="1"/>
-    <col min="1545" max="1545" width="13.33203125" style="76" customWidth="1"/>
-    <col min="1546" max="1790" width="10" style="76" customWidth="1"/>
-    <col min="1791" max="1795" width="15.44140625" style="76" customWidth="1"/>
-    <col min="1796" max="1800" width="10" style="76" customWidth="1"/>
-    <col min="1801" max="1801" width="13.33203125" style="76" customWidth="1"/>
-    <col min="1802" max="2046" width="10" style="76" customWidth="1"/>
-    <col min="2047" max="2051" width="15.44140625" style="76" customWidth="1"/>
-    <col min="2052" max="2056" width="10" style="76" customWidth="1"/>
-    <col min="2057" max="2057" width="13.33203125" style="76" customWidth="1"/>
-    <col min="2058" max="2302" width="10" style="76" customWidth="1"/>
-    <col min="2303" max="2307" width="15.44140625" style="76" customWidth="1"/>
-    <col min="2308" max="2312" width="10" style="76" customWidth="1"/>
-    <col min="2313" max="2313" width="13.33203125" style="76" customWidth="1"/>
-    <col min="2314" max="2558" width="10" style="76" customWidth="1"/>
-    <col min="2559" max="2563" width="15.44140625" style="76" customWidth="1"/>
-    <col min="2564" max="2568" width="10" style="76" customWidth="1"/>
-    <col min="2569" max="2569" width="13.33203125" style="76" customWidth="1"/>
-    <col min="2570" max="2814" width="10" style="76" customWidth="1"/>
-    <col min="2815" max="2819" width="15.44140625" style="76" customWidth="1"/>
-    <col min="2820" max="2824" width="10" style="76" customWidth="1"/>
-    <col min="2825" max="2825" width="13.33203125" style="76" customWidth="1"/>
-    <col min="2826" max="3070" width="10" style="76" customWidth="1"/>
-    <col min="3071" max="3075" width="15.44140625" style="76" customWidth="1"/>
-    <col min="3076" max="3080" width="10" style="76" customWidth="1"/>
-    <col min="3081" max="3081" width="13.33203125" style="76" customWidth="1"/>
-    <col min="3082" max="3326" width="10" style="76" customWidth="1"/>
-    <col min="3327" max="3331" width="15.44140625" style="76" customWidth="1"/>
-    <col min="3332" max="3336" width="10" style="76" customWidth="1"/>
-    <col min="3337" max="3337" width="13.33203125" style="76" customWidth="1"/>
-    <col min="3338" max="3582" width="10" style="76" customWidth="1"/>
-    <col min="3583" max="3587" width="15.44140625" style="76" customWidth="1"/>
-    <col min="3588" max="3592" width="10" style="76" customWidth="1"/>
-    <col min="3593" max="3593" width="13.33203125" style="76" customWidth="1"/>
-    <col min="3594" max="3838" width="10" style="76" customWidth="1"/>
-    <col min="3839" max="3843" width="15.44140625" style="76" customWidth="1"/>
-    <col min="3844" max="3848" width="10" style="76" customWidth="1"/>
-    <col min="3849" max="3849" width="13.33203125" style="76" customWidth="1"/>
-    <col min="3850" max="4094" width="10" style="76" customWidth="1"/>
-    <col min="4095" max="4099" width="15.44140625" style="76" customWidth="1"/>
-    <col min="4100" max="4104" width="10" style="76" customWidth="1"/>
-    <col min="4105" max="4105" width="13.33203125" style="76" customWidth="1"/>
-    <col min="4106" max="4350" width="10" style="76" customWidth="1"/>
-    <col min="4351" max="4355" width="15.44140625" style="76" customWidth="1"/>
-    <col min="4356" max="4360" width="10" style="76" customWidth="1"/>
-    <col min="4361" max="4361" width="13.33203125" style="76" customWidth="1"/>
-    <col min="4362" max="4606" width="10" style="76" customWidth="1"/>
-    <col min="4607" max="4611" width="15.44140625" style="76" customWidth="1"/>
-    <col min="4612" max="4616" width="10" style="76" customWidth="1"/>
-    <col min="4617" max="4617" width="13.33203125" style="76" customWidth="1"/>
-    <col min="4618" max="4862" width="10" style="76" customWidth="1"/>
-    <col min="4863" max="4867" width="15.44140625" style="76" customWidth="1"/>
-    <col min="4868" max="4872" width="10" style="76" customWidth="1"/>
-    <col min="4873" max="4873" width="13.33203125" style="76" customWidth="1"/>
-    <col min="4874" max="5118" width="10" style="76" customWidth="1"/>
-    <col min="5119" max="5123" width="15.44140625" style="76" customWidth="1"/>
-    <col min="5124" max="5128" width="10" style="76" customWidth="1"/>
-    <col min="5129" max="5129" width="13.33203125" style="76" customWidth="1"/>
-    <col min="5130" max="5374" width="10" style="76" customWidth="1"/>
-    <col min="5375" max="5379" width="15.44140625" style="76" customWidth="1"/>
-    <col min="5380" max="5384" width="10" style="76" customWidth="1"/>
-    <col min="5385" max="5385" width="13.33203125" style="76" customWidth="1"/>
-    <col min="5386" max="5630" width="10" style="76" customWidth="1"/>
-    <col min="5631" max="5635" width="15.44140625" style="76" customWidth="1"/>
-    <col min="5636" max="5640" width="10" style="76" customWidth="1"/>
-    <col min="5641" max="5641" width="13.33203125" style="76" customWidth="1"/>
-    <col min="5642" max="5886" width="10" style="76" customWidth="1"/>
-    <col min="5887" max="5891" width="15.44140625" style="76" customWidth="1"/>
-    <col min="5892" max="5896" width="10" style="76" customWidth="1"/>
-    <col min="5897" max="5897" width="13.33203125" style="76" customWidth="1"/>
-    <col min="5898" max="6142" width="10" style="76" customWidth="1"/>
-    <col min="6143" max="6147" width="15.44140625" style="76" customWidth="1"/>
-    <col min="6148" max="6152" width="10" style="76" customWidth="1"/>
-    <col min="6153" max="6153" width="13.33203125" style="76" customWidth="1"/>
-    <col min="6154" max="6398" width="10" style="76" customWidth="1"/>
-    <col min="6399" max="6403" width="15.44140625" style="76" customWidth="1"/>
-    <col min="6404" max="6408" width="10" style="76" customWidth="1"/>
-    <col min="6409" max="6409" width="13.33203125" style="76" customWidth="1"/>
-    <col min="6410" max="6654" width="10" style="76" customWidth="1"/>
-    <col min="6655" max="6659" width="15.44140625" style="76" customWidth="1"/>
-    <col min="6660" max="6664" width="10" style="76" customWidth="1"/>
-    <col min="6665" max="6665" width="13.33203125" style="76" customWidth="1"/>
-    <col min="6666" max="6910" width="10" style="76" customWidth="1"/>
-    <col min="6911" max="6915" width="15.44140625" style="76" customWidth="1"/>
-    <col min="6916" max="6920" width="10" style="76" customWidth="1"/>
-    <col min="6921" max="6921" width="13.33203125" style="76" customWidth="1"/>
-    <col min="6922" max="7166" width="10" style="76" customWidth="1"/>
-    <col min="7167" max="7171" width="15.44140625" style="76" customWidth="1"/>
-    <col min="7172" max="7176" width="10" style="76" customWidth="1"/>
-    <col min="7177" max="7177" width="13.33203125" style="76" customWidth="1"/>
-    <col min="7178" max="7422" width="10" style="76" customWidth="1"/>
-    <col min="7423" max="7427" width="15.44140625" style="76" customWidth="1"/>
-    <col min="7428" max="7432" width="10" style="76" customWidth="1"/>
-    <col min="7433" max="7433" width="13.33203125" style="76" customWidth="1"/>
-    <col min="7434" max="7678" width="10" style="76" customWidth="1"/>
-    <col min="7679" max="7683" width="15.44140625" style="76" customWidth="1"/>
-    <col min="7684" max="7688" width="10" style="76" customWidth="1"/>
-    <col min="7689" max="7689" width="13.33203125" style="76" customWidth="1"/>
-    <col min="7690" max="7934" width="10" style="76" customWidth="1"/>
-    <col min="7935" max="7939" width="15.44140625" style="76" customWidth="1"/>
-    <col min="7940" max="7944" width="10" style="76" customWidth="1"/>
-    <col min="7945" max="7945" width="13.33203125" style="76" customWidth="1"/>
-    <col min="7946" max="8190" width="10" style="76" customWidth="1"/>
-    <col min="8191" max="8195" width="15.44140625" style="76" customWidth="1"/>
-    <col min="8196" max="8200" width="10" style="76" customWidth="1"/>
-    <col min="8201" max="8201" width="13.33203125" style="76" customWidth="1"/>
-    <col min="8202" max="8446" width="10" style="76" customWidth="1"/>
-    <col min="8447" max="8451" width="15.44140625" style="76" customWidth="1"/>
-    <col min="8452" max="8456" width="10" style="76" customWidth="1"/>
-    <col min="8457" max="8457" width="13.33203125" style="76" customWidth="1"/>
-    <col min="8458" max="8702" width="10" style="76" customWidth="1"/>
-    <col min="8703" max="8707" width="15.44140625" style="76" customWidth="1"/>
-    <col min="8708" max="8712" width="10" style="76" customWidth="1"/>
-    <col min="8713" max="8713" width="13.33203125" style="76" customWidth="1"/>
-    <col min="8714" max="8958" width="10" style="76" customWidth="1"/>
-    <col min="8959" max="8963" width="15.44140625" style="76" customWidth="1"/>
-    <col min="8964" max="8968" width="10" style="76" customWidth="1"/>
-    <col min="8969" max="8969" width="13.33203125" style="76" customWidth="1"/>
-    <col min="8970" max="9214" width="10" style="76" customWidth="1"/>
-    <col min="9215" max="9219" width="15.44140625" style="76" customWidth="1"/>
-    <col min="9220" max="9224" width="10" style="76" customWidth="1"/>
-    <col min="9225" max="9225" width="13.33203125" style="76" customWidth="1"/>
-    <col min="9226" max="9470" width="10" style="76" customWidth="1"/>
-    <col min="9471" max="9475" width="15.44140625" style="76" customWidth="1"/>
-    <col min="9476" max="9480" width="10" style="76" customWidth="1"/>
-    <col min="9481" max="9481" width="13.33203125" style="76" customWidth="1"/>
-    <col min="9482" max="9726" width="10" style="76" customWidth="1"/>
-    <col min="9727" max="9731" width="15.44140625" style="76" customWidth="1"/>
-    <col min="9732" max="9736" width="10" style="76" customWidth="1"/>
-    <col min="9737" max="9737" width="13.33203125" style="76" customWidth="1"/>
-    <col min="9738" max="9982" width="10" style="76" customWidth="1"/>
-    <col min="9983" max="9987" width="15.44140625" style="76" customWidth="1"/>
-    <col min="9988" max="9992" width="10" style="76" customWidth="1"/>
-    <col min="9993" max="9993" width="13.33203125" style="76" customWidth="1"/>
-    <col min="9994" max="10238" width="10" style="76" customWidth="1"/>
-    <col min="10239" max="10243" width="15.44140625" style="76" customWidth="1"/>
-    <col min="10244" max="10248" width="10" style="76" customWidth="1"/>
-    <col min="10249" max="10249" width="13.33203125" style="76" customWidth="1"/>
-    <col min="10250" max="10494" width="10" style="76" customWidth="1"/>
-    <col min="10495" max="10499" width="15.44140625" style="76" customWidth="1"/>
-    <col min="10500" max="10504" width="10" style="76" customWidth="1"/>
-    <col min="10505" max="10505" width="13.33203125" style="76" customWidth="1"/>
-    <col min="10506" max="10750" width="10" style="76" customWidth="1"/>
-    <col min="10751" max="10755" width="15.44140625" style="76" customWidth="1"/>
-    <col min="10756" max="10760" width="10" style="76" customWidth="1"/>
-    <col min="10761" max="10761" width="13.33203125" style="76" customWidth="1"/>
-    <col min="10762" max="11006" width="10" style="76" customWidth="1"/>
-    <col min="11007" max="11011" width="15.44140625" style="76" customWidth="1"/>
-    <col min="11012" max="11016" width="10" style="76" customWidth="1"/>
-    <col min="11017" max="11017" width="13.33203125" style="76" customWidth="1"/>
-    <col min="11018" max="11262" width="10" style="76" customWidth="1"/>
-    <col min="11263" max="11267" width="15.44140625" style="76" customWidth="1"/>
-    <col min="11268" max="11272" width="10" style="76" customWidth="1"/>
-    <col min="11273" max="11273" width="13.33203125" style="76" customWidth="1"/>
-    <col min="11274" max="11518" width="10" style="76" customWidth="1"/>
-    <col min="11519" max="11523" width="15.44140625" style="76" customWidth="1"/>
-    <col min="11524" max="11528" width="10" style="76" customWidth="1"/>
-    <col min="11529" max="11529" width="13.33203125" style="76" customWidth="1"/>
-    <col min="11530" max="11774" width="10" style="76" customWidth="1"/>
-    <col min="11775" max="11779" width="15.44140625" style="76" customWidth="1"/>
-    <col min="11780" max="11784" width="10" style="76" customWidth="1"/>
-    <col min="11785" max="11785" width="13.33203125" style="76" customWidth="1"/>
-    <col min="11786" max="12030" width="10" style="76" customWidth="1"/>
-    <col min="12031" max="12035" width="15.44140625" style="76" customWidth="1"/>
-    <col min="12036" max="12040" width="10" style="76" customWidth="1"/>
-    <col min="12041" max="12041" width="13.33203125" style="76" customWidth="1"/>
-    <col min="12042" max="12286" width="10" style="76" customWidth="1"/>
-    <col min="12287" max="12291" width="15.44140625" style="76" customWidth="1"/>
-    <col min="12292" max="12296" width="10" style="76" customWidth="1"/>
-    <col min="12297" max="12297" width="13.33203125" style="76" customWidth="1"/>
-    <col min="12298" max="12542" width="10" style="76" customWidth="1"/>
-    <col min="12543" max="12547" width="15.44140625" style="76" customWidth="1"/>
-    <col min="12548" max="12552" width="10" style="76" customWidth="1"/>
-    <col min="12553" max="12553" width="13.33203125" style="76" customWidth="1"/>
-    <col min="12554" max="12798" width="10" style="76" customWidth="1"/>
-    <col min="12799" max="12803" width="15.44140625" style="76" customWidth="1"/>
-    <col min="12804" max="12808" width="10" style="76" customWidth="1"/>
-    <col min="12809" max="12809" width="13.33203125" style="76" customWidth="1"/>
-    <col min="12810" max="13054" width="10" style="76" customWidth="1"/>
-    <col min="13055" max="13059" width="15.44140625" style="76" customWidth="1"/>
-    <col min="13060" max="13064" width="10" style="76" customWidth="1"/>
-    <col min="13065" max="13065" width="13.33203125" style="76" customWidth="1"/>
-    <col min="13066" max="13310" width="10" style="76" customWidth="1"/>
-    <col min="13311" max="13315" width="15.44140625" style="76" customWidth="1"/>
-    <col min="13316" max="13320" width="10" style="76" customWidth="1"/>
-    <col min="13321" max="13321" width="13.33203125" style="76" customWidth="1"/>
-    <col min="13322" max="13566" width="10" style="76" customWidth="1"/>
-    <col min="13567" max="13571" width="15.44140625" style="76" customWidth="1"/>
-    <col min="13572" max="13576" width="10" style="76" customWidth="1"/>
-    <col min="13577" max="13577" width="13.33203125" style="76" customWidth="1"/>
-    <col min="13578" max="13822" width="10" style="76" customWidth="1"/>
-    <col min="13823" max="13827" width="15.44140625" style="76" customWidth="1"/>
-    <col min="13828" max="13832" width="10" style="76" customWidth="1"/>
-    <col min="13833" max="13833" width="13.33203125" style="76" customWidth="1"/>
-    <col min="13834" max="14078" width="10" style="76" customWidth="1"/>
-    <col min="14079" max="14083" width="15.44140625" style="76" customWidth="1"/>
-    <col min="14084" max="14088" width="10" style="76" customWidth="1"/>
-    <col min="14089" max="14089" width="13.33203125" style="76" customWidth="1"/>
-    <col min="14090" max="14334" width="10" style="76" customWidth="1"/>
-    <col min="14335" max="14339" width="15.44140625" style="76" customWidth="1"/>
-    <col min="14340" max="14344" width="10" style="76" customWidth="1"/>
-    <col min="14345" max="14345" width="13.33203125" style="76" customWidth="1"/>
-    <col min="14346" max="14590" width="10" style="76" customWidth="1"/>
-    <col min="14591" max="14595" width="15.44140625" style="76" customWidth="1"/>
-    <col min="14596" max="14600" width="10" style="76" customWidth="1"/>
-    <col min="14601" max="14601" width="13.33203125" style="76" customWidth="1"/>
-    <col min="14602" max="14846" width="10" style="76" customWidth="1"/>
-    <col min="14847" max="14851" width="15.44140625" style="76" customWidth="1"/>
-    <col min="14852" max="14856" width="10" style="76" customWidth="1"/>
-    <col min="14857" max="14857" width="13.33203125" style="76" customWidth="1"/>
-    <col min="14858" max="15102" width="10" style="76" customWidth="1"/>
-    <col min="15103" max="15107" width="15.44140625" style="76" customWidth="1"/>
-    <col min="15108" max="15112" width="10" style="76" customWidth="1"/>
-    <col min="15113" max="15113" width="13.33203125" style="76" customWidth="1"/>
-    <col min="15114" max="15358" width="10" style="76" customWidth="1"/>
-    <col min="15359" max="15363" width="15.44140625" style="76" customWidth="1"/>
-    <col min="15364" max="15368" width="10" style="76" customWidth="1"/>
-    <col min="15369" max="15369" width="13.33203125" style="76" customWidth="1"/>
-    <col min="15370" max="15614" width="10" style="76" customWidth="1"/>
-    <col min="15615" max="15619" width="15.44140625" style="76" customWidth="1"/>
-    <col min="15620" max="15624" width="10" style="76" customWidth="1"/>
-    <col min="15625" max="15625" width="13.33203125" style="76" customWidth="1"/>
-    <col min="15626" max="15870" width="10" style="76" customWidth="1"/>
-    <col min="15871" max="15875" width="15.44140625" style="76" customWidth="1"/>
-    <col min="15876" max="15880" width="10" style="76" customWidth="1"/>
-    <col min="15881" max="15881" width="13.33203125" style="76" customWidth="1"/>
-    <col min="15882" max="16126" width="10" style="76" customWidth="1"/>
-    <col min="16127" max="16131" width="15.44140625" style="76" customWidth="1"/>
-    <col min="16132" max="16136" width="10" style="76" customWidth="1"/>
-    <col min="16137" max="16137" width="13.33203125" style="76" customWidth="1"/>
-    <col min="16138" max="16384" width="10" style="76" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="74" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="74" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="74" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" style="74" customWidth="1"/>
+    <col min="6" max="8" width="10" style="74" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10" max="254" width="10" style="74" customWidth="1"/>
+    <col min="255" max="259" width="15.44140625" style="74" customWidth="1"/>
+    <col min="260" max="264" width="10" style="74" customWidth="1"/>
+    <col min="265" max="265" width="13.33203125" style="74" customWidth="1"/>
+    <col min="266" max="510" width="10" style="74" customWidth="1"/>
+    <col min="511" max="515" width="15.44140625" style="74" customWidth="1"/>
+    <col min="516" max="520" width="10" style="74" customWidth="1"/>
+    <col min="521" max="521" width="13.33203125" style="74" customWidth="1"/>
+    <col min="522" max="766" width="10" style="74" customWidth="1"/>
+    <col min="767" max="771" width="15.44140625" style="74" customWidth="1"/>
+    <col min="772" max="776" width="10" style="74" customWidth="1"/>
+    <col min="777" max="777" width="13.33203125" style="74" customWidth="1"/>
+    <col min="778" max="1022" width="10" style="74" customWidth="1"/>
+    <col min="1023" max="1027" width="15.44140625" style="74" customWidth="1"/>
+    <col min="1028" max="1032" width="10" style="74" customWidth="1"/>
+    <col min="1033" max="1033" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1034" max="1278" width="10" style="74" customWidth="1"/>
+    <col min="1279" max="1283" width="15.44140625" style="74" customWidth="1"/>
+    <col min="1284" max="1288" width="10" style="74" customWidth="1"/>
+    <col min="1289" max="1289" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1290" max="1534" width="10" style="74" customWidth="1"/>
+    <col min="1535" max="1539" width="15.44140625" style="74" customWidth="1"/>
+    <col min="1540" max="1544" width="10" style="74" customWidth="1"/>
+    <col min="1545" max="1545" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1546" max="1790" width="10" style="74" customWidth="1"/>
+    <col min="1791" max="1795" width="15.44140625" style="74" customWidth="1"/>
+    <col min="1796" max="1800" width="10" style="74" customWidth="1"/>
+    <col min="1801" max="1801" width="13.33203125" style="74" customWidth="1"/>
+    <col min="1802" max="2046" width="10" style="74" customWidth="1"/>
+    <col min="2047" max="2051" width="15.44140625" style="74" customWidth="1"/>
+    <col min="2052" max="2056" width="10" style="74" customWidth="1"/>
+    <col min="2057" max="2057" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2058" max="2302" width="10" style="74" customWidth="1"/>
+    <col min="2303" max="2307" width="15.44140625" style="74" customWidth="1"/>
+    <col min="2308" max="2312" width="10" style="74" customWidth="1"/>
+    <col min="2313" max="2313" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2314" max="2558" width="10" style="74" customWidth="1"/>
+    <col min="2559" max="2563" width="15.44140625" style="74" customWidth="1"/>
+    <col min="2564" max="2568" width="10" style="74" customWidth="1"/>
+    <col min="2569" max="2569" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2570" max="2814" width="10" style="74" customWidth="1"/>
+    <col min="2815" max="2819" width="15.44140625" style="74" customWidth="1"/>
+    <col min="2820" max="2824" width="10" style="74" customWidth="1"/>
+    <col min="2825" max="2825" width="13.33203125" style="74" customWidth="1"/>
+    <col min="2826" max="3070" width="10" style="74" customWidth="1"/>
+    <col min="3071" max="3075" width="15.44140625" style="74" customWidth="1"/>
+    <col min="3076" max="3080" width="10" style="74" customWidth="1"/>
+    <col min="3081" max="3081" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3082" max="3326" width="10" style="74" customWidth="1"/>
+    <col min="3327" max="3331" width="15.44140625" style="74" customWidth="1"/>
+    <col min="3332" max="3336" width="10" style="74" customWidth="1"/>
+    <col min="3337" max="3337" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3338" max="3582" width="10" style="74" customWidth="1"/>
+    <col min="3583" max="3587" width="15.44140625" style="74" customWidth="1"/>
+    <col min="3588" max="3592" width="10" style="74" customWidth="1"/>
+    <col min="3593" max="3593" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3594" max="3838" width="10" style="74" customWidth="1"/>
+    <col min="3839" max="3843" width="15.44140625" style="74" customWidth="1"/>
+    <col min="3844" max="3848" width="10" style="74" customWidth="1"/>
+    <col min="3849" max="3849" width="13.33203125" style="74" customWidth="1"/>
+    <col min="3850" max="4094" width="10" style="74" customWidth="1"/>
+    <col min="4095" max="4099" width="15.44140625" style="74" customWidth="1"/>
+    <col min="4100" max="4104" width="10" style="74" customWidth="1"/>
+    <col min="4105" max="4105" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4106" max="4350" width="10" style="74" customWidth="1"/>
+    <col min="4351" max="4355" width="15.44140625" style="74" customWidth="1"/>
+    <col min="4356" max="4360" width="10" style="74" customWidth="1"/>
+    <col min="4361" max="4361" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4362" max="4606" width="10" style="74" customWidth="1"/>
+    <col min="4607" max="4611" width="15.44140625" style="74" customWidth="1"/>
+    <col min="4612" max="4616" width="10" style="74" customWidth="1"/>
+    <col min="4617" max="4617" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4618" max="4862" width="10" style="74" customWidth="1"/>
+    <col min="4863" max="4867" width="15.44140625" style="74" customWidth="1"/>
+    <col min="4868" max="4872" width="10" style="74" customWidth="1"/>
+    <col min="4873" max="4873" width="13.33203125" style="74" customWidth="1"/>
+    <col min="4874" max="5118" width="10" style="74" customWidth="1"/>
+    <col min="5119" max="5123" width="15.44140625" style="74" customWidth="1"/>
+    <col min="5124" max="5128" width="10" style="74" customWidth="1"/>
+    <col min="5129" max="5129" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5130" max="5374" width="10" style="74" customWidth="1"/>
+    <col min="5375" max="5379" width="15.44140625" style="74" customWidth="1"/>
+    <col min="5380" max="5384" width="10" style="74" customWidth="1"/>
+    <col min="5385" max="5385" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5386" max="5630" width="10" style="74" customWidth="1"/>
+    <col min="5631" max="5635" width="15.44140625" style="74" customWidth="1"/>
+    <col min="5636" max="5640" width="10" style="74" customWidth="1"/>
+    <col min="5641" max="5641" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5642" max="5886" width="10" style="74" customWidth="1"/>
+    <col min="5887" max="5891" width="15.44140625" style="74" customWidth="1"/>
+    <col min="5892" max="5896" width="10" style="74" customWidth="1"/>
+    <col min="5897" max="5897" width="13.33203125" style="74" customWidth="1"/>
+    <col min="5898" max="6142" width="10" style="74" customWidth="1"/>
+    <col min="6143" max="6147" width="15.44140625" style="74" customWidth="1"/>
+    <col min="6148" max="6152" width="10" style="74" customWidth="1"/>
+    <col min="6153" max="6153" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6154" max="6398" width="10" style="74" customWidth="1"/>
+    <col min="6399" max="6403" width="15.44140625" style="74" customWidth="1"/>
+    <col min="6404" max="6408" width="10" style="74" customWidth="1"/>
+    <col min="6409" max="6409" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6410" max="6654" width="10" style="74" customWidth="1"/>
+    <col min="6655" max="6659" width="15.44140625" style="74" customWidth="1"/>
+    <col min="6660" max="6664" width="10" style="74" customWidth="1"/>
+    <col min="6665" max="6665" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6666" max="6910" width="10" style="74" customWidth="1"/>
+    <col min="6911" max="6915" width="15.44140625" style="74" customWidth="1"/>
+    <col min="6916" max="6920" width="10" style="74" customWidth="1"/>
+    <col min="6921" max="6921" width="13.33203125" style="74" customWidth="1"/>
+    <col min="6922" max="7166" width="10" style="74" customWidth="1"/>
+    <col min="7167" max="7171" width="15.44140625" style="74" customWidth="1"/>
+    <col min="7172" max="7176" width="10" style="74" customWidth="1"/>
+    <col min="7177" max="7177" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7178" max="7422" width="10" style="74" customWidth="1"/>
+    <col min="7423" max="7427" width="15.44140625" style="74" customWidth="1"/>
+    <col min="7428" max="7432" width="10" style="74" customWidth="1"/>
+    <col min="7433" max="7433" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7434" max="7678" width="10" style="74" customWidth="1"/>
+    <col min="7679" max="7683" width="15.44140625" style="74" customWidth="1"/>
+    <col min="7684" max="7688" width="10" style="74" customWidth="1"/>
+    <col min="7689" max="7689" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7690" max="7934" width="10" style="74" customWidth="1"/>
+    <col min="7935" max="7939" width="15.44140625" style="74" customWidth="1"/>
+    <col min="7940" max="7944" width="10" style="74" customWidth="1"/>
+    <col min="7945" max="7945" width="13.33203125" style="74" customWidth="1"/>
+    <col min="7946" max="8190" width="10" style="74" customWidth="1"/>
+    <col min="8191" max="8195" width="15.44140625" style="74" customWidth="1"/>
+    <col min="8196" max="8200" width="10" style="74" customWidth="1"/>
+    <col min="8201" max="8201" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8202" max="8446" width="10" style="74" customWidth="1"/>
+    <col min="8447" max="8451" width="15.44140625" style="74" customWidth="1"/>
+    <col min="8452" max="8456" width="10" style="74" customWidth="1"/>
+    <col min="8457" max="8457" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8458" max="8702" width="10" style="74" customWidth="1"/>
+    <col min="8703" max="8707" width="15.44140625" style="74" customWidth="1"/>
+    <col min="8708" max="8712" width="10" style="74" customWidth="1"/>
+    <col min="8713" max="8713" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8714" max="8958" width="10" style="74" customWidth="1"/>
+    <col min="8959" max="8963" width="15.44140625" style="74" customWidth="1"/>
+    <col min="8964" max="8968" width="10" style="74" customWidth="1"/>
+    <col min="8969" max="8969" width="13.33203125" style="74" customWidth="1"/>
+    <col min="8970" max="9214" width="10" style="74" customWidth="1"/>
+    <col min="9215" max="9219" width="15.44140625" style="74" customWidth="1"/>
+    <col min="9220" max="9224" width="10" style="74" customWidth="1"/>
+    <col min="9225" max="9225" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9226" max="9470" width="10" style="74" customWidth="1"/>
+    <col min="9471" max="9475" width="15.44140625" style="74" customWidth="1"/>
+    <col min="9476" max="9480" width="10" style="74" customWidth="1"/>
+    <col min="9481" max="9481" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9482" max="9726" width="10" style="74" customWidth="1"/>
+    <col min="9727" max="9731" width="15.44140625" style="74" customWidth="1"/>
+    <col min="9732" max="9736" width="10" style="74" customWidth="1"/>
+    <col min="9737" max="9737" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9738" max="9982" width="10" style="74" customWidth="1"/>
+    <col min="9983" max="9987" width="15.44140625" style="74" customWidth="1"/>
+    <col min="9988" max="9992" width="10" style="74" customWidth="1"/>
+    <col min="9993" max="9993" width="13.33203125" style="74" customWidth="1"/>
+    <col min="9994" max="10238" width="10" style="74" customWidth="1"/>
+    <col min="10239" max="10243" width="15.44140625" style="74" customWidth="1"/>
+    <col min="10244" max="10248" width="10" style="74" customWidth="1"/>
+    <col min="10249" max="10249" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10250" max="10494" width="10" style="74" customWidth="1"/>
+    <col min="10495" max="10499" width="15.44140625" style="74" customWidth="1"/>
+    <col min="10500" max="10504" width="10" style="74" customWidth="1"/>
+    <col min="10505" max="10505" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10506" max="10750" width="10" style="74" customWidth="1"/>
+    <col min="10751" max="10755" width="15.44140625" style="74" customWidth="1"/>
+    <col min="10756" max="10760" width="10" style="74" customWidth="1"/>
+    <col min="10761" max="10761" width="13.33203125" style="74" customWidth="1"/>
+    <col min="10762" max="11006" width="10" style="74" customWidth="1"/>
+    <col min="11007" max="11011" width="15.44140625" style="74" customWidth="1"/>
+    <col min="11012" max="11016" width="10" style="74" customWidth="1"/>
+    <col min="11017" max="11017" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11018" max="11262" width="10" style="74" customWidth="1"/>
+    <col min="11263" max="11267" width="15.44140625" style="74" customWidth="1"/>
+    <col min="11268" max="11272" width="10" style="74" customWidth="1"/>
+    <col min="11273" max="11273" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11274" max="11518" width="10" style="74" customWidth="1"/>
+    <col min="11519" max="11523" width="15.44140625" style="74" customWidth="1"/>
+    <col min="11524" max="11528" width="10" style="74" customWidth="1"/>
+    <col min="11529" max="11529" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11530" max="11774" width="10" style="74" customWidth="1"/>
+    <col min="11775" max="11779" width="15.44140625" style="74" customWidth="1"/>
+    <col min="11780" max="11784" width="10" style="74" customWidth="1"/>
+    <col min="11785" max="11785" width="13.33203125" style="74" customWidth="1"/>
+    <col min="11786" max="12030" width="10" style="74" customWidth="1"/>
+    <col min="12031" max="12035" width="15.44140625" style="74" customWidth="1"/>
+    <col min="12036" max="12040" width="10" style="74" customWidth="1"/>
+    <col min="12041" max="12041" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12042" max="12286" width="10" style="74" customWidth="1"/>
+    <col min="12287" max="12291" width="15.44140625" style="74" customWidth="1"/>
+    <col min="12292" max="12296" width="10" style="74" customWidth="1"/>
+    <col min="12297" max="12297" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12298" max="12542" width="10" style="74" customWidth="1"/>
+    <col min="12543" max="12547" width="15.44140625" style="74" customWidth="1"/>
+    <col min="12548" max="12552" width="10" style="74" customWidth="1"/>
+    <col min="12553" max="12553" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12554" max="12798" width="10" style="74" customWidth="1"/>
+    <col min="12799" max="12803" width="15.44140625" style="74" customWidth="1"/>
+    <col min="12804" max="12808" width="10" style="74" customWidth="1"/>
+    <col min="12809" max="12809" width="13.33203125" style="74" customWidth="1"/>
+    <col min="12810" max="13054" width="10" style="74" customWidth="1"/>
+    <col min="13055" max="13059" width="15.44140625" style="74" customWidth="1"/>
+    <col min="13060" max="13064" width="10" style="74" customWidth="1"/>
+    <col min="13065" max="13065" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13066" max="13310" width="10" style="74" customWidth="1"/>
+    <col min="13311" max="13315" width="15.44140625" style="74" customWidth="1"/>
+    <col min="13316" max="13320" width="10" style="74" customWidth="1"/>
+    <col min="13321" max="13321" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13322" max="13566" width="10" style="74" customWidth="1"/>
+    <col min="13567" max="13571" width="15.44140625" style="74" customWidth="1"/>
+    <col min="13572" max="13576" width="10" style="74" customWidth="1"/>
+    <col min="13577" max="13577" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13578" max="13822" width="10" style="74" customWidth="1"/>
+    <col min="13823" max="13827" width="15.44140625" style="74" customWidth="1"/>
+    <col min="13828" max="13832" width="10" style="74" customWidth="1"/>
+    <col min="13833" max="13833" width="13.33203125" style="74" customWidth="1"/>
+    <col min="13834" max="14078" width="10" style="74" customWidth="1"/>
+    <col min="14079" max="14083" width="15.44140625" style="74" customWidth="1"/>
+    <col min="14084" max="14088" width="10" style="74" customWidth="1"/>
+    <col min="14089" max="14089" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14090" max="14334" width="10" style="74" customWidth="1"/>
+    <col min="14335" max="14339" width="15.44140625" style="74" customWidth="1"/>
+    <col min="14340" max="14344" width="10" style="74" customWidth="1"/>
+    <col min="14345" max="14345" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14346" max="14590" width="10" style="74" customWidth="1"/>
+    <col min="14591" max="14595" width="15.44140625" style="74" customWidth="1"/>
+    <col min="14596" max="14600" width="10" style="74" customWidth="1"/>
+    <col min="14601" max="14601" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14602" max="14846" width="10" style="74" customWidth="1"/>
+    <col min="14847" max="14851" width="15.44140625" style="74" customWidth="1"/>
+    <col min="14852" max="14856" width="10" style="74" customWidth="1"/>
+    <col min="14857" max="14857" width="13.33203125" style="74" customWidth="1"/>
+    <col min="14858" max="15102" width="10" style="74" customWidth="1"/>
+    <col min="15103" max="15107" width="15.44140625" style="74" customWidth="1"/>
+    <col min="15108" max="15112" width="10" style="74" customWidth="1"/>
+    <col min="15113" max="15113" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15114" max="15358" width="10" style="74" customWidth="1"/>
+    <col min="15359" max="15363" width="15.44140625" style="74" customWidth="1"/>
+    <col min="15364" max="15368" width="10" style="74" customWidth="1"/>
+    <col min="15369" max="15369" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15370" max="15614" width="10" style="74" customWidth="1"/>
+    <col min="15615" max="15619" width="15.44140625" style="74" customWidth="1"/>
+    <col min="15620" max="15624" width="10" style="74" customWidth="1"/>
+    <col min="15625" max="15625" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15626" max="15870" width="10" style="74" customWidth="1"/>
+    <col min="15871" max="15875" width="15.44140625" style="74" customWidth="1"/>
+    <col min="15876" max="15880" width="10" style="74" customWidth="1"/>
+    <col min="15881" max="15881" width="13.33203125" style="74" customWidth="1"/>
+    <col min="15882" max="16126" width="10" style="74" customWidth="1"/>
+    <col min="16127" max="16131" width="15.44140625" style="74" customWidth="1"/>
+    <col min="16132" max="16136" width="10" style="74" customWidth="1"/>
+    <col min="16137" max="16137" width="13.33203125" style="74" customWidth="1"/>
+    <col min="16138" max="16384" width="10" style="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="122" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="110"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="37" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
+      <c r="A9" s="37"/>
     </row>
     <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="118" t="s">
         <v>256</v>
       </c>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="117"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
+      <c r="A11" s="75"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
     </row>
     <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="76" t="s">
         <v>257</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="76" t="s">
         <v>258</v>
       </c>
-      <c r="C12" s="78" t="s">
+      <c r="C12" s="76" t="s">
         <v>259</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="39" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="39" t="s">
         <v>267</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="120" t="s">
+      <c r="A17" s="121" t="s">
         <v>269</v>
       </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="117"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="120"/>
     </row>
     <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="D19" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="39" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="39" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
     </row>
     <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="121" t="s">
         <v>285</v>
       </c>
-      <c r="B23" s="116"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="117"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="120"/>
     </row>
     <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D24" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="123"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
+      <c r="A30" s="116"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="119"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
+      <c r="A31" s="115"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="119"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
+      <c r="A32" s="115"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="119"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
+      <c r="A33" s="115"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="119"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
+      <c r="A34" s="115"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="115"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="79"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="79"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="79"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
+      <c r="A37" s="77"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="77"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
+      <c r="A39" s="37" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="75"/>
-      <c r="B41" s="75"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
+      <c r="A41" s="73"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
-      <c r="B42" s="79"/>
-      <c r="C42" s="79"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
+      <c r="A42" s="73"/>
+      <c r="B42" s="77"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
-      <c r="B43" s="79"/>
-      <c r="C43" s="79"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="79"/>
+      <c r="A43" s="73"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="123"/>
-      <c r="B44" s="79"/>
-      <c r="C44" s="79"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
+      <c r="A44" s="116"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="119"/>
-      <c r="B45" s="79"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
+      <c r="A45" s="115"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="119"/>
-      <c r="B46" s="79"/>
-      <c r="C46" s="79"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
+      <c r="A46" s="115"/>
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="119"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="79"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="79"/>
+      <c r="A47" s="115"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="119"/>
-      <c r="B48" s="79"/>
-      <c r="C48" s="79"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
+      <c r="A48" s="115"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="119"/>
-      <c r="B49" s="79"/>
-      <c r="C49" s="79"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="79"/>
+      <c r="A49" s="115"/>
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="77"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="119"/>
-      <c r="B50" s="79"/>
-      <c r="C50" s="79"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="45"/>
+      <c r="A50" s="115"/>
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="43"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="119"/>
-      <c r="B51" s="79"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="45"/>
+      <c r="A51" s="115"/>
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="119"/>
-      <c r="B52" s="79"/>
-      <c r="C52" s="79"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="45"/>
+      <c r="A52" s="115"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="43"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="119"/>
-      <c r="B53" s="79"/>
-      <c r="C53" s="79"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="45"/>
+      <c r="A53" s="115"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="45"/>
+      <c r="E53" s="43"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="119"/>
-      <c r="B54" s="79"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="46"/>
+      <c r="A54" s="115"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="45"/>
+      <c r="E54" s="44"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="119"/>
-      <c r="B55" s="79"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="79"/>
+      <c r="A55" s="115"/>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="77"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="119"/>
-      <c r="B56" s="79"/>
-      <c r="C56" s="79"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="79"/>
+      <c r="A56" s="115"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="77"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="119"/>
-      <c r="B57" s="79"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="79"/>
+      <c r="A57" s="115"/>
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="45"/>
+      <c r="E57" s="77"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="119"/>
-      <c r="B58" s="79"/>
-      <c r="C58" s="79"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="79"/>
+      <c r="A58" s="115"/>
+      <c r="B58" s="77"/>
+      <c r="C58" s="77"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="77"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="119"/>
-      <c r="B59" s="79"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="79"/>
+      <c r="A59" s="115"/>
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="45"/>
+      <c r="E59" s="77"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="119"/>
-      <c r="B60" s="79"/>
-      <c r="C60" s="79"/>
-      <c r="D60" s="47"/>
-      <c r="E60" s="79"/>
+      <c r="A60" s="115"/>
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="45"/>
+      <c r="E60" s="77"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="38" t="s">
+      <c r="A63" s="36" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="122" t="s">
+      <c r="A65" s="114" t="s">
         <v>291</v>
       </c>
-      <c r="B65" s="119"/>
-      <c r="C65" s="119"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
+      <c r="B65" s="115"/>
+      <c r="C65" s="115"/>
+      <c r="D65" s="115"/>
+      <c r="E65" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="D30:D34"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A30:A34"/>
     <mergeCell ref="E30:E34"/>
     <mergeCell ref="A44:A60"/>
     <mergeCell ref="C30:C34"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="D30:D34"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A1:E3"/>
-    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7826,8 +7826,8 @@
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="68" customWidth="1"/>
-    <col min="11" max="11" width="7.44140625" style="68" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="66" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" style="66" customWidth="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7841,78 +7841,78 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="68" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="66" customWidth="1"/>
     <col min="2" max="2" width="60.21875" style="2" customWidth="1"/>
     <col min="3" max="3" width="24.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="68" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="68" customWidth="1"/>
-    <col min="8" max="8" width="35.33203125" style="68" customWidth="1"/>
+    <col min="4" max="4" width="41.77734375" style="66" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="66" customWidth="1"/>
+    <col min="8" max="8" width="35.33203125" style="66" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="85" t="s">
+      <c r="D1" s="83" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="88" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="90"/>
+      <c r="D3" s="89"/>
     </row>
     <row r="4" spans="1:8" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="88" t="s">
+      <c r="A4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90"/>
+      <c r="D4" s="89"/>
     </row>
     <row r="5" spans="1:8" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="91"/>
+      <c r="D5" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7928,65 +7928,129 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.21875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="25.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="49.21875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="25.77734375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" style="7" customWidth="1"/>
-    <col min="9" max="10" width="9" style="7" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="9" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="15.88671875" style="123" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="82" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="82" customWidth="1"/>
+    <col min="4" max="4" width="57.33203125" style="82" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="123" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="123" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" style="82" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" style="82" customWidth="1"/>
+    <col min="9" max="10" width="9" style="82" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" style="82" customWidth="1"/>
+    <col min="12" max="12" width="9" style="82" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="81" t="s">
+    <row r="1" spans="1:7" s="82" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="81" t="s">
+      <c r="F1" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="85" t="s">
+      <c r="G1" s="83" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="14.4" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+    </row>
+    <row r="3" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+    </row>
+    <row r="4" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+    </row>
+    <row r="5" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+    </row>
+    <row r="6" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
+    </row>
+    <row r="7" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+    </row>
+    <row r="8" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
+    </row>
+    <row r="9" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="123"/>
+    </row>
+    <row r="10" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+    </row>
+    <row r="11" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="123"/>
+    </row>
+    <row r="12" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+    </row>
+    <row r="13" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="123"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="123"/>
+    </row>
+    <row r="14" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
+    </row>
+    <row r="15" spans="1:7" s="82" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="123"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
+    </row>
+    <row r="16" spans="1:7" s="82" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+    </row>
+    <row r="22" spans="1:6" s="82" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7995,81 +8059,81 @@
   <dimension ref="A1:IM4"/>
   <sheetFormatPr defaultRowHeight="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="83" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="83" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="83" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="83" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" style="83" customWidth="1"/>
-    <col min="6" max="12" width="11.109375" style="83" customWidth="1"/>
-    <col min="13" max="13" width="12" style="83" customWidth="1"/>
-    <col min="14" max="14" width="44.44140625" style="83" customWidth="1"/>
-    <col min="15" max="247" width="30" style="83" customWidth="1"/>
-    <col min="248" max="16384" width="8.88671875" style="84"/>
+    <col min="1" max="1" width="15.33203125" style="81" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="81" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="81" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" style="81" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="81" customWidth="1"/>
+    <col min="6" max="12" width="11.109375" style="81" customWidth="1"/>
+    <col min="13" max="13" width="12" style="81" customWidth="1"/>
+    <col min="14" max="14" width="44.44140625" style="81" customWidth="1"/>
+    <col min="15" max="247" width="30" style="81" customWidth="1"/>
+    <col min="248" max="16384" width="8.88671875" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="91" t="s">
         <v>303</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="91" t="s">
         <v>306</v>
       </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="93" t="s">
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="92" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="83" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="81" t="s">
+    <row r="2" spans="1:14" s="81" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="91"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="D2" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="81" t="s">
+      <c r="J2" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="81" t="s">
+      <c r="K2" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="81" t="s">
+      <c r="L2" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="82" t="s">
+      <c r="M2" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="93"/>
-    </row>
-    <row r="4" spans="1:14" s="83" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N2" s="92"/>
+    </row>
+    <row r="4" spans="1:14" s="81" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -8094,59 +8158,59 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="29.4" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" style="23" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="24" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" style="24" customWidth="1"/>
-    <col min="6" max="6" width="58.77734375" style="25" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="10" style="26" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" style="22" customWidth="1"/>
+    <col min="6" max="6" width="58.77734375" style="23" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" style="24" customWidth="1"/>
+    <col min="8" max="8" width="10" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-    </row>
-    <row r="2" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+    </row>
+    <row r="2" spans="1:8" s="26" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="82" t="s">
+      <c r="D2" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="F2" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="82" t="s">
+      <c r="G2" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="82" t="s">
+      <c r="H2" s="80" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="29" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:8" s="30" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:8" s="30" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:8" s="30" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:8" s="30" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:8" s="27" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -8165,119 +8229,119 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" style="61" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="61" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" style="62" customWidth="1"/>
-    <col min="5" max="7" width="30.5546875" style="63" customWidth="1"/>
-    <col min="8" max="8" width="13" style="61" customWidth="1"/>
-    <col min="9" max="9" width="34.21875" style="63" customWidth="1"/>
-    <col min="10" max="10" width="13" style="62" customWidth="1"/>
-    <col min="11" max="11" width="34.21875" style="63" customWidth="1"/>
-    <col min="12" max="12" width="13" style="62" customWidth="1"/>
-    <col min="13" max="13" width="11" style="62" customWidth="1"/>
-    <col min="14" max="14" width="34.21875" style="63" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" style="61" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.44140625" style="62" customWidth="1"/>
-    <col min="18" max="18" width="13" style="62" customWidth="1"/>
-    <col min="19" max="19" width="11.21875" style="61" customWidth="1"/>
-    <col min="20" max="20" width="16.109375" style="61" customWidth="1"/>
-    <col min="21" max="21" width="9" style="61" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="61"/>
+    <col min="1" max="1" width="13.77734375" style="59" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="59" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5546875" style="60" customWidth="1"/>
+    <col min="5" max="7" width="30.5546875" style="61" customWidth="1"/>
+    <col min="8" max="8" width="13" style="59" customWidth="1"/>
+    <col min="9" max="9" width="34.21875" style="61" customWidth="1"/>
+    <col min="10" max="10" width="13" style="60" customWidth="1"/>
+    <col min="11" max="11" width="34.21875" style="61" customWidth="1"/>
+    <col min="12" max="12" width="13" style="60" customWidth="1"/>
+    <col min="13" max="13" width="11" style="60" customWidth="1"/>
+    <col min="14" max="14" width="34.21875" style="61" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" style="59" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="59" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.44140625" style="60" customWidth="1"/>
+    <col min="18" max="18" width="13" style="60" customWidth="1"/>
+    <col min="19" max="19" width="11.21875" style="59" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" style="59" customWidth="1"/>
+    <col min="21" max="21" width="9" style="59" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="60" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+    <row r="1" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="95" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="98" t="s">
+      <c r="B1" s="97" t="s">
         <v>303</v>
       </c>
-      <c r="C1" s="98" t="s">
+      <c r="C1" s="97" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="100" t="s">
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="92" t="s">
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92" t="s">
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="60" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="80" t="s">
+    <row r="2" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="96"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="81" t="s">
+      <c r="J2" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="81" t="s">
+      <c r="K2" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="81" t="s">
+      <c r="L2" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="81" t="s">
+      <c r="M2" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="81" t="s">
+      <c r="O2" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="81" t="s">
+      <c r="P2" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="81" t="s">
+      <c r="Q2" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="80" t="s">
+      <c r="R2" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="80" t="s">
+      <c r="S2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="92"/>
-    </row>
-    <row r="3" spans="1:20" s="60" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="T2" s="91"/>
+    </row>
+    <row r="3" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="T1:T2"/>
@@ -8302,7 +8366,7 @@
   <dimension ref="A1:IT2"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.21875" style="27" customWidth="1"/>
+    <col min="1" max="2" width="20.21875" style="25" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" style="5" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" style="5" customWidth="1"/>
@@ -8315,56 +8379,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="102" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102" t="s">
         <v>299</v>
       </c>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="104" t="s">
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="103" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="K2" s="104"/>
+      <c r="K2" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8383,2161 +8447,2161 @@
   <dimension ref="A1:E145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="59" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" style="59" customWidth="1"/>
-    <col min="3" max="3" width="75.44140625" style="59" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" style="59" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="59" customWidth="1"/>
-    <col min="6" max="6" width="9" style="59" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="59"/>
+    <col min="1" max="1" width="20.21875" style="57" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" style="57" customWidth="1"/>
+    <col min="3" max="3" width="75.44140625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" style="57" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="57" customWidth="1"/>
+    <col min="6" max="6" width="9" style="57" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
-    </row>
-    <row r="2" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
+    </row>
+    <row r="2" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="32" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="10" customFormat="1" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:5" s="8" customFormat="1" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-    </row>
-    <row r="4" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+    </row>
+    <row r="4" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="12"/>
-    </row>
-    <row r="5" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="12"/>
-    </row>
-    <row r="6" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="12"/>
-    </row>
-    <row r="7" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="12"/>
-    </row>
-    <row r="8" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="12"/>
-    </row>
-    <row r="9" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="12"/>
-    </row>
-    <row r="11" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="12"/>
-    </row>
-    <row r="12" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="12"/>
-    </row>
-    <row r="13" spans="1:5" s="9" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55" t="s">
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" spans="1:5" s="7" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="12"/>
-    </row>
-    <row r="14" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="12"/>
-    </row>
-    <row r="15" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="12"/>
-    </row>
-    <row r="16" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="55" t="s">
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="1:5" s="10" customFormat="1" ht="22.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" spans="1:5" s="8" customFormat="1" ht="22.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-    </row>
-    <row r="20" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+    </row>
+    <row r="20" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="12"/>
-    </row>
-    <row r="21" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48" t="s">
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="12"/>
-    </row>
-    <row r="22" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="12"/>
-    </row>
-    <row r="23" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="12"/>
-    </row>
-    <row r="24" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="48" t="s">
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C24" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="12"/>
-    </row>
-    <row r="25" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="48" t="s">
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E25" s="12"/>
-    </row>
-    <row r="26" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48" t="s">
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="12"/>
-    </row>
-    <row r="27" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="12"/>
-    </row>
-    <row r="28" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="48" t="s">
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="12"/>
-    </row>
-    <row r="29" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="48" t="s">
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="48" t="s">
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="12"/>
-    </row>
-    <row r="31" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="48" t="s">
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="12"/>
-    </row>
-    <row r="32" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="48" t="s">
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="12"/>
-    </row>
-    <row r="33" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="48" t="s">
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="12"/>
-    </row>
-    <row r="34" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="48" t="s">
+      <c r="E33" s="10"/>
+    </row>
+    <row r="34" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="12"/>
-    </row>
-    <row r="35" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="48" t="s">
+      <c r="E34" s="10"/>
+    </row>
+    <row r="35" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="12"/>
-    </row>
-    <row r="36" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="48" t="s">
+      <c r="E35" s="10"/>
+    </row>
+    <row r="36" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E36" s="12"/>
-    </row>
-    <row r="37" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="48" t="s">
+      <c r="E36" s="10"/>
+    </row>
+    <row r="37" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="12"/>
-    </row>
-    <row r="38" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="48" t="s">
+      <c r="E37" s="10"/>
+    </row>
+    <row r="38" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="12"/>
-    </row>
-    <row r="39" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="48" t="s">
+      <c r="E38" s="10"/>
+    </row>
+    <row r="39" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E39" s="12"/>
-    </row>
-    <row r="40" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="48" t="s">
+      <c r="E39" s="10"/>
+    </row>
+    <row r="40" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E40" s="12"/>
-    </row>
-    <row r="41" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="48" t="s">
+      <c r="E40" s="10"/>
+    </row>
+    <row r="41" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="12"/>
-    </row>
-    <row r="42" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="48" t="s">
+      <c r="E41" s="10"/>
+    </row>
+    <row r="42" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="57" t="s">
+      <c r="C42" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E42" s="12"/>
-    </row>
-    <row r="43" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="48" t="s">
+      <c r="E42" s="10"/>
+    </row>
+    <row r="43" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="57" t="s">
+      <c r="B43" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="57" t="s">
+      <c r="C43" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="12"/>
-    </row>
-    <row r="44" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="48" t="s">
+      <c r="E43" s="10"/>
+    </row>
+    <row r="44" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C44" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="12"/>
-    </row>
-    <row r="45" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="48" t="s">
+      <c r="E44" s="10"/>
+    </row>
+    <row r="45" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E45" s="12"/>
-    </row>
-    <row r="46" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="48" t="s">
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="12"/>
-    </row>
-    <row r="47" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="48" t="s">
+      <c r="E46" s="10"/>
+    </row>
+    <row r="47" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B47" s="57" t="s">
+      <c r="B47" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="57" t="s">
+      <c r="C47" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E47" s="12"/>
-    </row>
-    <row r="48" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="48" t="s">
+      <c r="E47" s="10"/>
+    </row>
+    <row r="48" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B48" s="57" t="s">
+      <c r="B48" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="57" t="s">
+      <c r="C48" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E48" s="12"/>
-    </row>
-    <row r="49" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="48" t="s">
+      <c r="E48" s="10"/>
+    </row>
+    <row r="49" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="57" t="s">
+      <c r="B49" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E49" s="12"/>
-    </row>
-    <row r="50" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="48" t="s">
+      <c r="E49" s="10"/>
+    </row>
+    <row r="50" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="C50" s="57" t="s">
+      <c r="C50" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E50" s="12"/>
-    </row>
-    <row r="51" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="48" t="s">
+      <c r="E50" s="10"/>
+    </row>
+    <row r="51" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B51" s="57" t="s">
+      <c r="B51" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E51" s="12"/>
-    </row>
-    <row r="52" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="48" t="s">
+      <c r="E51" s="10"/>
+    </row>
+    <row r="52" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="57" t="s">
+      <c r="B52" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="57" t="s">
+      <c r="C52" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E52" s="12"/>
-    </row>
-    <row r="53" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="48" t="s">
+      <c r="E52" s="10"/>
+    </row>
+    <row r="53" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C53" s="57" t="s">
+      <c r="C53" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E53" s="12"/>
-    </row>
-    <row r="54" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="48" t="s">
+      <c r="E53" s="10"/>
+    </row>
+    <row r="54" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="57" t="s">
+      <c r="B54" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="55" t="s">
         <v>132</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E54" s="12"/>
-    </row>
-    <row r="55" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="48" t="s">
+      <c r="E54" s="10"/>
+    </row>
+    <row r="55" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E55" s="12"/>
-    </row>
-    <row r="56" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="48" t="s">
+      <c r="E55" s="10"/>
+    </row>
+    <row r="56" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="57" t="s">
+      <c r="B56" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="57" t="s">
+      <c r="C56" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E56" s="12"/>
-    </row>
-    <row r="57" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="48" t="s">
+      <c r="E56" s="10"/>
+    </row>
+    <row r="57" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C57" s="57" t="s">
+      <c r="C57" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E57" s="12"/>
-    </row>
-    <row r="58" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="48" t="s">
+      <c r="E57" s="10"/>
+    </row>
+    <row r="58" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B58" s="57" t="s">
+      <c r="B58" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E58" s="12"/>
-    </row>
-    <row r="59" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="48" t="s">
+      <c r="E58" s="10"/>
+    </row>
+    <row r="59" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B59" s="57" t="s">
+      <c r="B59" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C59" s="57" t="s">
+      <c r="C59" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E59" s="12"/>
-    </row>
-    <row r="60" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="48" t="s">
+      <c r="E59" s="10"/>
+    </row>
+    <row r="60" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B60" s="57" t="s">
+      <c r="B60" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C60" s="57" t="s">
+      <c r="C60" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E60" s="12"/>
-    </row>
-    <row r="61" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="48" t="s">
+      <c r="E60" s="10"/>
+    </row>
+    <row r="61" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="57" t="s">
+      <c r="B61" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="12"/>
-    </row>
-    <row r="62" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="48" t="s">
+      <c r="E61" s="10"/>
+    </row>
+    <row r="62" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B62" s="57" t="s">
+      <c r="B62" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="12"/>
-    </row>
-    <row r="63" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="48" t="s">
+      <c r="E62" s="10"/>
+    </row>
+    <row r="63" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B63" s="57" t="s">
+      <c r="B63" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E63" s="12"/>
-    </row>
-    <row r="64" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="48" t="s">
+      <c r="E63" s="10"/>
+    </row>
+    <row r="64" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C64" s="57" t="s">
+      <c r="C64" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E64" s="12"/>
-    </row>
-    <row r="65" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="48" t="s">
+      <c r="E64" s="10"/>
+    </row>
+    <row r="65" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B65" s="49" t="s">
+      <c r="B65" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E65" s="12"/>
-    </row>
-    <row r="66" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="48" t="s">
+      <c r="E65" s="10"/>
+    </row>
+    <row r="66" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B66" s="49" t="s">
+      <c r="B66" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E66" s="12"/>
-    </row>
-    <row r="67" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="48"/>
-      <c r="B67" s="57"/>
-      <c r="C67" s="57"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-    </row>
-    <row r="68" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="35" t="s">
+      <c r="E66" s="10"/>
+    </row>
+    <row r="67" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="46"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="55"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+    </row>
+    <row r="68" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-    </row>
-    <row r="69" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="50" t="s">
+      <c r="B68" s="34"/>
+      <c r="C68" s="34"/>
+      <c r="D68" s="34"/>
+      <c r="E68" s="34"/>
+    </row>
+    <row r="69" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B69" s="57" t="s">
+      <c r="B69" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="51" t="s">
+      <c r="C69" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E69" s="12"/>
-    </row>
-    <row r="70" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="50" t="s">
+      <c r="E69" s="10"/>
+    </row>
+    <row r="70" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="57" t="s">
+      <c r="B70" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="51" t="s">
+      <c r="C70" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="12"/>
-    </row>
-    <row r="71" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="50" t="s">
+      <c r="E70" s="10"/>
+    </row>
+    <row r="71" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B71" s="57" t="s">
+      <c r="B71" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E71" s="12"/>
-    </row>
-    <row r="72" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="50" t="s">
+      <c r="E71" s="10"/>
+    </row>
+    <row r="72" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="57" t="s">
+      <c r="B72" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E72" s="12"/>
-    </row>
-    <row r="73" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="50" t="s">
+      <c r="E72" s="10"/>
+    </row>
+    <row r="73" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="57" t="s">
+      <c r="B73" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E73" s="12"/>
-    </row>
-    <row r="74" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="50" t="s">
+      <c r="E73" s="10"/>
+    </row>
+    <row r="74" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B74" s="57" t="s">
+      <c r="B74" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E74" s="12"/>
-    </row>
-    <row r="75" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="50" t="s">
+      <c r="E74" s="10"/>
+    </row>
+    <row r="75" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B75" s="57" t="s">
+      <c r="B75" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E75" s="12"/>
-    </row>
-    <row r="76" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="50" t="s">
+      <c r="E75" s="10"/>
+    </row>
+    <row r="76" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="12"/>
-    </row>
-    <row r="77" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="50" t="s">
+      <c r="E76" s="10"/>
+    </row>
+    <row r="77" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="57" t="s">
+      <c r="B77" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E77" s="12"/>
-    </row>
-    <row r="78" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="50" t="s">
+      <c r="E77" s="10"/>
+    </row>
+    <row r="78" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B78" s="57" t="s">
+      <c r="B78" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E78" s="12"/>
-    </row>
-    <row r="79" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
+      <c r="E78" s="10"/>
+    </row>
+    <row r="79" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B79" s="49" t="s">
+      <c r="B79" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E79" s="12"/>
-    </row>
-    <row r="80" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="50" t="s">
+      <c r="E79" s="10"/>
+    </row>
+    <row r="80" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B80" s="49" t="s">
+      <c r="B80" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E80" s="12"/>
-    </row>
-    <row r="81" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="50" t="s">
+      <c r="E80" s="10"/>
+    </row>
+    <row r="81" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B81" s="49" t="s">
+      <c r="B81" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C81" s="51" t="s">
+      <c r="C81" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E81" s="12"/>
-    </row>
-    <row r="82" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="50" t="s">
+      <c r="E81" s="10"/>
+    </row>
+    <row r="82" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C82" s="51" t="s">
+      <c r="C82" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E82" s="12"/>
-    </row>
-    <row r="83" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="50" t="s">
+      <c r="E82" s="10"/>
+    </row>
+    <row r="83" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B83" s="49" t="s">
+      <c r="B83" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E83" s="12"/>
-    </row>
-    <row r="84" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="50" t="s">
+      <c r="E83" s="10"/>
+    </row>
+    <row r="84" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B84" s="49" t="s">
+      <c r="B84" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E84" s="12"/>
-    </row>
-    <row r="85" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="50" t="s">
+      <c r="E84" s="10"/>
+    </row>
+    <row r="85" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B85" s="49" t="s">
+      <c r="B85" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E85" s="12"/>
-    </row>
-    <row r="86" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="50" t="s">
+      <c r="E85" s="10"/>
+    </row>
+    <row r="86" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B86" s="49" t="s">
+      <c r="B86" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E86" s="12"/>
-    </row>
-    <row r="87" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="50" t="s">
+      <c r="E86" s="10"/>
+    </row>
+    <row r="87" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B87" s="49" t="s">
+      <c r="B87" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E87" s="12"/>
-    </row>
-    <row r="88" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="50" t="s">
+      <c r="E87" s="10"/>
+    </row>
+    <row r="88" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B88" s="49" t="s">
+      <c r="B88" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C88" s="51" t="s">
+      <c r="C88" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E88" s="12"/>
-    </row>
-    <row r="89" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="50" t="s">
+      <c r="E88" s="10"/>
+    </row>
+    <row r="89" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B89" s="55" t="s">
+      <c r="B89" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E89" s="12"/>
-    </row>
-    <row r="90" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="50" t="s">
+      <c r="E89" s="10"/>
+    </row>
+    <row r="90" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B90" s="55" t="s">
+      <c r="B90" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E90" s="12"/>
-    </row>
-    <row r="91" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="50" t="s">
+      <c r="E90" s="10"/>
+    </row>
+    <row r="91" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B91" s="49" t="s">
+      <c r="B91" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C91" s="57" t="s">
+      <c r="C91" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E91" s="12"/>
-    </row>
-    <row r="92" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="50" t="s">
+      <c r="E91" s="10"/>
+    </row>
+    <row r="92" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B92" s="49" t="s">
+      <c r="B92" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E92" s="12"/>
-    </row>
-    <row r="93" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="50" t="s">
+      <c r="E92" s="10"/>
+    </row>
+    <row r="93" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B93" s="49" t="s">
+      <c r="B93" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E93" s="12"/>
-    </row>
-    <row r="94" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="50" t="s">
+      <c r="E93" s="10"/>
+    </row>
+    <row r="94" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B94" s="49" t="s">
+      <c r="B94" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E94" s="12"/>
-    </row>
-    <row r="95" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="50" t="s">
+      <c r="E94" s="10"/>
+    </row>
+    <row r="95" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B95" s="49" t="s">
+      <c r="B95" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E95" s="12"/>
-    </row>
-    <row r="96" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="50" t="s">
+      <c r="E95" s="10"/>
+    </row>
+    <row r="96" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B96" s="49" t="s">
+      <c r="B96" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E96" s="12"/>
-    </row>
-    <row r="97" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="50" t="s">
+      <c r="E96" s="10"/>
+    </row>
+    <row r="97" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B97" s="49" t="s">
+      <c r="B97" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E97" s="12"/>
-    </row>
-    <row r="98" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="50" t="s">
+      <c r="E97" s="10"/>
+    </row>
+    <row r="98" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B98" s="49" t="s">
+      <c r="B98" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E98" s="12"/>
-    </row>
-    <row r="99" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="50" t="s">
+      <c r="E98" s="10"/>
+    </row>
+    <row r="99" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B99" s="49" t="s">
+      <c r="B99" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E99" s="12"/>
-    </row>
-    <row r="100" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="50" t="s">
+      <c r="E99" s="10"/>
+    </row>
+    <row r="100" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B100" s="49" t="s">
+      <c r="B100" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E100" s="12"/>
-    </row>
-    <row r="101" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="50" t="s">
+      <c r="E100" s="10"/>
+    </row>
+    <row r="101" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B101" s="49" t="s">
+      <c r="B101" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C101" s="57" t="s">
+      <c r="C101" s="55" t="s">
         <v>180</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E101" s="12"/>
-    </row>
-    <row r="102" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="50" t="s">
+      <c r="E101" s="10"/>
+    </row>
+    <row r="102" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B102" s="49" t="s">
+      <c r="B102" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E102" s="12"/>
-    </row>
-    <row r="103" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="50" t="s">
+      <c r="E102" s="10"/>
+    </row>
+    <row r="103" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B103" s="55" t="s">
+      <c r="B103" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C103" s="57" t="s">
+      <c r="C103" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E103" s="12"/>
-    </row>
-    <row r="104" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="50" t="s">
+      <c r="E103" s="10"/>
+    </row>
+    <row r="104" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B104" s="55" t="s">
+      <c r="B104" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C104" s="57" t="s">
+      <c r="C104" s="55" t="s">
         <v>184</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E104" s="12"/>
-    </row>
-    <row r="105" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="50" t="s">
+      <c r="E104" s="10"/>
+    </row>
+    <row r="105" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B105" s="49" t="s">
+      <c r="B105" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C105" s="57" t="s">
+      <c r="C105" s="55" t="s">
         <v>185</v>
       </c>
-      <c r="D105" s="12" t="s">
+      <c r="D105" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E105" s="12"/>
-    </row>
-    <row r="106" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="50" t="s">
+      <c r="E105" s="10"/>
+    </row>
+    <row r="106" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B106" s="49" t="s">
+      <c r="B106" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C106" s="57" t="s">
+      <c r="C106" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="D106" s="12" t="s">
+      <c r="D106" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E106" s="12"/>
-    </row>
-    <row r="107" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="50" t="s">
+      <c r="E106" s="10"/>
+    </row>
+    <row r="107" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B107" s="55" t="s">
+      <c r="B107" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C107" s="57" t="s">
+      <c r="C107" s="55" t="s">
         <v>187</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E107" s="12"/>
-    </row>
-    <row r="108" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="50" t="s">
+      <c r="E107" s="10"/>
+    </row>
+    <row r="108" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B108" s="55" t="s">
+      <c r="B108" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C108" s="57" t="s">
+      <c r="C108" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="D108" s="12" t="s">
+      <c r="D108" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E108" s="12"/>
-    </row>
-    <row r="109" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="50" t="s">
+      <c r="E108" s="10"/>
+    </row>
+    <row r="109" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B109" s="55" t="s">
+      <c r="B109" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C109" s="57" t="s">
+      <c r="C109" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="D109" s="12" t="s">
+      <c r="D109" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E109" s="12"/>
-    </row>
-    <row r="110" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="50" t="s">
+      <c r="E109" s="10"/>
+    </row>
+    <row r="110" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B110" s="49" t="s">
+      <c r="B110" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C110" s="57" t="s">
+      <c r="C110" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="D110" s="12" t="s">
+      <c r="D110" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E110" s="12"/>
-    </row>
-    <row r="111" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="50" t="s">
+      <c r="E110" s="10"/>
+    </row>
+    <row r="111" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B111" s="55" t="s">
+      <c r="B111" s="53" t="s">
         <v>182</v>
       </c>
-      <c r="C111" s="57" t="s">
+      <c r="C111" s="55" t="s">
         <v>192</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="D111" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E111" s="12"/>
-    </row>
-    <row r="112" spans="1:5" s="10" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="35" t="s">
+      <c r="E111" s="10"/>
+    </row>
+    <row r="112" spans="1:5" s="8" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="B112" s="36"/>
-      <c r="C112" s="36"/>
-      <c r="D112" s="36"/>
-      <c r="E112" s="36"/>
-    </row>
-    <row r="113" spans="1:5" s="9" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="55" t="s">
+      <c r="B112" s="34"/>
+      <c r="C112" s="34"/>
+      <c r="D112" s="34"/>
+      <c r="E112" s="34"/>
+    </row>
+    <row r="113" spans="1:5" s="7" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E113" s="12"/>
-    </row>
-    <row r="114" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="55" t="s">
+      <c r="E113" s="10"/>
+    </row>
+    <row r="114" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B114" s="55" t="s">
+      <c r="B114" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C114" s="51" t="s">
+      <c r="C114" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="D114" s="11" t="s">
+      <c r="D114" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E114" s="10" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="115" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="55" t="s">
+    <row r="115" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B115" s="55" t="s">
+      <c r="B115" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C115" s="51" t="s">
+      <c r="C115" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="10" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="116" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="55" t="s">
+    <row r="116" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B116" s="56" t="s">
+      <c r="B116" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C116" s="57" t="s">
+      <c r="C116" s="55" t="s">
         <v>201</v>
       </c>
-      <c r="D116" s="12" t="s">
+      <c r="D116" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E116" s="12"/>
-    </row>
-    <row r="117" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="55" t="s">
+      <c r="E116" s="10"/>
+    </row>
+    <row r="117" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B117" s="56" t="s">
+      <c r="B117" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="D117" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E117" s="12"/>
-    </row>
-    <row r="118" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="55" t="s">
+      <c r="E117" s="10"/>
+    </row>
+    <row r="118" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B118" s="56" t="s">
+      <c r="B118" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D118" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E118" s="12"/>
-    </row>
-    <row r="119" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="55" t="s">
+      <c r="E118" s="10"/>
+    </row>
+    <row r="119" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B119" s="56" t="s">
+      <c r="B119" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E119" s="12"/>
-    </row>
-    <row r="120" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="55" t="s">
+      <c r="E119" s="10"/>
+    </row>
+    <row r="120" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B120" s="56" t="s">
+      <c r="B120" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D120" s="12" t="s">
+      <c r="D120" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E120" s="12"/>
-    </row>
-    <row r="121" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="55" t="s">
+      <c r="E120" s="10"/>
+    </row>
+    <row r="121" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B121" s="56" t="s">
+      <c r="B121" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C121" s="57" t="s">
+      <c r="C121" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D121" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E121" s="12"/>
-    </row>
-    <row r="122" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="55" t="s">
+      <c r="E121" s="10"/>
+    </row>
+    <row r="122" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B122" s="56" t="s">
+      <c r="B122" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C122" s="57" t="s">
+      <c r="C122" s="55" t="s">
         <v>207</v>
       </c>
-      <c r="D122" s="12" t="s">
+      <c r="D122" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E122" s="12"/>
-    </row>
-    <row r="123" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="55" t="s">
+      <c r="E122" s="10"/>
+    </row>
+    <row r="123" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C123" s="57" t="s">
+      <c r="C123" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E123" s="12"/>
-    </row>
-    <row r="124" spans="1:5" s="9" customFormat="1" ht="45.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="55" t="s">
+      <c r="E123" s="10"/>
+    </row>
+    <row r="124" spans="1:5" s="7" customFormat="1" ht="45.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B124" s="49" t="s">
+      <c r="B124" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D124" s="12" t="s">
+      <c r="D124" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E124" s="12"/>
-    </row>
-    <row r="125" spans="1:5" s="9" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="55" t="s">
+      <c r="E124" s="10"/>
+    </row>
+    <row r="125" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B125" s="55" t="s">
+      <c r="B125" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C125" s="57" t="s">
+      <c r="C125" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E125" s="12"/>
-    </row>
-    <row r="126" spans="1:5" s="9" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="55" t="s">
+      <c r="E125" s="10"/>
+    </row>
+    <row r="126" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B126" s="55" t="s">
+      <c r="B126" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C126" s="57" t="s">
+      <c r="C126" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E126" s="12"/>
-    </row>
-    <row r="127" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="55" t="s">
+      <c r="E126" s="10"/>
+    </row>
+    <row r="127" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B127" s="55" t="s">
+      <c r="B127" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C127" s="52" t="s">
+      <c r="C127" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E127" s="12"/>
-    </row>
-    <row r="128" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="55" t="s">
+      <c r="E127" s="10"/>
+    </row>
+    <row r="128" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B128" s="55" t="s">
+      <c r="B128" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C128" s="51" t="s">
+      <c r="C128" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E128" s="12" t="s">
+      <c r="E128" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="129" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="55" t="s">
+    <row r="129" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B129" s="55" t="s">
+      <c r="B129" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C129" s="51" t="s">
+      <c r="C129" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D129" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E129" s="12" t="s">
+      <c r="E129" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="130" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="55" t="s">
+    <row r="130" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B130" s="49" t="s">
+      <c r="B130" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="D130" s="11" t="s">
+      <c r="D130" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E130" s="12"/>
-    </row>
-    <row r="131" spans="1:5" s="9" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="55" t="s">
+      <c r="E130" s="10"/>
+    </row>
+    <row r="131" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B131" s="55" t="s">
+      <c r="B131" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C131" s="57" t="s">
+      <c r="C131" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="D131" s="12" t="s">
+      <c r="D131" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E131" s="12"/>
-    </row>
-    <row r="132" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="55" t="s">
+      <c r="E131" s="10"/>
+    </row>
+    <row r="132" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B132" s="56" t="s">
+      <c r="B132" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C132" s="51" t="s">
+      <c r="C132" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="D132" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E132" s="12"/>
-    </row>
-    <row r="133" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="55" t="s">
+      <c r="E132" s="10"/>
+    </row>
+    <row r="133" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B133" s="55" t="s">
+      <c r="B133" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C133" s="51" t="s">
+      <c r="C133" s="49" t="s">
         <v>220</v>
       </c>
-      <c r="D133" s="11" t="s">
+      <c r="D133" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E133" s="12"/>
-    </row>
-    <row r="134" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="55" t="s">
+      <c r="E133" s="10"/>
+    </row>
+    <row r="134" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B134" s="55" t="s">
+      <c r="B134" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C134" s="51" t="s">
+      <c r="C134" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="D134" s="11" t="s">
+      <c r="D134" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E134" s="12"/>
-    </row>
-    <row r="135" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="55" t="s">
+      <c r="E134" s="10"/>
+    </row>
+    <row r="135" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B135" s="49" t="s">
+      <c r="B135" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="C135" s="51" t="s">
+      <c r="C135" s="49" t="s">
         <v>222</v>
       </c>
-      <c r="D135" s="11" t="s">
+      <c r="D135" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E135" s="12"/>
-    </row>
-    <row r="136" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="55" t="s">
+      <c r="E135" s="10"/>
+    </row>
+    <row r="136" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B136" s="55" t="s">
+      <c r="B136" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C136" s="51" t="s">
+      <c r="C136" s="49" t="s">
         <v>223</v>
       </c>
-      <c r="D136" s="11" t="s">
+      <c r="D136" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E136" s="12"/>
-    </row>
-    <row r="137" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="55" t="s">
+      <c r="E136" s="10"/>
+    </row>
+    <row r="137" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B137" s="55" t="s">
+      <c r="B137" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="C137" s="51" t="s">
+      <c r="C137" s="49" t="s">
         <v>224</v>
       </c>
-      <c r="D137" s="11" t="s">
+      <c r="D137" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E137" s="12"/>
-    </row>
-    <row r="138" spans="1:5" s="9" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="55" t="s">
+      <c r="E137" s="10"/>
+    </row>
+    <row r="138" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B138" s="55" t="s">
+      <c r="B138" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D138" s="11" t="s">
+      <c r="D138" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E138" s="12"/>
-    </row>
-    <row r="139" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="55" t="s">
+      <c r="E138" s="10"/>
+    </row>
+    <row r="139" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C139" s="57" t="s">
+      <c r="C139" s="55" t="s">
         <v>226</v>
       </c>
-      <c r="D139" s="12" t="s">
+      <c r="D139" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E139" s="12"/>
-    </row>
-    <row r="140" spans="1:5" s="9" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="55" t="s">
+      <c r="E139" s="10"/>
+    </row>
+    <row r="140" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C140" s="57" t="s">
+      <c r="C140" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="D140" s="12" t="s">
+      <c r="D140" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E140" s="12"/>
-    </row>
-    <row r="141" spans="1:5" s="9" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="55" t="s">
+      <c r="E140" s="10"/>
+    </row>
+    <row r="141" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B141" s="49" t="s">
+      <c r="B141" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="C141" s="12" t="s">
+      <c r="C141" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="D141" s="11" t="s">
+      <c r="D141" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E141" s="12"/>
+      <c r="E141" s="10"/>
     </row>
     <row r="142" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="55" t="s">
+      <c r="A142" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B142" s="49" t="s">
+      <c r="B142" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="C142" s="57" t="s">
+      <c r="C142" s="55" t="s">
         <v>229</v>
       </c>
-      <c r="D142" s="11" t="s">
+      <c r="D142" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E142" s="12"/>
+      <c r="E142" s="10"/>
     </row>
     <row r="143" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="55" t="s">
+      <c r="A143" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B143" s="49" t="s">
+      <c r="B143" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="C143" s="53" t="s">
+      <c r="C143" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="D143" s="11" t="s">
+      <c r="D143" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E143" s="58"/>
+      <c r="E143" s="56"/>
     </row>
     <row r="144" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="55" t="s">
+      <c r="A144" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B144" s="56" t="s">
+      <c r="B144" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C144" s="53" t="s">
+      <c r="C144" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="D144" s="11" t="s">
+      <c r="D144" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E144" s="58"/>
+      <c r="E144" s="56"/>
     </row>
     <row r="145" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="55" t="s">
+      <c r="A145" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="B145" s="56" t="s">
+      <c r="B145" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="C145" s="57" t="s">
+      <c r="C145" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E145" s="58"/>
+      <c r="E145" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10554,1082 +10618,1076 @@
   <dimension ref="A1:L136"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="72" customWidth="1"/>
-    <col min="2" max="5" width="20.6640625" style="72" customWidth="1"/>
-    <col min="6" max="8" width="10" style="72" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" style="72" customWidth="1"/>
-    <col min="10" max="254" width="10" style="72" customWidth="1"/>
-    <col min="255" max="259" width="15.44140625" style="72" customWidth="1"/>
-    <col min="260" max="264" width="10" style="72" customWidth="1"/>
-    <col min="265" max="265" width="13.33203125" style="72" customWidth="1"/>
-    <col min="266" max="510" width="10" style="72" customWidth="1"/>
-    <col min="511" max="515" width="15.44140625" style="72" customWidth="1"/>
-    <col min="516" max="520" width="10" style="72" customWidth="1"/>
-    <col min="521" max="521" width="13.33203125" style="72" customWidth="1"/>
-    <col min="522" max="766" width="10" style="72" customWidth="1"/>
-    <col min="767" max="771" width="15.44140625" style="72" customWidth="1"/>
-    <col min="772" max="776" width="10" style="72" customWidth="1"/>
-    <col min="777" max="777" width="13.33203125" style="72" customWidth="1"/>
-    <col min="778" max="1022" width="10" style="72" customWidth="1"/>
-    <col min="1023" max="1027" width="15.44140625" style="72" customWidth="1"/>
-    <col min="1028" max="1032" width="10" style="72" customWidth="1"/>
-    <col min="1033" max="1033" width="13.33203125" style="72" customWidth="1"/>
-    <col min="1034" max="1278" width="10" style="72" customWidth="1"/>
-    <col min="1279" max="1283" width="15.44140625" style="72" customWidth="1"/>
-    <col min="1284" max="1288" width="10" style="72" customWidth="1"/>
-    <col min="1289" max="1289" width="13.33203125" style="72" customWidth="1"/>
-    <col min="1290" max="1534" width="10" style="72" customWidth="1"/>
-    <col min="1535" max="1539" width="15.44140625" style="72" customWidth="1"/>
-    <col min="1540" max="1544" width="10" style="72" customWidth="1"/>
-    <col min="1545" max="1545" width="13.33203125" style="72" customWidth="1"/>
-    <col min="1546" max="1790" width="10" style="72" customWidth="1"/>
-    <col min="1791" max="1795" width="15.44140625" style="72" customWidth="1"/>
-    <col min="1796" max="1800" width="10" style="72" customWidth="1"/>
-    <col min="1801" max="1801" width="13.33203125" style="72" customWidth="1"/>
-    <col min="1802" max="2046" width="10" style="72" customWidth="1"/>
-    <col min="2047" max="2051" width="15.44140625" style="72" customWidth="1"/>
-    <col min="2052" max="2056" width="10" style="72" customWidth="1"/>
-    <col min="2057" max="2057" width="13.33203125" style="72" customWidth="1"/>
-    <col min="2058" max="2302" width="10" style="72" customWidth="1"/>
-    <col min="2303" max="2307" width="15.44140625" style="72" customWidth="1"/>
-    <col min="2308" max="2312" width="10" style="72" customWidth="1"/>
-    <col min="2313" max="2313" width="13.33203125" style="72" customWidth="1"/>
-    <col min="2314" max="2558" width="10" style="72" customWidth="1"/>
-    <col min="2559" max="2563" width="15.44140625" style="72" customWidth="1"/>
-    <col min="2564" max="2568" width="10" style="72" customWidth="1"/>
-    <col min="2569" max="2569" width="13.33203125" style="72" customWidth="1"/>
-    <col min="2570" max="2814" width="10" style="72" customWidth="1"/>
-    <col min="2815" max="2819" width="15.44140625" style="72" customWidth="1"/>
-    <col min="2820" max="2824" width="10" style="72" customWidth="1"/>
-    <col min="2825" max="2825" width="13.33203125" style="72" customWidth="1"/>
-    <col min="2826" max="3070" width="10" style="72" customWidth="1"/>
-    <col min="3071" max="3075" width="15.44140625" style="72" customWidth="1"/>
-    <col min="3076" max="3080" width="10" style="72" customWidth="1"/>
-    <col min="3081" max="3081" width="13.33203125" style="72" customWidth="1"/>
-    <col min="3082" max="3326" width="10" style="72" customWidth="1"/>
-    <col min="3327" max="3331" width="15.44140625" style="72" customWidth="1"/>
-    <col min="3332" max="3336" width="10" style="72" customWidth="1"/>
-    <col min="3337" max="3337" width="13.33203125" style="72" customWidth="1"/>
-    <col min="3338" max="3582" width="10" style="72" customWidth="1"/>
-    <col min="3583" max="3587" width="15.44140625" style="72" customWidth="1"/>
-    <col min="3588" max="3592" width="10" style="72" customWidth="1"/>
-    <col min="3593" max="3593" width="13.33203125" style="72" customWidth="1"/>
-    <col min="3594" max="3838" width="10" style="72" customWidth="1"/>
-    <col min="3839" max="3843" width="15.44140625" style="72" customWidth="1"/>
-    <col min="3844" max="3848" width="10" style="72" customWidth="1"/>
-    <col min="3849" max="3849" width="13.33203125" style="72" customWidth="1"/>
-    <col min="3850" max="4094" width="10" style="72" customWidth="1"/>
-    <col min="4095" max="4099" width="15.44140625" style="72" customWidth="1"/>
-    <col min="4100" max="4104" width="10" style="72" customWidth="1"/>
-    <col min="4105" max="4105" width="13.33203125" style="72" customWidth="1"/>
-    <col min="4106" max="4350" width="10" style="72" customWidth="1"/>
-    <col min="4351" max="4355" width="15.44140625" style="72" customWidth="1"/>
-    <col min="4356" max="4360" width="10" style="72" customWidth="1"/>
-    <col min="4361" max="4361" width="13.33203125" style="72" customWidth="1"/>
-    <col min="4362" max="4606" width="10" style="72" customWidth="1"/>
-    <col min="4607" max="4611" width="15.44140625" style="72" customWidth="1"/>
-    <col min="4612" max="4616" width="10" style="72" customWidth="1"/>
-    <col min="4617" max="4617" width="13.33203125" style="72" customWidth="1"/>
-    <col min="4618" max="4862" width="10" style="72" customWidth="1"/>
-    <col min="4863" max="4867" width="15.44140625" style="72" customWidth="1"/>
-    <col min="4868" max="4872" width="10" style="72" customWidth="1"/>
-    <col min="4873" max="4873" width="13.33203125" style="72" customWidth="1"/>
-    <col min="4874" max="5118" width="10" style="72" customWidth="1"/>
-    <col min="5119" max="5123" width="15.44140625" style="72" customWidth="1"/>
-    <col min="5124" max="5128" width="10" style="72" customWidth="1"/>
-    <col min="5129" max="5129" width="13.33203125" style="72" customWidth="1"/>
-    <col min="5130" max="5374" width="10" style="72" customWidth="1"/>
-    <col min="5375" max="5379" width="15.44140625" style="72" customWidth="1"/>
-    <col min="5380" max="5384" width="10" style="72" customWidth="1"/>
-    <col min="5385" max="5385" width="13.33203125" style="72" customWidth="1"/>
-    <col min="5386" max="5630" width="10" style="72" customWidth="1"/>
-    <col min="5631" max="5635" width="15.44140625" style="72" customWidth="1"/>
-    <col min="5636" max="5640" width="10" style="72" customWidth="1"/>
-    <col min="5641" max="5641" width="13.33203125" style="72" customWidth="1"/>
-    <col min="5642" max="5886" width="10" style="72" customWidth="1"/>
-    <col min="5887" max="5891" width="15.44140625" style="72" customWidth="1"/>
-    <col min="5892" max="5896" width="10" style="72" customWidth="1"/>
-    <col min="5897" max="5897" width="13.33203125" style="72" customWidth="1"/>
-    <col min="5898" max="6142" width="10" style="72" customWidth="1"/>
-    <col min="6143" max="6147" width="15.44140625" style="72" customWidth="1"/>
-    <col min="6148" max="6152" width="10" style="72" customWidth="1"/>
-    <col min="6153" max="6153" width="13.33203125" style="72" customWidth="1"/>
-    <col min="6154" max="6398" width="10" style="72" customWidth="1"/>
-    <col min="6399" max="6403" width="15.44140625" style="72" customWidth="1"/>
-    <col min="6404" max="6408" width="10" style="72" customWidth="1"/>
-    <col min="6409" max="6409" width="13.33203125" style="72" customWidth="1"/>
-    <col min="6410" max="6654" width="10" style="72" customWidth="1"/>
-    <col min="6655" max="6659" width="15.44140625" style="72" customWidth="1"/>
-    <col min="6660" max="6664" width="10" style="72" customWidth="1"/>
-    <col min="6665" max="6665" width="13.33203125" style="72" customWidth="1"/>
-    <col min="6666" max="6910" width="10" style="72" customWidth="1"/>
-    <col min="6911" max="6915" width="15.44140625" style="72" customWidth="1"/>
-    <col min="6916" max="6920" width="10" style="72" customWidth="1"/>
-    <col min="6921" max="6921" width="13.33203125" style="72" customWidth="1"/>
-    <col min="6922" max="7166" width="10" style="72" customWidth="1"/>
-    <col min="7167" max="7171" width="15.44140625" style="72" customWidth="1"/>
-    <col min="7172" max="7176" width="10" style="72" customWidth="1"/>
-    <col min="7177" max="7177" width="13.33203125" style="72" customWidth="1"/>
-    <col min="7178" max="7422" width="10" style="72" customWidth="1"/>
-    <col min="7423" max="7427" width="15.44140625" style="72" customWidth="1"/>
-    <col min="7428" max="7432" width="10" style="72" customWidth="1"/>
-    <col min="7433" max="7433" width="13.33203125" style="72" customWidth="1"/>
-    <col min="7434" max="7678" width="10" style="72" customWidth="1"/>
-    <col min="7679" max="7683" width="15.44140625" style="72" customWidth="1"/>
-    <col min="7684" max="7688" width="10" style="72" customWidth="1"/>
-    <col min="7689" max="7689" width="13.33203125" style="72" customWidth="1"/>
-    <col min="7690" max="7934" width="10" style="72" customWidth="1"/>
-    <col min="7935" max="7939" width="15.44140625" style="72" customWidth="1"/>
-    <col min="7940" max="7944" width="10" style="72" customWidth="1"/>
-    <col min="7945" max="7945" width="13.33203125" style="72" customWidth="1"/>
-    <col min="7946" max="8190" width="10" style="72" customWidth="1"/>
-    <col min="8191" max="8195" width="15.44140625" style="72" customWidth="1"/>
-    <col min="8196" max="8200" width="10" style="72" customWidth="1"/>
-    <col min="8201" max="8201" width="13.33203125" style="72" customWidth="1"/>
-    <col min="8202" max="8446" width="10" style="72" customWidth="1"/>
-    <col min="8447" max="8451" width="15.44140625" style="72" customWidth="1"/>
-    <col min="8452" max="8456" width="10" style="72" customWidth="1"/>
-    <col min="8457" max="8457" width="13.33203125" style="72" customWidth="1"/>
-    <col min="8458" max="8702" width="10" style="72" customWidth="1"/>
-    <col min="8703" max="8707" width="15.44140625" style="72" customWidth="1"/>
-    <col min="8708" max="8712" width="10" style="72" customWidth="1"/>
-    <col min="8713" max="8713" width="13.33203125" style="72" customWidth="1"/>
-    <col min="8714" max="8958" width="10" style="72" customWidth="1"/>
-    <col min="8959" max="8963" width="15.44140625" style="72" customWidth="1"/>
-    <col min="8964" max="8968" width="10" style="72" customWidth="1"/>
-    <col min="8969" max="8969" width="13.33203125" style="72" customWidth="1"/>
-    <col min="8970" max="9214" width="10" style="72" customWidth="1"/>
-    <col min="9215" max="9219" width="15.44140625" style="72" customWidth="1"/>
-    <col min="9220" max="9224" width="10" style="72" customWidth="1"/>
-    <col min="9225" max="9225" width="13.33203125" style="72" customWidth="1"/>
-    <col min="9226" max="9470" width="10" style="72" customWidth="1"/>
-    <col min="9471" max="9475" width="15.44140625" style="72" customWidth="1"/>
-    <col min="9476" max="9480" width="10" style="72" customWidth="1"/>
-    <col min="9481" max="9481" width="13.33203125" style="72" customWidth="1"/>
-    <col min="9482" max="9726" width="10" style="72" customWidth="1"/>
-    <col min="9727" max="9731" width="15.44140625" style="72" customWidth="1"/>
-    <col min="9732" max="9736" width="10" style="72" customWidth="1"/>
-    <col min="9737" max="9737" width="13.33203125" style="72" customWidth="1"/>
-    <col min="9738" max="9982" width="10" style="72" customWidth="1"/>
-    <col min="9983" max="9987" width="15.44140625" style="72" customWidth="1"/>
-    <col min="9988" max="9992" width="10" style="72" customWidth="1"/>
-    <col min="9993" max="9993" width="13.33203125" style="72" customWidth="1"/>
-    <col min="9994" max="10238" width="10" style="72" customWidth="1"/>
-    <col min="10239" max="10243" width="15.44140625" style="72" customWidth="1"/>
-    <col min="10244" max="10248" width="10" style="72" customWidth="1"/>
-    <col min="10249" max="10249" width="13.33203125" style="72" customWidth="1"/>
-    <col min="10250" max="10494" width="10" style="72" customWidth="1"/>
-    <col min="10495" max="10499" width="15.44140625" style="72" customWidth="1"/>
-    <col min="10500" max="10504" width="10" style="72" customWidth="1"/>
-    <col min="10505" max="10505" width="13.33203125" style="72" customWidth="1"/>
-    <col min="10506" max="10750" width="10" style="72" customWidth="1"/>
-    <col min="10751" max="10755" width="15.44140625" style="72" customWidth="1"/>
-    <col min="10756" max="10760" width="10" style="72" customWidth="1"/>
-    <col min="10761" max="10761" width="13.33203125" style="72" customWidth="1"/>
-    <col min="10762" max="11006" width="10" style="72" customWidth="1"/>
-    <col min="11007" max="11011" width="15.44140625" style="72" customWidth="1"/>
-    <col min="11012" max="11016" width="10" style="72" customWidth="1"/>
-    <col min="11017" max="11017" width="13.33203125" style="72" customWidth="1"/>
-    <col min="11018" max="11262" width="10" style="72" customWidth="1"/>
-    <col min="11263" max="11267" width="15.44140625" style="72" customWidth="1"/>
-    <col min="11268" max="11272" width="10" style="72" customWidth="1"/>
-    <col min="11273" max="11273" width="13.33203125" style="72" customWidth="1"/>
-    <col min="11274" max="11518" width="10" style="72" customWidth="1"/>
-    <col min="11519" max="11523" width="15.44140625" style="72" customWidth="1"/>
-    <col min="11524" max="11528" width="10" style="72" customWidth="1"/>
-    <col min="11529" max="11529" width="13.33203125" style="72" customWidth="1"/>
-    <col min="11530" max="11774" width="10" style="72" customWidth="1"/>
-    <col min="11775" max="11779" width="15.44140625" style="72" customWidth="1"/>
-    <col min="11780" max="11784" width="10" style="72" customWidth="1"/>
-    <col min="11785" max="11785" width="13.33203125" style="72" customWidth="1"/>
-    <col min="11786" max="12030" width="10" style="72" customWidth="1"/>
-    <col min="12031" max="12035" width="15.44140625" style="72" customWidth="1"/>
-    <col min="12036" max="12040" width="10" style="72" customWidth="1"/>
-    <col min="12041" max="12041" width="13.33203125" style="72" customWidth="1"/>
-    <col min="12042" max="12286" width="10" style="72" customWidth="1"/>
-    <col min="12287" max="12291" width="15.44140625" style="72" customWidth="1"/>
-    <col min="12292" max="12296" width="10" style="72" customWidth="1"/>
-    <col min="12297" max="12297" width="13.33203125" style="72" customWidth="1"/>
-    <col min="12298" max="12542" width="10" style="72" customWidth="1"/>
-    <col min="12543" max="12547" width="15.44140625" style="72" customWidth="1"/>
-    <col min="12548" max="12552" width="10" style="72" customWidth="1"/>
-    <col min="12553" max="12553" width="13.33203125" style="72" customWidth="1"/>
-    <col min="12554" max="12798" width="10" style="72" customWidth="1"/>
-    <col min="12799" max="12803" width="15.44140625" style="72" customWidth="1"/>
-    <col min="12804" max="12808" width="10" style="72" customWidth="1"/>
-    <col min="12809" max="12809" width="13.33203125" style="72" customWidth="1"/>
-    <col min="12810" max="13054" width="10" style="72" customWidth="1"/>
-    <col min="13055" max="13059" width="15.44140625" style="72" customWidth="1"/>
-    <col min="13060" max="13064" width="10" style="72" customWidth="1"/>
-    <col min="13065" max="13065" width="13.33203125" style="72" customWidth="1"/>
-    <col min="13066" max="13310" width="10" style="72" customWidth="1"/>
-    <col min="13311" max="13315" width="15.44140625" style="72" customWidth="1"/>
-    <col min="13316" max="13320" width="10" style="72" customWidth="1"/>
-    <col min="13321" max="13321" width="13.33203125" style="72" customWidth="1"/>
-    <col min="13322" max="13566" width="10" style="72" customWidth="1"/>
-    <col min="13567" max="13571" width="15.44140625" style="72" customWidth="1"/>
-    <col min="13572" max="13576" width="10" style="72" customWidth="1"/>
-    <col min="13577" max="13577" width="13.33203125" style="72" customWidth="1"/>
-    <col min="13578" max="13822" width="10" style="72" customWidth="1"/>
-    <col min="13823" max="13827" width="15.44140625" style="72" customWidth="1"/>
-    <col min="13828" max="13832" width="10" style="72" customWidth="1"/>
-    <col min="13833" max="13833" width="13.33203125" style="72" customWidth="1"/>
-    <col min="13834" max="14078" width="10" style="72" customWidth="1"/>
-    <col min="14079" max="14083" width="15.44140625" style="72" customWidth="1"/>
-    <col min="14084" max="14088" width="10" style="72" customWidth="1"/>
-    <col min="14089" max="14089" width="13.33203125" style="72" customWidth="1"/>
-    <col min="14090" max="14334" width="10" style="72" customWidth="1"/>
-    <col min="14335" max="14339" width="15.44140625" style="72" customWidth="1"/>
-    <col min="14340" max="14344" width="10" style="72" customWidth="1"/>
-    <col min="14345" max="14345" width="13.33203125" style="72" customWidth="1"/>
-    <col min="14346" max="14590" width="10" style="72" customWidth="1"/>
-    <col min="14591" max="14595" width="15.44140625" style="72" customWidth="1"/>
-    <col min="14596" max="14600" width="10" style="72" customWidth="1"/>
-    <col min="14601" max="14601" width="13.33203125" style="72" customWidth="1"/>
-    <col min="14602" max="14846" width="10" style="72" customWidth="1"/>
-    <col min="14847" max="14851" width="15.44140625" style="72" customWidth="1"/>
-    <col min="14852" max="14856" width="10" style="72" customWidth="1"/>
-    <col min="14857" max="14857" width="13.33203125" style="72" customWidth="1"/>
-    <col min="14858" max="15102" width="10" style="72" customWidth="1"/>
-    <col min="15103" max="15107" width="15.44140625" style="72" customWidth="1"/>
-    <col min="15108" max="15112" width="10" style="72" customWidth="1"/>
-    <col min="15113" max="15113" width="13.33203125" style="72" customWidth="1"/>
-    <col min="15114" max="15358" width="10" style="72" customWidth="1"/>
-    <col min="15359" max="15363" width="15.44140625" style="72" customWidth="1"/>
-    <col min="15364" max="15368" width="10" style="72" customWidth="1"/>
-    <col min="15369" max="15369" width="13.33203125" style="72" customWidth="1"/>
-    <col min="15370" max="15614" width="10" style="72" customWidth="1"/>
-    <col min="15615" max="15619" width="15.44140625" style="72" customWidth="1"/>
-    <col min="15620" max="15624" width="10" style="72" customWidth="1"/>
-    <col min="15625" max="15625" width="13.33203125" style="72" customWidth="1"/>
-    <col min="15626" max="15870" width="10" style="72" customWidth="1"/>
-    <col min="15871" max="15875" width="15.44140625" style="72" customWidth="1"/>
-    <col min="15876" max="15880" width="10" style="72" customWidth="1"/>
-    <col min="15881" max="15881" width="13.33203125" style="72" customWidth="1"/>
-    <col min="15882" max="16126" width="10" style="72" customWidth="1"/>
-    <col min="16127" max="16131" width="15.44140625" style="72" customWidth="1"/>
-    <col min="16132" max="16136" width="10" style="72" customWidth="1"/>
-    <col min="16137" max="16137" width="13.33203125" style="72" customWidth="1"/>
-    <col min="16138" max="16384" width="10" style="72" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="70" customWidth="1"/>
+    <col min="2" max="5" width="20.6640625" style="70" customWidth="1"/>
+    <col min="6" max="8" width="10" style="70" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" style="70" customWidth="1"/>
+    <col min="10" max="254" width="10" style="70" customWidth="1"/>
+    <col min="255" max="259" width="15.44140625" style="70" customWidth="1"/>
+    <col min="260" max="264" width="10" style="70" customWidth="1"/>
+    <col min="265" max="265" width="13.33203125" style="70" customWidth="1"/>
+    <col min="266" max="510" width="10" style="70" customWidth="1"/>
+    <col min="511" max="515" width="15.44140625" style="70" customWidth="1"/>
+    <col min="516" max="520" width="10" style="70" customWidth="1"/>
+    <col min="521" max="521" width="13.33203125" style="70" customWidth="1"/>
+    <col min="522" max="766" width="10" style="70" customWidth="1"/>
+    <col min="767" max="771" width="15.44140625" style="70" customWidth="1"/>
+    <col min="772" max="776" width="10" style="70" customWidth="1"/>
+    <col min="777" max="777" width="13.33203125" style="70" customWidth="1"/>
+    <col min="778" max="1022" width="10" style="70" customWidth="1"/>
+    <col min="1023" max="1027" width="15.44140625" style="70" customWidth="1"/>
+    <col min="1028" max="1032" width="10" style="70" customWidth="1"/>
+    <col min="1033" max="1033" width="13.33203125" style="70" customWidth="1"/>
+    <col min="1034" max="1278" width="10" style="70" customWidth="1"/>
+    <col min="1279" max="1283" width="15.44140625" style="70" customWidth="1"/>
+    <col min="1284" max="1288" width="10" style="70" customWidth="1"/>
+    <col min="1289" max="1289" width="13.33203125" style="70" customWidth="1"/>
+    <col min="1290" max="1534" width="10" style="70" customWidth="1"/>
+    <col min="1535" max="1539" width="15.44140625" style="70" customWidth="1"/>
+    <col min="1540" max="1544" width="10" style="70" customWidth="1"/>
+    <col min="1545" max="1545" width="13.33203125" style="70" customWidth="1"/>
+    <col min="1546" max="1790" width="10" style="70" customWidth="1"/>
+    <col min="1791" max="1795" width="15.44140625" style="70" customWidth="1"/>
+    <col min="1796" max="1800" width="10" style="70" customWidth="1"/>
+    <col min="1801" max="1801" width="13.33203125" style="70" customWidth="1"/>
+    <col min="1802" max="2046" width="10" style="70" customWidth="1"/>
+    <col min="2047" max="2051" width="15.44140625" style="70" customWidth="1"/>
+    <col min="2052" max="2056" width="10" style="70" customWidth="1"/>
+    <col min="2057" max="2057" width="13.33203125" style="70" customWidth="1"/>
+    <col min="2058" max="2302" width="10" style="70" customWidth="1"/>
+    <col min="2303" max="2307" width="15.44140625" style="70" customWidth="1"/>
+    <col min="2308" max="2312" width="10" style="70" customWidth="1"/>
+    <col min="2313" max="2313" width="13.33203125" style="70" customWidth="1"/>
+    <col min="2314" max="2558" width="10" style="70" customWidth="1"/>
+    <col min="2559" max="2563" width="15.44140625" style="70" customWidth="1"/>
+    <col min="2564" max="2568" width="10" style="70" customWidth="1"/>
+    <col min="2569" max="2569" width="13.33203125" style="70" customWidth="1"/>
+    <col min="2570" max="2814" width="10" style="70" customWidth="1"/>
+    <col min="2815" max="2819" width="15.44140625" style="70" customWidth="1"/>
+    <col min="2820" max="2824" width="10" style="70" customWidth="1"/>
+    <col min="2825" max="2825" width="13.33203125" style="70" customWidth="1"/>
+    <col min="2826" max="3070" width="10" style="70" customWidth="1"/>
+    <col min="3071" max="3075" width="15.44140625" style="70" customWidth="1"/>
+    <col min="3076" max="3080" width="10" style="70" customWidth="1"/>
+    <col min="3081" max="3081" width="13.33203125" style="70" customWidth="1"/>
+    <col min="3082" max="3326" width="10" style="70" customWidth="1"/>
+    <col min="3327" max="3331" width="15.44140625" style="70" customWidth="1"/>
+    <col min="3332" max="3336" width="10" style="70" customWidth="1"/>
+    <col min="3337" max="3337" width="13.33203125" style="70" customWidth="1"/>
+    <col min="3338" max="3582" width="10" style="70" customWidth="1"/>
+    <col min="3583" max="3587" width="15.44140625" style="70" customWidth="1"/>
+    <col min="3588" max="3592" width="10" style="70" customWidth="1"/>
+    <col min="3593" max="3593" width="13.33203125" style="70" customWidth="1"/>
+    <col min="3594" max="3838" width="10" style="70" customWidth="1"/>
+    <col min="3839" max="3843" width="15.44140625" style="70" customWidth="1"/>
+    <col min="3844" max="3848" width="10" style="70" customWidth="1"/>
+    <col min="3849" max="3849" width="13.33203125" style="70" customWidth="1"/>
+    <col min="3850" max="4094" width="10" style="70" customWidth="1"/>
+    <col min="4095" max="4099" width="15.44140625" style="70" customWidth="1"/>
+    <col min="4100" max="4104" width="10" style="70" customWidth="1"/>
+    <col min="4105" max="4105" width="13.33203125" style="70" customWidth="1"/>
+    <col min="4106" max="4350" width="10" style="70" customWidth="1"/>
+    <col min="4351" max="4355" width="15.44140625" style="70" customWidth="1"/>
+    <col min="4356" max="4360" width="10" style="70" customWidth="1"/>
+    <col min="4361" max="4361" width="13.33203125" style="70" customWidth="1"/>
+    <col min="4362" max="4606" width="10" style="70" customWidth="1"/>
+    <col min="4607" max="4611" width="15.44140625" style="70" customWidth="1"/>
+    <col min="4612" max="4616" width="10" style="70" customWidth="1"/>
+    <col min="4617" max="4617" width="13.33203125" style="70" customWidth="1"/>
+    <col min="4618" max="4862" width="10" style="70" customWidth="1"/>
+    <col min="4863" max="4867" width="15.44140625" style="70" customWidth="1"/>
+    <col min="4868" max="4872" width="10" style="70" customWidth="1"/>
+    <col min="4873" max="4873" width="13.33203125" style="70" customWidth="1"/>
+    <col min="4874" max="5118" width="10" style="70" customWidth="1"/>
+    <col min="5119" max="5123" width="15.44140625" style="70" customWidth="1"/>
+    <col min="5124" max="5128" width="10" style="70" customWidth="1"/>
+    <col min="5129" max="5129" width="13.33203125" style="70" customWidth="1"/>
+    <col min="5130" max="5374" width="10" style="70" customWidth="1"/>
+    <col min="5375" max="5379" width="15.44140625" style="70" customWidth="1"/>
+    <col min="5380" max="5384" width="10" style="70" customWidth="1"/>
+    <col min="5385" max="5385" width="13.33203125" style="70" customWidth="1"/>
+    <col min="5386" max="5630" width="10" style="70" customWidth="1"/>
+    <col min="5631" max="5635" width="15.44140625" style="70" customWidth="1"/>
+    <col min="5636" max="5640" width="10" style="70" customWidth="1"/>
+    <col min="5641" max="5641" width="13.33203125" style="70" customWidth="1"/>
+    <col min="5642" max="5886" width="10" style="70" customWidth="1"/>
+    <col min="5887" max="5891" width="15.44140625" style="70" customWidth="1"/>
+    <col min="5892" max="5896" width="10" style="70" customWidth="1"/>
+    <col min="5897" max="5897" width="13.33203125" style="70" customWidth="1"/>
+    <col min="5898" max="6142" width="10" style="70" customWidth="1"/>
+    <col min="6143" max="6147" width="15.44140625" style="70" customWidth="1"/>
+    <col min="6148" max="6152" width="10" style="70" customWidth="1"/>
+    <col min="6153" max="6153" width="13.33203125" style="70" customWidth="1"/>
+    <col min="6154" max="6398" width="10" style="70" customWidth="1"/>
+    <col min="6399" max="6403" width="15.44140625" style="70" customWidth="1"/>
+    <col min="6404" max="6408" width="10" style="70" customWidth="1"/>
+    <col min="6409" max="6409" width="13.33203125" style="70" customWidth="1"/>
+    <col min="6410" max="6654" width="10" style="70" customWidth="1"/>
+    <col min="6655" max="6659" width="15.44140625" style="70" customWidth="1"/>
+    <col min="6660" max="6664" width="10" style="70" customWidth="1"/>
+    <col min="6665" max="6665" width="13.33203125" style="70" customWidth="1"/>
+    <col min="6666" max="6910" width="10" style="70" customWidth="1"/>
+    <col min="6911" max="6915" width="15.44140625" style="70" customWidth="1"/>
+    <col min="6916" max="6920" width="10" style="70" customWidth="1"/>
+    <col min="6921" max="6921" width="13.33203125" style="70" customWidth="1"/>
+    <col min="6922" max="7166" width="10" style="70" customWidth="1"/>
+    <col min="7167" max="7171" width="15.44140625" style="70" customWidth="1"/>
+    <col min="7172" max="7176" width="10" style="70" customWidth="1"/>
+    <col min="7177" max="7177" width="13.33203125" style="70" customWidth="1"/>
+    <col min="7178" max="7422" width="10" style="70" customWidth="1"/>
+    <col min="7423" max="7427" width="15.44140625" style="70" customWidth="1"/>
+    <col min="7428" max="7432" width="10" style="70" customWidth="1"/>
+    <col min="7433" max="7433" width="13.33203125" style="70" customWidth="1"/>
+    <col min="7434" max="7678" width="10" style="70" customWidth="1"/>
+    <col min="7679" max="7683" width="15.44140625" style="70" customWidth="1"/>
+    <col min="7684" max="7688" width="10" style="70" customWidth="1"/>
+    <col min="7689" max="7689" width="13.33203125" style="70" customWidth="1"/>
+    <col min="7690" max="7934" width="10" style="70" customWidth="1"/>
+    <col min="7935" max="7939" width="15.44140625" style="70" customWidth="1"/>
+    <col min="7940" max="7944" width="10" style="70" customWidth="1"/>
+    <col min="7945" max="7945" width="13.33203125" style="70" customWidth="1"/>
+    <col min="7946" max="8190" width="10" style="70" customWidth="1"/>
+    <col min="8191" max="8195" width="15.44140625" style="70" customWidth="1"/>
+    <col min="8196" max="8200" width="10" style="70" customWidth="1"/>
+    <col min="8201" max="8201" width="13.33203125" style="70" customWidth="1"/>
+    <col min="8202" max="8446" width="10" style="70" customWidth="1"/>
+    <col min="8447" max="8451" width="15.44140625" style="70" customWidth="1"/>
+    <col min="8452" max="8456" width="10" style="70" customWidth="1"/>
+    <col min="8457" max="8457" width="13.33203125" style="70" customWidth="1"/>
+    <col min="8458" max="8702" width="10" style="70" customWidth="1"/>
+    <col min="8703" max="8707" width="15.44140625" style="70" customWidth="1"/>
+    <col min="8708" max="8712" width="10" style="70" customWidth="1"/>
+    <col min="8713" max="8713" width="13.33203125" style="70" customWidth="1"/>
+    <col min="8714" max="8958" width="10" style="70" customWidth="1"/>
+    <col min="8959" max="8963" width="15.44140625" style="70" customWidth="1"/>
+    <col min="8964" max="8968" width="10" style="70" customWidth="1"/>
+    <col min="8969" max="8969" width="13.33203125" style="70" customWidth="1"/>
+    <col min="8970" max="9214" width="10" style="70" customWidth="1"/>
+    <col min="9215" max="9219" width="15.44140625" style="70" customWidth="1"/>
+    <col min="9220" max="9224" width="10" style="70" customWidth="1"/>
+    <col min="9225" max="9225" width="13.33203125" style="70" customWidth="1"/>
+    <col min="9226" max="9470" width="10" style="70" customWidth="1"/>
+    <col min="9471" max="9475" width="15.44140625" style="70" customWidth="1"/>
+    <col min="9476" max="9480" width="10" style="70" customWidth="1"/>
+    <col min="9481" max="9481" width="13.33203125" style="70" customWidth="1"/>
+    <col min="9482" max="9726" width="10" style="70" customWidth="1"/>
+    <col min="9727" max="9731" width="15.44140625" style="70" customWidth="1"/>
+    <col min="9732" max="9736" width="10" style="70" customWidth="1"/>
+    <col min="9737" max="9737" width="13.33203125" style="70" customWidth="1"/>
+    <col min="9738" max="9982" width="10" style="70" customWidth="1"/>
+    <col min="9983" max="9987" width="15.44140625" style="70" customWidth="1"/>
+    <col min="9988" max="9992" width="10" style="70" customWidth="1"/>
+    <col min="9993" max="9993" width="13.33203125" style="70" customWidth="1"/>
+    <col min="9994" max="10238" width="10" style="70" customWidth="1"/>
+    <col min="10239" max="10243" width="15.44140625" style="70" customWidth="1"/>
+    <col min="10244" max="10248" width="10" style="70" customWidth="1"/>
+    <col min="10249" max="10249" width="13.33203125" style="70" customWidth="1"/>
+    <col min="10250" max="10494" width="10" style="70" customWidth="1"/>
+    <col min="10495" max="10499" width="15.44140625" style="70" customWidth="1"/>
+    <col min="10500" max="10504" width="10" style="70" customWidth="1"/>
+    <col min="10505" max="10505" width="13.33203125" style="70" customWidth="1"/>
+    <col min="10506" max="10750" width="10" style="70" customWidth="1"/>
+    <col min="10751" max="10755" width="15.44140625" style="70" customWidth="1"/>
+    <col min="10756" max="10760" width="10" style="70" customWidth="1"/>
+    <col min="10761" max="10761" width="13.33203125" style="70" customWidth="1"/>
+    <col min="10762" max="11006" width="10" style="70" customWidth="1"/>
+    <col min="11007" max="11011" width="15.44140625" style="70" customWidth="1"/>
+    <col min="11012" max="11016" width="10" style="70" customWidth="1"/>
+    <col min="11017" max="11017" width="13.33203125" style="70" customWidth="1"/>
+    <col min="11018" max="11262" width="10" style="70" customWidth="1"/>
+    <col min="11263" max="11267" width="15.44140625" style="70" customWidth="1"/>
+    <col min="11268" max="11272" width="10" style="70" customWidth="1"/>
+    <col min="11273" max="11273" width="13.33203125" style="70" customWidth="1"/>
+    <col min="11274" max="11518" width="10" style="70" customWidth="1"/>
+    <col min="11519" max="11523" width="15.44140625" style="70" customWidth="1"/>
+    <col min="11524" max="11528" width="10" style="70" customWidth="1"/>
+    <col min="11529" max="11529" width="13.33203125" style="70" customWidth="1"/>
+    <col min="11530" max="11774" width="10" style="70" customWidth="1"/>
+    <col min="11775" max="11779" width="15.44140625" style="70" customWidth="1"/>
+    <col min="11780" max="11784" width="10" style="70" customWidth="1"/>
+    <col min="11785" max="11785" width="13.33203125" style="70" customWidth="1"/>
+    <col min="11786" max="12030" width="10" style="70" customWidth="1"/>
+    <col min="12031" max="12035" width="15.44140625" style="70" customWidth="1"/>
+    <col min="12036" max="12040" width="10" style="70" customWidth="1"/>
+    <col min="12041" max="12041" width="13.33203125" style="70" customWidth="1"/>
+    <col min="12042" max="12286" width="10" style="70" customWidth="1"/>
+    <col min="12287" max="12291" width="15.44140625" style="70" customWidth="1"/>
+    <col min="12292" max="12296" width="10" style="70" customWidth="1"/>
+    <col min="12297" max="12297" width="13.33203125" style="70" customWidth="1"/>
+    <col min="12298" max="12542" width="10" style="70" customWidth="1"/>
+    <col min="12543" max="12547" width="15.44140625" style="70" customWidth="1"/>
+    <col min="12548" max="12552" width="10" style="70" customWidth="1"/>
+    <col min="12553" max="12553" width="13.33203125" style="70" customWidth="1"/>
+    <col min="12554" max="12798" width="10" style="70" customWidth="1"/>
+    <col min="12799" max="12803" width="15.44140625" style="70" customWidth="1"/>
+    <col min="12804" max="12808" width="10" style="70" customWidth="1"/>
+    <col min="12809" max="12809" width="13.33203125" style="70" customWidth="1"/>
+    <col min="12810" max="13054" width="10" style="70" customWidth="1"/>
+    <col min="13055" max="13059" width="15.44140625" style="70" customWidth="1"/>
+    <col min="13060" max="13064" width="10" style="70" customWidth="1"/>
+    <col min="13065" max="13065" width="13.33203125" style="70" customWidth="1"/>
+    <col min="13066" max="13310" width="10" style="70" customWidth="1"/>
+    <col min="13311" max="13315" width="15.44140625" style="70" customWidth="1"/>
+    <col min="13316" max="13320" width="10" style="70" customWidth="1"/>
+    <col min="13321" max="13321" width="13.33203125" style="70" customWidth="1"/>
+    <col min="13322" max="13566" width="10" style="70" customWidth="1"/>
+    <col min="13567" max="13571" width="15.44140625" style="70" customWidth="1"/>
+    <col min="13572" max="13576" width="10" style="70" customWidth="1"/>
+    <col min="13577" max="13577" width="13.33203125" style="70" customWidth="1"/>
+    <col min="13578" max="13822" width="10" style="70" customWidth="1"/>
+    <col min="13823" max="13827" width="15.44140625" style="70" customWidth="1"/>
+    <col min="13828" max="13832" width="10" style="70" customWidth="1"/>
+    <col min="13833" max="13833" width="13.33203125" style="70" customWidth="1"/>
+    <col min="13834" max="14078" width="10" style="70" customWidth="1"/>
+    <col min="14079" max="14083" width="15.44140625" style="70" customWidth="1"/>
+    <col min="14084" max="14088" width="10" style="70" customWidth="1"/>
+    <col min="14089" max="14089" width="13.33203125" style="70" customWidth="1"/>
+    <col min="14090" max="14334" width="10" style="70" customWidth="1"/>
+    <col min="14335" max="14339" width="15.44140625" style="70" customWidth="1"/>
+    <col min="14340" max="14344" width="10" style="70" customWidth="1"/>
+    <col min="14345" max="14345" width="13.33203125" style="70" customWidth="1"/>
+    <col min="14346" max="14590" width="10" style="70" customWidth="1"/>
+    <col min="14591" max="14595" width="15.44140625" style="70" customWidth="1"/>
+    <col min="14596" max="14600" width="10" style="70" customWidth="1"/>
+    <col min="14601" max="14601" width="13.33203125" style="70" customWidth="1"/>
+    <col min="14602" max="14846" width="10" style="70" customWidth="1"/>
+    <col min="14847" max="14851" width="15.44140625" style="70" customWidth="1"/>
+    <col min="14852" max="14856" width="10" style="70" customWidth="1"/>
+    <col min="14857" max="14857" width="13.33203125" style="70" customWidth="1"/>
+    <col min="14858" max="15102" width="10" style="70" customWidth="1"/>
+    <col min="15103" max="15107" width="15.44140625" style="70" customWidth="1"/>
+    <col min="15108" max="15112" width="10" style="70" customWidth="1"/>
+    <col min="15113" max="15113" width="13.33203125" style="70" customWidth="1"/>
+    <col min="15114" max="15358" width="10" style="70" customWidth="1"/>
+    <col min="15359" max="15363" width="15.44140625" style="70" customWidth="1"/>
+    <col min="15364" max="15368" width="10" style="70" customWidth="1"/>
+    <col min="15369" max="15369" width="13.33203125" style="70" customWidth="1"/>
+    <col min="15370" max="15614" width="10" style="70" customWidth="1"/>
+    <col min="15615" max="15619" width="15.44140625" style="70" customWidth="1"/>
+    <col min="15620" max="15624" width="10" style="70" customWidth="1"/>
+    <col min="15625" max="15625" width="13.33203125" style="70" customWidth="1"/>
+    <col min="15626" max="15870" width="10" style="70" customWidth="1"/>
+    <col min="15871" max="15875" width="15.44140625" style="70" customWidth="1"/>
+    <col min="15876" max="15880" width="10" style="70" customWidth="1"/>
+    <col min="15881" max="15881" width="13.33203125" style="70" customWidth="1"/>
+    <col min="15882" max="16126" width="10" style="70" customWidth="1"/>
+    <col min="16127" max="16131" width="15.44140625" style="70" customWidth="1"/>
+    <col min="16132" max="16136" width="10" style="70" customWidth="1"/>
+    <col min="16137" max="16137" width="13.33203125" style="70" customWidth="1"/>
+    <col min="16138" max="16384" width="10" style="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="111" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="110"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="12"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="12"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="12"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="12"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="12"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="12"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="12"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="12"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="12"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
+      <c r="A18" s="12"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="12"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="12"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="12"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
+      <c r="A22" s="12"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="12"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="12"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="69"/>
+      <c r="A26" s="67"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="74"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="70"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="70"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
+      <c r="A29" s="68"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="114"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="113"/>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
+      <c r="A30" s="109"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="109"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="108"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="109"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
+      <c r="A32" s="108"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="109"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
+      <c r="A33" s="108"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="108"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="109"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="109"/>
+      <c r="A34" s="108"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="71"/>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
+      <c r="A35" s="69"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="71"/>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
+      <c r="A36" s="69"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="71"/>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
+      <c r="A37" s="69"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="71"/>
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
+      <c r="A38" s="69"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="71"/>
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
+      <c r="A39" s="69"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="71"/>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
+      <c r="A40" s="69"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="71"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
+      <c r="A41" s="69"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="71"/>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
+      <c r="A42" s="69"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="71"/>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
+      <c r="A43" s="69"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="71"/>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71"/>
+      <c r="A44" s="69"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="71"/>
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="71"/>
+      <c r="A45" s="69"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="71"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
+      <c r="A46" s="69"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="74" t="s">
+      <c r="A48" s="72" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="112" t="s">
+      <c r="A49" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="B49" s="109"/>
-      <c r="C49" s="109"/>
-      <c r="D49" s="109"/>
-      <c r="E49" s="109"/>
+      <c r="B49" s="108"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B52" s="109" t="s">
+      <c r="B52" s="108" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="109"/>
-      <c r="D52" s="109"/>
-      <c r="E52" s="109"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="B53" s="109" t="s">
+      <c r="B53" s="108" t="s">
         <v>242</v>
       </c>
-      <c r="C53" s="109"/>
-      <c r="D53" s="109"/>
-      <c r="E53" s="109"/>
+      <c r="C53" s="108"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="108"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B54" s="112" t="s">
+      <c r="B54" s="110" t="s">
         <v>244</v>
       </c>
-      <c r="C54" s="109"/>
-      <c r="D54" s="109"/>
-      <c r="E54" s="109"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="108"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B55" s="112" t="s">
+      <c r="B55" s="110" t="s">
         <v>246</v>
       </c>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="108"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B56" s="112" t="s">
+      <c r="B56" s="110" t="s">
         <v>248</v>
       </c>
-      <c r="C56" s="109"/>
-      <c r="D56" s="109"/>
-      <c r="E56" s="109"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="108"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="B57" s="112" t="s">
+      <c r="B57" s="110" t="s">
         <v>250</v>
       </c>
-      <c r="C57" s="109"/>
-      <c r="D57" s="109"/>
-      <c r="E57" s="109"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="108"/>
+      <c r="E57" s="108"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B58" s="112" t="s">
+      <c r="B58" s="110" t="s">
         <v>252</v>
       </c>
-      <c r="C58" s="109"/>
-      <c r="D58" s="109"/>
-      <c r="E58" s="109"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="108"/>
+      <c r="E58" s="108"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="12" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="70"/>
-      <c r="B62" s="70"/>
-      <c r="C62" s="70"/>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
+      <c r="A62" s="68"/>
+      <c r="B62" s="68"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="68"/>
+      <c r="E62" s="68"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="70"/>
-      <c r="B63" s="71"/>
-      <c r="C63" s="71"/>
-      <c r="D63" s="71"/>
-      <c r="E63" s="71"/>
+      <c r="A63" s="68"/>
+      <c r="B63" s="69"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="70"/>
-      <c r="B64" s="71"/>
-      <c r="C64" s="71"/>
-      <c r="D64" s="71"/>
-      <c r="E64" s="71"/>
+      <c r="A64" s="68"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="69"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="114"/>
-      <c r="B65" s="71"/>
-      <c r="C65" s="71"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="71"/>
+      <c r="A65" s="109"/>
+      <c r="B65" s="69"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="69"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="109"/>
-      <c r="B66" s="71"/>
-      <c r="C66" s="71"/>
-      <c r="D66" s="71"/>
-      <c r="E66" s="71"/>
+      <c r="A66" s="108"/>
+      <c r="B66" s="69"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="109"/>
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
+      <c r="A67" s="108"/>
+      <c r="B67" s="69"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="69"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="109"/>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
+      <c r="A68" s="108"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="69"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="109"/>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
+      <c r="A69" s="108"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="69"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="109"/>
-      <c r="B70" s="71"/>
-      <c r="C70" s="71"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="71"/>
+      <c r="A70" s="108"/>
+      <c r="B70" s="69"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="69"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="109"/>
-      <c r="B71" s="71"/>
-      <c r="C71" s="71"/>
-      <c r="D71" s="69"/>
-      <c r="E71" s="18"/>
+      <c r="A71" s="108"/>
+      <c r="B71" s="69"/>
+      <c r="C71" s="69"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="16"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="109"/>
-      <c r="B72" s="71"/>
-      <c r="C72" s="71"/>
-      <c r="D72" s="73"/>
-      <c r="E72" s="18"/>
+      <c r="A72" s="108"/>
+      <c r="B72" s="69"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="16"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="109"/>
-      <c r="B73" s="71"/>
-      <c r="C73" s="71"/>
-      <c r="D73" s="73"/>
-      <c r="E73" s="18"/>
+      <c r="A73" s="108"/>
+      <c r="B73" s="69"/>
+      <c r="C73" s="69"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="16"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="109"/>
-      <c r="B74" s="71"/>
-      <c r="C74" s="71"/>
-      <c r="D74" s="73"/>
-      <c r="E74" s="18"/>
+      <c r="A74" s="108"/>
+      <c r="B74" s="69"/>
+      <c r="C74" s="69"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="16"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="109"/>
-      <c r="B75" s="71"/>
-      <c r="C75" s="71"/>
-      <c r="D75" s="73"/>
-      <c r="E75" s="69"/>
+      <c r="A75" s="108"/>
+      <c r="B75" s="69"/>
+      <c r="C75" s="69"/>
+      <c r="D75" s="71"/>
+      <c r="E75" s="67"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="109"/>
-      <c r="B76" s="71"/>
-      <c r="C76" s="71"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="71"/>
+      <c r="A76" s="108"/>
+      <c r="B76" s="69"/>
+      <c r="C76" s="69"/>
+      <c r="D76" s="71"/>
+      <c r="E76" s="69"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="109"/>
-      <c r="B77" s="71"/>
-      <c r="C77" s="71"/>
-      <c r="D77" s="73"/>
-      <c r="E77" s="71"/>
+      <c r="A77" s="108"/>
+      <c r="B77" s="69"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="71"/>
+      <c r="E77" s="69"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="109"/>
-      <c r="B78" s="71"/>
-      <c r="C78" s="71"/>
-      <c r="D78" s="73"/>
-      <c r="E78" s="71"/>
+      <c r="A78" s="108"/>
+      <c r="B78" s="69"/>
+      <c r="C78" s="69"/>
+      <c r="D78" s="71"/>
+      <c r="E78" s="69"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="109"/>
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="71"/>
+      <c r="A79" s="108"/>
+      <c r="B79" s="69"/>
+      <c r="C79" s="69"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="69"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="109"/>
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="73"/>
-      <c r="E80" s="71"/>
+      <c r="A80" s="108"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="69"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="109"/>
-      <c r="B81" s="71"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="73"/>
-      <c r="E81" s="71"/>
+      <c r="A81" s="108"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="71"/>
+      <c r="E81" s="69"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="109"/>
-      <c r="B82" s="71"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="73"/>
-      <c r="E82" s="71"/>
+      <c r="A82" s="108"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="69"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="109"/>
-      <c r="B83" s="71"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="73"/>
-      <c r="E83" s="71"/>
+      <c r="A83" s="108"/>
+      <c r="B83" s="69"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="69"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="109"/>
-      <c r="B84" s="71"/>
-      <c r="C84" s="69"/>
-      <c r="D84" s="73"/>
-      <c r="E84" s="73"/>
+      <c r="A84" s="108"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="67"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="71"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="70"/>
+      <c r="A86" s="68"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="113"/>
-      <c r="B87" s="109"/>
-      <c r="C87" s="109"/>
-      <c r="D87" s="109"/>
-      <c r="E87" s="109"/>
+      <c r="A87" s="107"/>
+      <c r="B87" s="108"/>
+      <c r="C87" s="108"/>
+      <c r="D87" s="108"/>
+      <c r="E87" s="108"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="71"/>
-      <c r="B88" s="73"/>
-      <c r="C88" s="73"/>
-      <c r="D88" s="73"/>
-      <c r="E88" s="73"/>
+      <c r="A88" s="69"/>
+      <c r="B88" s="71"/>
+      <c r="C88" s="71"/>
+      <c r="D88" s="71"/>
+      <c r="E88" s="71"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="71"/>
-      <c r="B89" s="73"/>
-      <c r="C89" s="73"/>
-      <c r="D89" s="73"/>
-      <c r="E89" s="73"/>
+      <c r="A89" s="69"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="71"/>
+      <c r="D89" s="71"/>
+      <c r="E89" s="71"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="19"/>
+      <c r="A90" s="17"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
+      <c r="A91" s="12"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="20"/>
-      <c r="B93" s="74"/>
-      <c r="C93" s="74"/>
-      <c r="D93" s="74"/>
-      <c r="E93" s="74"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="72"/>
+      <c r="E93" s="72"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="74"/>
-      <c r="B94" s="63"/>
-      <c r="C94" s="63"/>
-      <c r="D94" s="63"/>
-      <c r="E94" s="63"/>
+      <c r="A94" s="72"/>
+      <c r="B94" s="61"/>
+      <c r="C94" s="61"/>
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="21"/>
-      <c r="B95" s="63"/>
-      <c r="C95" s="63"/>
-      <c r="D95" s="63"/>
-      <c r="E95" s="63"/>
+      <c r="A95" s="19"/>
+      <c r="B95" s="61"/>
+      <c r="C95" s="61"/>
+      <c r="D95" s="61"/>
+      <c r="E95" s="61"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="111"/>
-      <c r="B96" s="63"/>
-      <c r="C96" s="63"/>
-      <c r="D96" s="63"/>
-      <c r="E96" s="63"/>
+      <c r="A96" s="113"/>
+      <c r="B96" s="61"/>
+      <c r="C96" s="61"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="109"/>
-      <c r="B97" s="63"/>
-      <c r="C97" s="63"/>
-      <c r="D97" s="63"/>
-      <c r="E97" s="63"/>
+      <c r="A97" s="108"/>
+      <c r="B97" s="61"/>
+      <c r="C97" s="61"/>
+      <c r="D97" s="61"/>
+      <c r="E97" s="61"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="109"/>
-      <c r="B98" s="63"/>
-      <c r="C98" s="63"/>
-      <c r="D98" s="63"/>
-      <c r="E98" s="63"/>
+      <c r="A98" s="108"/>
+      <c r="B98" s="61"/>
+      <c r="C98" s="61"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="61"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="109"/>
-      <c r="B99" s="22"/>
-      <c r="C99" s="63"/>
-      <c r="D99" s="63"/>
-      <c r="E99" s="63"/>
+      <c r="A99" s="108"/>
+      <c r="B99" s="20"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="109"/>
-      <c r="B100" s="22"/>
-      <c r="C100" s="22"/>
-      <c r="D100" s="63"/>
-      <c r="E100" s="63"/>
+      <c r="A100" s="108"/>
+      <c r="B100" s="20"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="109"/>
-      <c r="B101" s="22"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="63"/>
-      <c r="E101" s="63"/>
+      <c r="A101" s="108"/>
+      <c r="B101" s="20"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="61"/>
+      <c r="E101" s="61"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="109"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="63"/>
-      <c r="E102" s="63"/>
+      <c r="A102" s="108"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="61"/>
+      <c r="E102" s="61"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="109"/>
-      <c r="B103" s="22"/>
-      <c r="C103" s="22"/>
-      <c r="D103" s="63"/>
-      <c r="E103" s="63"/>
+      <c r="A103" s="108"/>
+      <c r="B103" s="20"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="61"/>
+      <c r="E103" s="61"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="109"/>
-      <c r="B104" s="22"/>
-      <c r="C104" s="22"/>
-      <c r="D104" s="63"/>
-      <c r="E104" s="63"/>
+      <c r="A104" s="108"/>
+      <c r="B104" s="20"/>
+      <c r="C104" s="20"/>
+      <c r="D104" s="61"/>
+      <c r="E104" s="61"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="109"/>
-      <c r="B105" s="22"/>
-      <c r="C105" s="22"/>
-      <c r="D105" s="63"/>
-      <c r="E105" s="63"/>
+      <c r="A105" s="108"/>
+      <c r="B105" s="20"/>
+      <c r="C105" s="20"/>
+      <c r="D105" s="61"/>
+      <c r="E105" s="61"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="109"/>
-      <c r="B106" s="22"/>
-      <c r="C106" s="22"/>
-      <c r="D106" s="63"/>
-      <c r="E106" s="63"/>
+      <c r="A106" s="108"/>
+      <c r="B106" s="20"/>
+      <c r="C106" s="20"/>
+      <c r="D106" s="61"/>
+      <c r="E106" s="61"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="109"/>
-      <c r="B107" s="22"/>
-      <c r="C107" s="22"/>
-      <c r="D107" s="63"/>
-      <c r="E107" s="63"/>
+      <c r="A107" s="108"/>
+      <c r="B107" s="20"/>
+      <c r="C107" s="20"/>
+      <c r="D107" s="61"/>
+      <c r="E107" s="61"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="109"/>
-      <c r="B108" s="22"/>
-      <c r="C108" s="22"/>
-      <c r="D108" s="63"/>
-      <c r="E108" s="63"/>
+      <c r="A108" s="108"/>
+      <c r="B108" s="20"/>
+      <c r="C108" s="20"/>
+      <c r="D108" s="61"/>
+      <c r="E108" s="61"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="109"/>
-      <c r="B109" s="22"/>
-      <c r="C109" s="22"/>
-      <c r="D109" s="63"/>
-      <c r="E109" s="63"/>
+      <c r="A109" s="108"/>
+      <c r="B109" s="20"/>
+      <c r="C109" s="20"/>
+      <c r="D109" s="61"/>
+      <c r="E109" s="61"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="109"/>
-      <c r="B110" s="22"/>
-      <c r="C110" s="22"/>
-      <c r="D110" s="63"/>
-      <c r="E110" s="63"/>
+      <c r="A110" s="108"/>
+      <c r="B110" s="20"/>
+      <c r="C110" s="20"/>
+      <c r="D110" s="61"/>
+      <c r="E110" s="61"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="109"/>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="63"/>
-      <c r="E111" s="63"/>
+      <c r="A111" s="108"/>
+      <c r="B111" s="20"/>
+      <c r="C111" s="20"/>
+      <c r="D111" s="61"/>
+      <c r="E111" s="61"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="109"/>
-      <c r="B112" s="22"/>
-      <c r="C112" s="22"/>
-      <c r="D112" s="63"/>
-      <c r="E112" s="63"/>
+      <c r="A112" s="108"/>
+      <c r="B112" s="20"/>
+      <c r="C112" s="20"/>
+      <c r="D112" s="61"/>
+      <c r="E112" s="61"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="109"/>
-      <c r="B113" s="22"/>
-      <c r="C113" s="22"/>
-      <c r="D113" s="63"/>
-      <c r="E113" s="63"/>
+      <c r="A113" s="108"/>
+      <c r="B113" s="20"/>
+      <c r="C113" s="20"/>
+      <c r="D113" s="61"/>
+      <c r="E113" s="61"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="109"/>
-      <c r="B114" s="22"/>
-      <c r="C114" s="22"/>
-      <c r="D114" s="63"/>
-      <c r="E114" s="63"/>
+      <c r="A114" s="108"/>
+      <c r="B114" s="20"/>
+      <c r="C114" s="20"/>
+      <c r="D114" s="61"/>
+      <c r="E114" s="61"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="109"/>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="63"/>
+      <c r="A115" s="108"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="61"/>
+      <c r="E115" s="61"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="109"/>
-      <c r="B116" s="22"/>
-      <c r="C116" s="22"/>
-      <c r="D116" s="63"/>
-      <c r="E116" s="63"/>
+      <c r="A116" s="108"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="20"/>
+      <c r="D116" s="61"/>
+      <c r="E116" s="61"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="109"/>
-      <c r="B117" s="22"/>
-      <c r="C117" s="22"/>
-      <c r="D117" s="63"/>
-      <c r="E117" s="63"/>
+      <c r="A117" s="108"/>
+      <c r="B117" s="20"/>
+      <c r="C117" s="20"/>
+      <c r="D117" s="61"/>
+      <c r="E117" s="61"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="109"/>
-      <c r="B118" s="22"/>
-      <c r="C118" s="22"/>
-      <c r="D118" s="63"/>
-      <c r="E118" s="63"/>
+      <c r="A118" s="108"/>
+      <c r="B118" s="20"/>
+      <c r="C118" s="20"/>
+      <c r="D118" s="61"/>
+      <c r="E118" s="61"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="109"/>
-      <c r="B119" s="22"/>
-      <c r="C119" s="22"/>
-      <c r="D119" s="63"/>
-      <c r="E119" s="63"/>
+      <c r="A119" s="108"/>
+      <c r="B119" s="20"/>
+      <c r="C119" s="20"/>
+      <c r="D119" s="61"/>
+      <c r="E119" s="61"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="109"/>
-      <c r="B120" s="22"/>
-      <c r="C120" s="22"/>
-      <c r="D120" s="63"/>
-      <c r="E120" s="63"/>
+      <c r="A120" s="108"/>
+      <c r="B120" s="20"/>
+      <c r="C120" s="20"/>
+      <c r="D120" s="61"/>
+      <c r="E120" s="61"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="109"/>
-      <c r="B121" s="22"/>
-      <c r="C121" s="22"/>
-      <c r="D121" s="63"/>
-      <c r="E121" s="63"/>
+      <c r="A121" s="108"/>
+      <c r="B121" s="20"/>
+      <c r="C121" s="20"/>
+      <c r="D121" s="61"/>
+      <c r="E121" s="61"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="109"/>
-      <c r="B122" s="22"/>
-      <c r="C122" s="22"/>
-      <c r="D122" s="63"/>
-      <c r="E122" s="63"/>
+      <c r="A122" s="108"/>
+      <c r="B122" s="20"/>
+      <c r="C122" s="20"/>
+      <c r="D122" s="61"/>
+      <c r="E122" s="61"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="109"/>
-      <c r="B123" s="22"/>
-      <c r="C123" s="22"/>
-      <c r="D123" s="63"/>
-      <c r="E123" s="63"/>
+      <c r="A123" s="108"/>
+      <c r="B123" s="20"/>
+      <c r="C123" s="20"/>
+      <c r="D123" s="61"/>
+      <c r="E123" s="61"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="109"/>
-      <c r="B124" s="22"/>
-      <c r="C124" s="22"/>
-      <c r="D124" s="63"/>
-      <c r="E124" s="63"/>
+      <c r="A124" s="108"/>
+      <c r="B124" s="20"/>
+      <c r="C124" s="20"/>
+      <c r="D124" s="61"/>
+      <c r="E124" s="61"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="109"/>
-      <c r="B125" s="22"/>
-      <c r="C125" s="22"/>
-      <c r="D125" s="63"/>
-      <c r="E125" s="63"/>
+      <c r="A125" s="108"/>
+      <c r="B125" s="20"/>
+      <c r="C125" s="20"/>
+      <c r="D125" s="61"/>
+      <c r="E125" s="61"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="109"/>
-      <c r="B126" s="22"/>
-      <c r="C126" s="22"/>
-      <c r="D126" s="63"/>
-      <c r="E126" s="63"/>
+      <c r="A126" s="108"/>
+      <c r="B126" s="20"/>
+      <c r="C126" s="20"/>
+      <c r="D126" s="61"/>
+      <c r="E126" s="61"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="109"/>
-      <c r="B127" s="22"/>
-      <c r="C127" s="22"/>
-      <c r="D127" s="63"/>
-      <c r="E127" s="63"/>
+      <c r="A127" s="108"/>
+      <c r="B127" s="20"/>
+      <c r="C127" s="20"/>
+      <c r="D127" s="61"/>
+      <c r="E127" s="61"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="109"/>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="63"/>
-      <c r="E128" s="63"/>
+      <c r="A128" s="108"/>
+      <c r="B128" s="20"/>
+      <c r="C128" s="20"/>
+      <c r="D128" s="61"/>
+      <c r="E128" s="61"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="109"/>
-      <c r="B129" s="22"/>
-      <c r="C129" s="22"/>
-      <c r="D129" s="63"/>
-      <c r="E129" s="63"/>
+      <c r="A129" s="108"/>
+      <c r="B129" s="20"/>
+      <c r="C129" s="20"/>
+      <c r="D129" s="61"/>
+      <c r="E129" s="61"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="109"/>
-      <c r="B130" s="22"/>
-      <c r="C130" s="22"/>
-      <c r="D130" s="63"/>
-      <c r="E130" s="63"/>
+      <c r="A130" s="108"/>
+      <c r="B130" s="20"/>
+      <c r="C130" s="20"/>
+      <c r="D130" s="61"/>
+      <c r="E130" s="61"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="70"/>
+      <c r="A132" s="68"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="113"/>
-      <c r="B133" s="109"/>
-      <c r="C133" s="109"/>
-      <c r="D133" s="109"/>
-      <c r="E133" s="109"/>
+      <c r="A133" s="107"/>
+      <c r="B133" s="108"/>
+      <c r="C133" s="108"/>
+      <c r="D133" s="108"/>
+      <c r="E133" s="108"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="11" t="s">
         <v>254</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A65:A84"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
     <mergeCell ref="A1:E3"/>
     <mergeCell ref="A96:A130"/>
     <mergeCell ref="B54:E54"/>
@@ -11641,6 +11699,12 @@
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:D34"/>
     <mergeCell ref="B52:E52"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A65:A84"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/skills/functional-safety/hazard_analysis/references/hara_template.xlsx
+++ b/skills/functional-safety/hazard_analysis/references/hara_template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7008" tabRatio="933" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7008" tabRatio="933" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="版本管理" sheetId="1" r:id="rId1"/>
@@ -2049,6 +2049,9 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2098,31 +2101,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2130,14 +2123,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -7313,33 +7313,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="121" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="112"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="112"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
       <c r="J3" s="35"/>
       <c r="K3" s="35"/>
       <c r="L3" s="35"/>
@@ -7358,13 +7358,13 @@
       <c r="A9" s="37"/>
     </row>
     <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="115" t="s">
         <v>256</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="117"/>
     </row>
     <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="75"/>
@@ -7433,13 +7433,13 @@
       <c r="E16" s="38"/>
     </row>
     <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>269</v>
       </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="120"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="117"/>
     </row>
     <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
@@ -7517,13 +7517,13 @@
       <c r="E22" s="39"/>
     </row>
     <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="121" t="s">
+      <c r="A23" s="120" t="s">
         <v>285</v>
       </c>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="120"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="117"/>
     </row>
     <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
@@ -7588,39 +7588,39 @@
       <c r="E29" s="77"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="116"/>
+      <c r="A30" s="123"/>
       <c r="B30" s="77"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="115"/>
+      <c r="A31" s="119"/>
       <c r="B31" s="77"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="115"/>
+      <c r="A32" s="119"/>
       <c r="B32" s="77"/>
-      <c r="C32" s="115"/>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
+      <c r="C32" s="119"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="115"/>
+      <c r="A33" s="119"/>
       <c r="B33" s="77"/>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
-      <c r="E33" s="115"/>
+      <c r="C33" s="119"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="115"/>
+      <c r="A34" s="119"/>
       <c r="B34" s="77"/>
-      <c r="C34" s="115"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="115"/>
+      <c r="C34" s="119"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="119"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="77"/>
@@ -7670,119 +7670,119 @@
       <c r="E43" s="77"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="116"/>
+      <c r="A44" s="123"/>
       <c r="B44" s="77"/>
       <c r="C44" s="77"/>
       <c r="D44" s="77"/>
       <c r="E44" s="77"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="115"/>
+      <c r="A45" s="119"/>
       <c r="B45" s="77"/>
       <c r="C45" s="77"/>
       <c r="D45" s="77"/>
       <c r="E45" s="77"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="115"/>
+      <c r="A46" s="119"/>
       <c r="B46" s="77"/>
       <c r="C46" s="77"/>
       <c r="D46" s="77"/>
       <c r="E46" s="77"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="115"/>
+      <c r="A47" s="119"/>
       <c r="B47" s="77"/>
       <c r="C47" s="77"/>
       <c r="D47" s="77"/>
       <c r="E47" s="77"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="115"/>
+      <c r="A48" s="119"/>
       <c r="B48" s="77"/>
       <c r="C48" s="77"/>
       <c r="D48" s="77"/>
       <c r="E48" s="77"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="115"/>
+      <c r="A49" s="119"/>
       <c r="B49" s="77"/>
       <c r="C49" s="77"/>
       <c r="D49" s="43"/>
       <c r="E49" s="77"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="115"/>
+      <c r="A50" s="119"/>
       <c r="B50" s="77"/>
       <c r="C50" s="77"/>
       <c r="D50" s="44"/>
       <c r="E50" s="43"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="115"/>
+      <c r="A51" s="119"/>
       <c r="B51" s="77"/>
       <c r="C51" s="77"/>
       <c r="D51" s="45"/>
       <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="115"/>
+      <c r="A52" s="119"/>
       <c r="B52" s="77"/>
       <c r="C52" s="77"/>
       <c r="D52" s="45"/>
       <c r="E52" s="43"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="115"/>
+      <c r="A53" s="119"/>
       <c r="B53" s="77"/>
       <c r="C53" s="77"/>
       <c r="D53" s="45"/>
       <c r="E53" s="43"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="115"/>
+      <c r="A54" s="119"/>
       <c r="B54" s="77"/>
       <c r="C54" s="77"/>
       <c r="D54" s="45"/>
       <c r="E54" s="44"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="115"/>
+      <c r="A55" s="119"/>
       <c r="B55" s="77"/>
       <c r="C55" s="77"/>
       <c r="D55" s="45"/>
       <c r="E55" s="77"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="115"/>
+      <c r="A56" s="119"/>
       <c r="B56" s="77"/>
       <c r="C56" s="77"/>
       <c r="D56" s="45"/>
       <c r="E56" s="77"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="115"/>
+      <c r="A57" s="119"/>
       <c r="B57" s="77"/>
       <c r="C57" s="77"/>
       <c r="D57" s="45"/>
       <c r="E57" s="77"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="115"/>
+      <c r="A58" s="119"/>
       <c r="B58" s="77"/>
       <c r="C58" s="77"/>
       <c r="D58" s="45"/>
       <c r="E58" s="77"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="115"/>
+      <c r="A59" s="119"/>
       <c r="B59" s="77"/>
       <c r="C59" s="77"/>
       <c r="D59" s="45"/>
       <c r="E59" s="77"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="115"/>
+      <c r="A60" s="119"/>
       <c r="B60" s="77"/>
       <c r="C60" s="77"/>
       <c r="D60" s="45"/>
@@ -7794,26 +7794,26 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="114" t="s">
+      <c r="A65" s="122" t="s">
         <v>291</v>
       </c>
-      <c r="B65" s="115"/>
-      <c r="C65" s="115"/>
-      <c r="D65" s="115"/>
-      <c r="E65" s="115"/>
+      <c r="B65" s="119"/>
+      <c r="C65" s="119"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="E30:E34"/>
+    <mergeCell ref="A44:A60"/>
+    <mergeCell ref="C30:C34"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="D30:D34"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A1:E3"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="E30:E34"/>
-    <mergeCell ref="A44:A60"/>
-    <mergeCell ref="C30:C34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7873,7 +7873,7 @@
       <c r="C2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="88" t="s">
+      <c r="D2" s="89" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="1"/>
@@ -7888,7 +7888,7 @@
       <c r="C3" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="89"/>
+      <c r="D3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="86" t="s">
@@ -7900,7 +7900,7 @@
       <c r="C4" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="89"/>
+      <c r="D4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="84" t="s">
@@ -7912,7 +7912,7 @@
       <c r="C5" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="90"/>
+      <c r="D5" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7930,12 +7930,12 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" style="123" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" style="88" customWidth="1"/>
     <col min="2" max="2" width="19.88671875" style="82" customWidth="1"/>
     <col min="3" max="3" width="22.5546875" style="82" customWidth="1"/>
     <col min="4" max="4" width="57.33203125" style="82" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="123" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="123" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="88" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="88" customWidth="1"/>
     <col min="7" max="7" width="28.6640625" style="82" customWidth="1"/>
     <col min="8" max="8" width="24.109375" style="82" customWidth="1"/>
     <col min="9" max="10" width="9" style="82" customWidth="1"/>
@@ -7944,7 +7944,7 @@
     <col min="13" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="82" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
@@ -7967,86 +7967,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-    </row>
-    <row r="3" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-    </row>
-    <row r="4" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-    </row>
-    <row r="5" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-    </row>
-    <row r="6" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123"/>
-    </row>
-    <row r="7" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-    </row>
-    <row r="8" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-    </row>
-    <row r="9" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="123"/>
-    </row>
-    <row r="10" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-    </row>
-    <row r="11" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-    </row>
-    <row r="12" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-    </row>
-    <row r="13" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-    </row>
-    <row r="14" spans="1:7" s="82" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-    </row>
-    <row r="15" spans="1:7" s="82" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="123"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="123"/>
-    </row>
-    <row r="16" spans="1:7" s="82" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="123"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-    </row>
-    <row r="22" spans="1:6" s="82" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="123"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="123"/>
-    </row>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="14.4" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8072,32 +8008,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="92" t="s">
         <v>303</v>
       </c>
-      <c r="C1" s="91" t="s">
+      <c r="C1" s="92" t="s">
         <v>306</v>
       </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="93" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="81" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="91"/>
-      <c r="B2" s="91"/>
+      <c r="A2" s="92"/>
+      <c r="B2" s="92"/>
       <c r="C2" s="79" t="s">
         <v>27</v>
       </c>
@@ -8131,7 +8067,7 @@
       <c r="M2" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="92"/>
+      <c r="N2" s="93"/>
     </row>
     <row r="4" spans="1:14" s="81" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -8161,24 +8097,24 @@
     <col min="1" max="1" width="14.6640625" style="21" customWidth="1"/>
     <col min="2" max="2" width="16.21875" style="21" customWidth="1"/>
     <col min="3" max="3" width="16.44140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" style="22" customWidth="1"/>
-    <col min="6" max="6" width="58.77734375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" style="24" customWidth="1"/>
-    <col min="8" max="8" width="10" style="24" customWidth="1"/>
+    <col min="4" max="4" width="40" style="22" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.77734375" style="23" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" style="24" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
     </row>
     <row r="2" spans="1:8" s="26" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
@@ -8252,45 +8188,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="98" t="s">
         <v>303</v>
       </c>
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="98" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="99" t="s">
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="91" t="s">
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91" t="s">
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="96"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
       <c r="D2" s="78" t="s">
         <v>43</v>
       </c>
@@ -8339,7 +8275,7 @@
       <c r="S2" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="91"/>
+      <c r="T2" s="92"/>
     </row>
     <row r="3" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -8379,21 +8315,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="103" t="s">
         <v>300</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102" t="s">
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103" t="s">
         <v>299</v>
       </c>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="103" t="s">
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="104" t="s">
         <v>298</v>
       </c>
     </row>
@@ -8428,7 +8364,7 @@
       <c r="J2" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="K2" s="103"/>
+      <c r="K2" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8457,13 +8393,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
@@ -10878,33 +10814,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="108" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="112"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="112"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -10995,39 +10931,39 @@
       <c r="E29" s="69"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="109"/>
+      <c r="A30" s="113"/>
       <c r="B30" s="69"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="107"/>
-      <c r="E30" s="107"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="108"/>
+      <c r="A31" s="109"/>
       <c r="B31" s="69"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="108"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="108"/>
+      <c r="A32" s="109"/>
       <c r="B32" s="69"/>
-      <c r="C32" s="108"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
+      <c r="C32" s="109"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="108"/>
+      <c r="A33" s="109"/>
       <c r="B33" s="69"/>
-      <c r="C33" s="108"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="108"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="108"/>
+      <c r="A34" s="109"/>
       <c r="B34" s="69"/>
-      <c r="C34" s="108"/>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="69"/>
@@ -11119,13 +11055,13 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="110" t="s">
+      <c r="A49" s="112" t="s">
         <v>237</v>
       </c>
-      <c r="B49" s="108"/>
-      <c r="C49" s="108"/>
-      <c r="D49" s="108"/>
-      <c r="E49" s="108"/>
+      <c r="B49" s="109"/>
+      <c r="C49" s="109"/>
+      <c r="D49" s="109"/>
+      <c r="E49" s="109"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
@@ -11136,78 +11072,78 @@
       <c r="A52" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B52" s="108" t="s">
+      <c r="B52" s="109" t="s">
         <v>240</v>
       </c>
-      <c r="C52" s="108"/>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
+      <c r="C52" s="109"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="B53" s="108" t="s">
+      <c r="B53" s="109" t="s">
         <v>242</v>
       </c>
-      <c r="C53" s="108"/>
-      <c r="D53" s="108"/>
-      <c r="E53" s="108"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="109"/>
+      <c r="E53" s="109"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B54" s="110" t="s">
+      <c r="B54" s="112" t="s">
         <v>244</v>
       </c>
-      <c r="C54" s="108"/>
-      <c r="D54" s="108"/>
-      <c r="E54" s="108"/>
+      <c r="C54" s="109"/>
+      <c r="D54" s="109"/>
+      <c r="E54" s="109"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B55" s="110" t="s">
+      <c r="B55" s="112" t="s">
         <v>246</v>
       </c>
-      <c r="C55" s="108"/>
-      <c r="D55" s="108"/>
-      <c r="E55" s="108"/>
+      <c r="C55" s="109"/>
+      <c r="D55" s="109"/>
+      <c r="E55" s="109"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="B56" s="110" t="s">
+      <c r="B56" s="112" t="s">
         <v>248</v>
       </c>
-      <c r="C56" s="108"/>
-      <c r="D56" s="108"/>
-      <c r="E56" s="108"/>
+      <c r="C56" s="109"/>
+      <c r="D56" s="109"/>
+      <c r="E56" s="109"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="B57" s="110" t="s">
+      <c r="B57" s="112" t="s">
         <v>250</v>
       </c>
-      <c r="C57" s="108"/>
-      <c r="D57" s="108"/>
-      <c r="E57" s="108"/>
+      <c r="C57" s="109"/>
+      <c r="D57" s="109"/>
+      <c r="E57" s="109"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B58" s="110" t="s">
+      <c r="B58" s="112" t="s">
         <v>252</v>
       </c>
-      <c r="C58" s="108"/>
-      <c r="D58" s="108"/>
-      <c r="E58" s="108"/>
+      <c r="C58" s="109"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="109"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
@@ -11236,140 +11172,140 @@
       <c r="E64" s="69"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="109"/>
+      <c r="A65" s="113"/>
       <c r="B65" s="69"/>
       <c r="C65" s="69"/>
       <c r="D65" s="69"/>
       <c r="E65" s="69"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="108"/>
+      <c r="A66" s="109"/>
       <c r="B66" s="69"/>
       <c r="C66" s="69"/>
       <c r="D66" s="69"/>
       <c r="E66" s="69"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="108"/>
+      <c r="A67" s="109"/>
       <c r="B67" s="69"/>
       <c r="C67" s="69"/>
       <c r="D67" s="69"/>
       <c r="E67" s="69"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="108"/>
+      <c r="A68" s="109"/>
       <c r="B68" s="69"/>
       <c r="C68" s="69"/>
       <c r="D68" s="69"/>
       <c r="E68" s="69"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="108"/>
+      <c r="A69" s="109"/>
       <c r="B69" s="69"/>
       <c r="C69" s="69"/>
       <c r="D69" s="69"/>
       <c r="E69" s="69"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="108"/>
+      <c r="A70" s="109"/>
       <c r="B70" s="69"/>
       <c r="C70" s="69"/>
       <c r="D70" s="16"/>
       <c r="E70" s="69"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="108"/>
+      <c r="A71" s="109"/>
       <c r="B71" s="69"/>
       <c r="C71" s="69"/>
       <c r="D71" s="67"/>
       <c r="E71" s="16"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="108"/>
+      <c r="A72" s="109"/>
       <c r="B72" s="69"/>
       <c r="C72" s="69"/>
       <c r="D72" s="71"/>
       <c r="E72" s="16"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="108"/>
+      <c r="A73" s="109"/>
       <c r="B73" s="69"/>
       <c r="C73" s="69"/>
       <c r="D73" s="71"/>
       <c r="E73" s="16"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="108"/>
+      <c r="A74" s="109"/>
       <c r="B74" s="69"/>
       <c r="C74" s="69"/>
       <c r="D74" s="71"/>
       <c r="E74" s="16"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="108"/>
+      <c r="A75" s="109"/>
       <c r="B75" s="69"/>
       <c r="C75" s="69"/>
       <c r="D75" s="71"/>
       <c r="E75" s="67"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="108"/>
+      <c r="A76" s="109"/>
       <c r="B76" s="69"/>
       <c r="C76" s="69"/>
       <c r="D76" s="71"/>
       <c r="E76" s="69"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="108"/>
+      <c r="A77" s="109"/>
       <c r="B77" s="69"/>
       <c r="C77" s="69"/>
       <c r="D77" s="71"/>
       <c r="E77" s="69"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="108"/>
+      <c r="A78" s="109"/>
       <c r="B78" s="69"/>
       <c r="C78" s="69"/>
       <c r="D78" s="71"/>
       <c r="E78" s="69"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="108"/>
+      <c r="A79" s="109"/>
       <c r="B79" s="69"/>
       <c r="C79" s="69"/>
       <c r="D79" s="71"/>
       <c r="E79" s="69"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="108"/>
+      <c r="A80" s="109"/>
       <c r="B80" s="69"/>
       <c r="C80" s="69"/>
       <c r="D80" s="71"/>
       <c r="E80" s="69"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="108"/>
+      <c r="A81" s="109"/>
       <c r="B81" s="69"/>
       <c r="C81" s="69"/>
       <c r="D81" s="71"/>
       <c r="E81" s="69"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="108"/>
+      <c r="A82" s="109"/>
       <c r="B82" s="69"/>
       <c r="C82" s="69"/>
       <c r="D82" s="71"/>
       <c r="E82" s="69"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="108"/>
+      <c r="A83" s="109"/>
       <c r="B83" s="69"/>
       <c r="C83" s="16"/>
       <c r="D83" s="71"/>
       <c r="E83" s="69"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="108"/>
+      <c r="A84" s="109"/>
       <c r="B84" s="69"/>
       <c r="C84" s="67"/>
       <c r="D84" s="71"/>
@@ -11379,11 +11315,11 @@
       <c r="A86" s="68"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="107"/>
-      <c r="B87" s="108"/>
-      <c r="C87" s="108"/>
-      <c r="D87" s="108"/>
-      <c r="E87" s="108"/>
+      <c r="A87" s="114"/>
+      <c r="B87" s="109"/>
+      <c r="C87" s="109"/>
+      <c r="D87" s="109"/>
+      <c r="E87" s="109"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="69"/>
@@ -11427,245 +11363,245 @@
       <c r="E95" s="61"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="113"/>
+      <c r="A96" s="111"/>
       <c r="B96" s="61"/>
       <c r="C96" s="61"/>
       <c r="D96" s="61"/>
       <c r="E96" s="61"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="108"/>
+      <c r="A97" s="109"/>
       <c r="B97" s="61"/>
       <c r="C97" s="61"/>
       <c r="D97" s="61"/>
       <c r="E97" s="61"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="108"/>
+      <c r="A98" s="109"/>
       <c r="B98" s="61"/>
       <c r="C98" s="61"/>
       <c r="D98" s="61"/>
       <c r="E98" s="61"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="108"/>
+      <c r="A99" s="109"/>
       <c r="B99" s="20"/>
       <c r="C99" s="61"/>
       <c r="D99" s="61"/>
       <c r="E99" s="61"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="108"/>
+      <c r="A100" s="109"/>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
       <c r="D100" s="61"/>
       <c r="E100" s="61"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="108"/>
+      <c r="A101" s="109"/>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
       <c r="D101" s="61"/>
       <c r="E101" s="61"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="108"/>
+      <c r="A102" s="109"/>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
       <c r="D102" s="61"/>
       <c r="E102" s="61"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="108"/>
+      <c r="A103" s="109"/>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
       <c r="D103" s="61"/>
       <c r="E103" s="61"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="108"/>
+      <c r="A104" s="109"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
       <c r="D104" s="61"/>
       <c r="E104" s="61"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="108"/>
+      <c r="A105" s="109"/>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
       <c r="D105" s="61"/>
       <c r="E105" s="61"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="108"/>
+      <c r="A106" s="109"/>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
       <c r="D106" s="61"/>
       <c r="E106" s="61"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="108"/>
+      <c r="A107" s="109"/>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
       <c r="D107" s="61"/>
       <c r="E107" s="61"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="108"/>
+      <c r="A108" s="109"/>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
       <c r="D108" s="61"/>
       <c r="E108" s="61"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="108"/>
+      <c r="A109" s="109"/>
       <c r="B109" s="20"/>
       <c r="C109" s="20"/>
       <c r="D109" s="61"/>
       <c r="E109" s="61"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="108"/>
+      <c r="A110" s="109"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
       <c r="D110" s="61"/>
       <c r="E110" s="61"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="108"/>
+      <c r="A111" s="109"/>
       <c r="B111" s="20"/>
       <c r="C111" s="20"/>
       <c r="D111" s="61"/>
       <c r="E111" s="61"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="108"/>
+      <c r="A112" s="109"/>
       <c r="B112" s="20"/>
       <c r="C112" s="20"/>
       <c r="D112" s="61"/>
       <c r="E112" s="61"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="108"/>
+      <c r="A113" s="109"/>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
       <c r="D113" s="61"/>
       <c r="E113" s="61"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="108"/>
+      <c r="A114" s="109"/>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
       <c r="D114" s="61"/>
       <c r="E114" s="61"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="108"/>
+      <c r="A115" s="109"/>
       <c r="B115" s="20"/>
       <c r="C115" s="20"/>
       <c r="D115" s="61"/>
       <c r="E115" s="61"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="108"/>
+      <c r="A116" s="109"/>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
       <c r="D116" s="61"/>
       <c r="E116" s="61"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="108"/>
+      <c r="A117" s="109"/>
       <c r="B117" s="20"/>
       <c r="C117" s="20"/>
       <c r="D117" s="61"/>
       <c r="E117" s="61"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="108"/>
+      <c r="A118" s="109"/>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
       <c r="D118" s="61"/>
       <c r="E118" s="61"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="108"/>
+      <c r="A119" s="109"/>
       <c r="B119" s="20"/>
       <c r="C119" s="20"/>
       <c r="D119" s="61"/>
       <c r="E119" s="61"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="108"/>
+      <c r="A120" s="109"/>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
       <c r="D120" s="61"/>
       <c r="E120" s="61"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="108"/>
+      <c r="A121" s="109"/>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
       <c r="D121" s="61"/>
       <c r="E121" s="61"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="108"/>
+      <c r="A122" s="109"/>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
       <c r="D122" s="61"/>
       <c r="E122" s="61"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="108"/>
+      <c r="A123" s="109"/>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
       <c r="D123" s="61"/>
       <c r="E123" s="61"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="108"/>
+      <c r="A124" s="109"/>
       <c r="B124" s="20"/>
       <c r="C124" s="20"/>
       <c r="D124" s="61"/>
       <c r="E124" s="61"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="108"/>
+      <c r="A125" s="109"/>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
       <c r="D125" s="61"/>
       <c r="E125" s="61"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="108"/>
+      <c r="A126" s="109"/>
       <c r="B126" s="20"/>
       <c r="C126" s="20"/>
       <c r="D126" s="61"/>
       <c r="E126" s="61"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="108"/>
+      <c r="A127" s="109"/>
       <c r="B127" s="20"/>
       <c r="C127" s="20"/>
       <c r="D127" s="61"/>
       <c r="E127" s="61"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="108"/>
+      <c r="A128" s="109"/>
       <c r="B128" s="20"/>
       <c r="C128" s="20"/>
       <c r="D128" s="61"/>
       <c r="E128" s="61"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="108"/>
+      <c r="A129" s="109"/>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
       <c r="D129" s="61"/>
       <c r="E129" s="61"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="108"/>
+      <c r="A130" s="109"/>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
       <c r="D130" s="61"/>
@@ -11675,11 +11611,11 @@
       <c r="A132" s="68"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="107"/>
-      <c r="B133" s="108"/>
-      <c r="C133" s="108"/>
-      <c r="D133" s="108"/>
-      <c r="E133" s="108"/>
+      <c r="A133" s="114"/>
+      <c r="B133" s="109"/>
+      <c r="C133" s="109"/>
+      <c r="D133" s="109"/>
+      <c r="E133" s="109"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
@@ -11688,6 +11624,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A65:A84"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
     <mergeCell ref="A1:E3"/>
     <mergeCell ref="A96:A130"/>
     <mergeCell ref="B54:E54"/>
@@ -11699,12 +11641,6 @@
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:D34"/>
     <mergeCell ref="B52:E52"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A65:A84"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/skills/functional-safety/hazard_analysis/references/hara_template.xlsx
+++ b/skills/functional-safety/hazard_analysis/references/hara_template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7008" tabRatio="933" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7008" tabRatio="933" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="版本管理" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="HAZOP 分析" sheetId="5" r:id="rId5"/>
     <sheet name="HARA 分析" sheetId="6" r:id="rId6"/>
     <sheet name="整车安全目标" sheetId="7" r:id="rId7"/>
-    <sheet name="参考场景 " sheetId="8" r:id="rId8"/>
-    <sheet name="S&amp;E&amp;C 评定参考（ ISO26262）" sheetId="9" r:id="rId9"/>
-    <sheet name="S&amp;E&amp;C 评定参考（ J2980）" sheetId="10" r:id="rId10"/>
-    <sheet name="ASIL 判定" sheetId="11" r:id="rId11"/>
+    <sheet name="S&amp;E&amp;C 评定参考（ ISO26262）" sheetId="9" r:id="rId8"/>
+    <sheet name="S&amp;E&amp;C 评定参考（ J2980）" sheetId="10" r:id="rId9"/>
+    <sheet name="ASIL 判定" sheetId="11" r:id="rId10"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
@@ -35,7 +35,6 @@
     <externalReference r:id="rId19"/>
     <externalReference r:id="rId20"/>
     <externalReference r:id="rId21"/>
-    <externalReference r:id="rId22"/>
   </externalReferences>
   <definedNames>
     <definedName name="___GoA1">'[1]Change History'!___GoA1</definedName>
@@ -49,14 +48,12 @@
     <definedName name="aaa">'[2]10_rating_matrix'!$O$13:$P$17</definedName>
     <definedName name="acceptance">'[3]1_basic_input'!$B$100:$B$102</definedName>
     <definedName name="act_pin_feature" localSheetId="4">#REF!</definedName>
-    <definedName name="act_pin_feature" localSheetId="7">#REF!</definedName>
     <definedName name="act_pin_feature">#REF!</definedName>
     <definedName name="aeb">#REF!</definedName>
     <definedName name="aebb">#REF!</definedName>
     <definedName name="Allocation">#REF!</definedName>
     <definedName name="Applicability">#REF!</definedName>
     <definedName name="application_signalname" localSheetId="4">#REF!</definedName>
-    <definedName name="application_signalname" localSheetId="7">#REF!</definedName>
     <definedName name="application_signalname">#REF!</definedName>
     <definedName name="as">'[3]10_rating_matrix'!$O$13:$P$17</definedName>
     <definedName name="asdasd">'[4]10_rating_matrix'!$O$13:$P$17</definedName>
@@ -92,12 +89,9 @@
     <definedName name="Bereich_1_1i_j_SoftwareArchitecture_2">'[6]1.1i-j Data SW Architecture'!$B$5:$B$9,'[6]1.1i-j Data SW Architecture'!$N$5:$O$9</definedName>
     <definedName name="Bereich_1_1k_l_SoftwareImplementation">'[6]1.1k-l Data SW Implementation'!$B$5:$B$9,'[6]1.1k-l Data SW Implementation'!$D$5:$E$9</definedName>
     <definedName name="Bereich_1_2a_ChangeRequests">'[6]1.2a Data Change Requests'!$B$5:$B$9,'[6]1.2a Data Change Requests'!$Z$5:$AC$9</definedName>
-    <definedName name="Bereich_1_2a_ChangeRequests_2" localSheetId="7">'[6]1.2a Data Change Requests'!$B$5:$B$9,'[6]1.2a Data Change Requests'!#REF!</definedName>
     <definedName name="Bereich_1_2a_ChangeRequests_2">'[6]1.2a Data Change Requests'!$B$5:$B$9,'[6]1.2a Data Change Requests'!#REF!</definedName>
-    <definedName name="Bereich_1_2a_ChangeRequests_3" localSheetId="7">'[6]1.2a Data Change Requests'!$B$5:$B$9,'[6]1.2a Data Change Requests'!#REF!</definedName>
     <definedName name="Bereich_1_2a_ChangeRequests_3">'[6]1.2a Data Change Requests'!$B$5:$B$9,'[6]1.2a Data Change Requests'!#REF!</definedName>
     <definedName name="Bereich_1_2b_ReportedDefects">'[6]1.2b Data Reported Defects'!$B$5:$B$9,'[6]1.2b Data Reported Defects'!$V$5:$Y$9</definedName>
-    <definedName name="Bereich_1_2b_ReportedDefects_2" localSheetId="7">'[6]1.2b Data Reported Defects'!$B$5:$B$9,'[6]1.2b Data Reported Defects'!#REF!</definedName>
     <definedName name="Bereich_1_2b_ReportedDefects_2">'[6]1.2b Data Reported Defects'!$B$5:$B$9,'[6]1.2b Data Reported Defects'!#REF!</definedName>
     <definedName name="Bereich_1_2c_TASKs">'[6]1.2c Data Status of TASKs'!$B$5:$B$9,'[6]1.2c Data Status of TASKs'!$J$5:$M$9</definedName>
     <definedName name="Bereich_1_2c_TASKs_2">'[6]1.2c Data Status of TASKs'!$B$5:$B$9,'[6]1.2c Data Status of TASKs'!$V$5:$V$9</definedName>
@@ -156,7 +150,6 @@
     <definedName name="functs">'[3]1_basic_input'!$C$24:$C$31</definedName>
     <definedName name="kdate">[7]Matrix矩阵!$I$2</definedName>
     <definedName name="kk" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="kk" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="kk">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="LookList">#REF!</definedName>
     <definedName name="mal_1">'[3]5_(mal)functions'!$D$5:$D$9</definedName>
@@ -174,40 +167,28 @@
     <definedName name="oroad">'[5]5.Exposure situation'!#REF!</definedName>
     <definedName name="park">'[5]5.Exposure situation'!#REF!</definedName>
     <definedName name="PFCEn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="PFCEn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="PFCEn_reg">#REF!</definedName>
     <definedName name="PFCn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="PFCn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="PFCn_reg">#REF!</definedName>
     <definedName name="PFn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="PFn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="PFn_reg">#REF!</definedName>
     <definedName name="pin_additional_features" localSheetId="4">#REF!</definedName>
-    <definedName name="pin_additional_features" localSheetId="7">#REF!</definedName>
     <definedName name="pin_additional_features">#REF!</definedName>
     <definedName name="pin_direction" localSheetId="4">#REF!</definedName>
-    <definedName name="pin_direction" localSheetId="7">#REF!</definedName>
     <definedName name="pin_direction">#REF!</definedName>
     <definedName name="pin_init_value" localSheetId="4">#REF!</definedName>
-    <definedName name="pin_init_value" localSheetId="7">#REF!</definedName>
     <definedName name="pin_init_value">#REF!</definedName>
     <definedName name="pin_name_possible_features" localSheetId="4">#REF!</definedName>
-    <definedName name="pin_name_possible_features" localSheetId="7">#REF!</definedName>
     <definedName name="pin_name_possible_features">#REF!</definedName>
     <definedName name="pin_number" localSheetId="4">#REF!</definedName>
-    <definedName name="pin_number" localSheetId="7">#REF!</definedName>
     <definedName name="pin_number">#REF!</definedName>
     <definedName name="PMCn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="PMCn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="PMCn_reg">#REF!</definedName>
     <definedName name="PMn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="PMn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="PMn_reg">#REF!</definedName>
     <definedName name="Pn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="Pn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="Pn_reg">#REF!</definedName>
     <definedName name="port_name" localSheetId="4">#REF!</definedName>
-    <definedName name="port_name" localSheetId="7">#REF!</definedName>
     <definedName name="port_name">#REF!</definedName>
     <definedName name="Powertrain_Mode">#REF!</definedName>
     <definedName name="preparer">[7]Matrix矩阵!$I$1</definedName>
@@ -215,7 +196,6 @@
     <definedName name="prospec">'[5]5.Exposure situation'!#REF!</definedName>
     <definedName name="ps">'[5]5.Exposure situation'!#REF!</definedName>
     <definedName name="PUn_reg" localSheetId="4">#REF!</definedName>
-    <definedName name="PUn_reg" localSheetId="7">#REF!</definedName>
     <definedName name="PUn_reg">#REF!</definedName>
     <definedName name="resp">[7]Matrix矩阵!$L$2</definedName>
     <definedName name="resp2">[7]Matrix矩阵!$L$3</definedName>
@@ -225,40 +205,28 @@
     <definedName name="rtype">#REF!</definedName>
     <definedName name="saaawww">#REF!</definedName>
     <definedName name="selection_PD70F3370" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3370" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3370">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3371" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3371" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3371">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3372" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3372" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3372">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3373" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3373" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3373">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3374" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3374" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3374">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3375" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3375" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3375">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3376" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3376" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3376">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3377" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3377" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3377">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3378" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3378" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3378">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3379" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3379" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3379">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3381" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3381" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3381">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3382" localSheetId="4">[11]preselection_MC9S12XDP512!#REF!</definedName>
-    <definedName name="selection_PD70F3382" localSheetId="7">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="selection_PD70F3382">[11]preselection_MC9S12XDP512!#REF!</definedName>
     <definedName name="ser">'[5]5.Exposure situation'!#REF!</definedName>
     <definedName name="sev">'[8]8.Rating_matrix'!$O$5:$O$8</definedName>
@@ -278,10 +246,8 @@
     <definedName name="weet">'[3]7_environmental_con.'!$C$4:$C$14</definedName>
     <definedName name="y_n">'[3]1_basic_input'!$C$103:$C$104</definedName>
     <definedName name="品" localSheetId="4">#REF!</definedName>
-    <definedName name="品" localSheetId="7">#REF!</definedName>
     <definedName name="品">#REF!</definedName>
     <definedName name="谁谁谁" localSheetId="4">#REF!</definedName>
-    <definedName name="谁谁谁" localSheetId="7">#REF!</definedName>
     <definedName name="谁谁谁">#REF!</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -289,7 +255,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
   <si>
     <t>Revision
 版本</t>
@@ -497,516 +463,6 @@
     <t>FTTI</t>
   </si>
   <si>
-    <t>参考场景（依据ISO 26262、J2980、头脑风暴以及项目经验）</t>
-  </si>
-  <si>
-    <t>主要结构</t>
-  </si>
-  <si>
-    <t>小组</t>
-  </si>
-  <si>
-    <t>评估环境</t>
-  </si>
-  <si>
-    <t>综合评定</t>
-  </si>
-  <si>
-    <t>环境</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>自然灾害</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>能见度</t>
-  </si>
-  <si>
-    <t>雪天</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>雾天/雾霾天 /沙尘</t>
-  </si>
-  <si>
-    <t>横风</t>
-  </si>
-  <si>
-    <t>雨夹雪</t>
-  </si>
-  <si>
-    <t>摩擦系数</t>
-  </si>
-  <si>
-    <t>在μ &lt;0.5 （+/- 0.1）的区域(如雪，冰…)上行驶时的低摩擦力。</t>
-  </si>
-  <si>
-    <t>行驶在μ-split路面上。(左/右偏移μ&gt; 0.3，例如从干/湿/冰的变化)</t>
-  </si>
-  <si>
-    <t>在μ-跳跃的道路上行驶(Delta- μ&gt; 0.3的过渡，例如从干/湿/冰的变化)</t>
-  </si>
-  <si>
-    <t>在能见度低于 50m 的能见度差（雾/眩光...）中驾驶</t>
-  </si>
-  <si>
-    <t>在μ &lt;0.8 （+/- 0.1）的区域内，以减少的摩擦系数驱动(例如，重湿、车辙、道路持续开裂)</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>在没有余光的黑暗中行驶，路边无任何反光物无法识别</t>
-  </si>
-  <si>
-    <t>普通路面驾驶</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>在黑暗中行驶，但路边有反光物可识别</t>
-  </si>
-  <si>
-    <t>障碍物</t>
-  </si>
-  <si>
-    <t>寒冷天气（需要进行电池加热）</t>
-  </si>
-  <si>
-    <t>行驶位置</t>
-  </si>
-  <si>
-    <t>道路类型</t>
-  </si>
-  <si>
-    <t>山路</t>
-  </si>
-  <si>
-    <t>越野</t>
-  </si>
-  <si>
-    <t>停车</t>
-  </si>
-  <si>
-    <t>服务站 洗车，内外清洁，车辆装修/贴膜</t>
-  </si>
-  <si>
-    <t>泥泞路</t>
-  </si>
-  <si>
-    <t>涉水路面</t>
-  </si>
-  <si>
-    <t>冰雪路面</t>
-  </si>
-  <si>
-    <t>砂石路；石子路</t>
-  </si>
-  <si>
-    <t>反光路面</t>
-  </si>
-  <si>
-    <t>乡间小路—十字路口</t>
-  </si>
-  <si>
-    <t>公路-隧道</t>
-  </si>
-  <si>
-    <t>高速公路</t>
-  </si>
-  <si>
-    <t>高架桥-交通灯</t>
-  </si>
-  <si>
-    <t>高速公路收费站</t>
-  </si>
-  <si>
-    <t>维修厂–自动升降机上的车辆</t>
-  </si>
-  <si>
-    <t>高速公路—进入</t>
-  </si>
-  <si>
-    <t>高速公路—退出</t>
-  </si>
-  <si>
-    <t>高速公路——拥堵即将结束</t>
-  </si>
-  <si>
-    <t>公路 - 狭窄的道路</t>
-  </si>
-  <si>
-    <t>在没有安全保障的陡坡的山口上行驶</t>
-  </si>
-  <si>
-    <t>通行道路</t>
-  </si>
-  <si>
-    <t>在关卡行驶</t>
-  </si>
-  <si>
-    <t>工地</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在施工区域（高速公路）行驶，无结构分离（中间无任何格挡，可直接冲入） </t>
-  </si>
-  <si>
-    <t>铁路道口</t>
-  </si>
-  <si>
-    <t xml:space="preserve">驶过铁路道口 </t>
-  </si>
-  <si>
-    <t>桥梁</t>
-  </si>
-  <si>
-    <t>乡村道路</t>
-  </si>
-  <si>
-    <t>窄路</t>
-  </si>
-  <si>
-    <t>隧道</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开车穿过隧道 </t>
-  </si>
-  <si>
-    <t>急弯/掉头/U路口</t>
-  </si>
-  <si>
-    <t>山岗</t>
-  </si>
-  <si>
-    <t>夜间在没有路灯的道路上驾驶</t>
-  </si>
-  <si>
-    <t>城市驾驶-单行道</t>
-  </si>
-  <si>
-    <t>在施工区域（高速公路）有分隔的行驶（道路有格挡，不可冲入）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">在乡村道路上行驶 </t>
-  </si>
-  <si>
-    <t>充电站</t>
-  </si>
-  <si>
-    <t>坡道</t>
-  </si>
-  <si>
-    <t>十字路口</t>
-  </si>
-  <si>
-    <t>城市道路</t>
-  </si>
-  <si>
-    <t>在停车场停车</t>
-  </si>
-  <si>
-    <t>在车库停车</t>
-  </si>
-  <si>
-    <t>路边停车</t>
-  </si>
-  <si>
-    <t>在高架道路上驾驶</t>
-  </si>
-  <si>
-    <t>在环线上行驶</t>
-  </si>
-  <si>
-    <t>城市驾驶-在红绿灯处停车</t>
-  </si>
-  <si>
-    <t>公路-交通繁忙/走走停停</t>
-  </si>
-  <si>
-    <t>弯道</t>
-  </si>
-  <si>
-    <t>交通状况驾驶</t>
-  </si>
-  <si>
-    <t>山上/坡度大于8%的斜坡</t>
-  </si>
-  <si>
-    <t>山上/坡度在2%到8%之间的斜坡</t>
-  </si>
-  <si>
-    <t>车辆状态</t>
-  </si>
-  <si>
-    <t>特殊行驶状态</t>
-  </si>
-  <si>
-    <t>高压电池热失控</t>
-  </si>
-  <si>
-    <t>碰撞</t>
-  </si>
-  <si>
-    <t>使用应急轮胎驾驶</t>
-  </si>
-  <si>
-    <t>用防滑链驾驶</t>
-  </si>
-  <si>
-    <t>用牵引链驾驶车辆牵引其他汽车</t>
-  </si>
-  <si>
-    <t>车辆正在被牵引(例如，在路上，从另一辆车)...)</t>
-  </si>
-  <si>
-    <t>维修厂-诊断</t>
-  </si>
-  <si>
-    <t>驾驶拖车</t>
-  </si>
-  <si>
-    <t>用装载的车顶行李架驾驶(例如箱子、轮子)</t>
-  </si>
-  <si>
-    <t>停在山上/坡度大于8%的斜坡上</t>
-  </si>
-  <si>
-    <t>停在山上/坡度在2%到8%之间的斜坡上</t>
-  </si>
-  <si>
-    <t>动态驾驶运动状态</t>
-  </si>
-  <si>
-    <t>滑行</t>
-  </si>
-  <si>
-    <t>其他的策略</t>
-  </si>
-  <si>
-    <t>充电</t>
-  </si>
-  <si>
-    <t>以超过 120km/h 的速度行驶</t>
-  </si>
-  <si>
-    <t>以超过 4 m / s2 的纵向加速度行驶</t>
-  </si>
-  <si>
-    <t>减速超过4米/秒2的驾驶</t>
-  </si>
-  <si>
-    <t>车辆进行超车(对向车道超车)</t>
-  </si>
-  <si>
-    <t>车辆进行超车(同向车道超车)</t>
-  </si>
-  <si>
-    <t>蠕行</t>
-  </si>
-  <si>
-    <t>在街道上停车(例如，在停车标志、红绿灯、人行横道前)...)</t>
-  </si>
-  <si>
-    <t>在交叉路口行驶，即车辆穿过其他道路使用者的道路(有/没有红绿灯、人行横道、自行车道…)</t>
-  </si>
-  <si>
-    <t>从十字路口转弯</t>
-  </si>
-  <si>
-    <t>启动过程：(0 &lt; v &lt; 10 km/h)</t>
-  </si>
-  <si>
-    <t>低速行驶：(0 &lt; v &lt; 10 km/h)</t>
-  </si>
-  <si>
-    <t>行驶速度：(10 &lt; v &lt; 30 km/h)</t>
-  </si>
-  <si>
-    <t>行驶速度：(30 &lt; v &lt; 60 km/h)</t>
-  </si>
-  <si>
-    <t>行驶速度：(60 &lt; v &lt; 120 km/h)</t>
-  </si>
-  <si>
-    <t>以正常纵向加速度 (&lt; 2 m/s2) 行驶</t>
-  </si>
-  <si>
-    <t>以超过 2 m/s2 的纵向加速度行驶</t>
-  </si>
-  <si>
-    <t>正常减速行驶 (&lt; 4m/s2)</t>
-  </si>
-  <si>
-    <t>执行车道变换(车辆不完全在一条车道上的时间段)</t>
-  </si>
-  <si>
-    <t>倒车</t>
-  </si>
-  <si>
-    <t>减速超过6米/秒2的驾驶（如紧急制动等）</t>
-  </si>
-  <si>
-    <t>特殊车辆状态</t>
-  </si>
-  <si>
-    <t>制动液位低</t>
-  </si>
-  <si>
-    <t>胎压异常</t>
-  </si>
-  <si>
-    <t>释放加速踏板</t>
-  </si>
-  <si>
-    <t>释放制动踏板</t>
-  </si>
-  <si>
-    <t>车辆在车位停车但未下电</t>
-  </si>
-  <si>
-    <t xml:space="preserve">动力电池温度达到阈值需要冷却 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> E1</t>
-  </si>
-  <si>
-    <t>电机及控制器过热</t>
-  </si>
-  <si>
-    <t>踩制动踏板</t>
-  </si>
-  <si>
-    <t>车辆对外放电V2L</t>
-  </si>
-  <si>
-    <t>交通参与者</t>
-  </si>
-  <si>
-    <t>乘客</t>
-  </si>
-  <si>
-    <t>人将身体部分伸出侧面或天窗</t>
-  </si>
-  <si>
-    <t>其他车辆</t>
-  </si>
-  <si>
-    <t>自车跟车距离较近</t>
-  </si>
-  <si>
-    <t>注: 停车时为E4 .</t>
-  </si>
-  <si>
-    <t>后车跟车距离较近</t>
-  </si>
-  <si>
-    <t>驾驶员行为</t>
-  </si>
-  <si>
-    <t>遵循正常距离行驶</t>
-  </si>
-  <si>
-    <t>驾驶员切换档位</t>
-  </si>
-  <si>
-    <t>主动转向信号驾驶</t>
-  </si>
-  <si>
-    <t>驾驶员解开安全带</t>
-  </si>
-  <si>
-    <t>司机系好安全带</t>
-  </si>
-  <si>
-    <t>驾驶员在车内不启动</t>
-  </si>
-  <si>
-    <t>在车内无人的情况（包括停车）</t>
-  </si>
-  <si>
-    <t>司机不在的情况下待在车内</t>
-  </si>
-  <si>
-    <t>弱势群体</t>
-  </si>
-  <si>
-    <t>在静止车辆前方/后方处于危险区域（约 1 辆车长）的人员</t>
-  </si>
-  <si>
-    <t>相邻车道有车</t>
-  </si>
-  <si>
-    <t>周围无车辆</t>
-  </si>
-  <si>
-    <t>侧向来车</t>
-  </si>
-  <si>
-    <t>自车跟车距离极近</t>
-  </si>
-  <si>
-    <t>注: 停车时为E3.</t>
-  </si>
-  <si>
-    <t>后车跟车距离极近</t>
-  </si>
-  <si>
-    <t>在静止车辆前方/后方处于危险区域（约 1 辆车长）的易受伤害人员</t>
-  </si>
-  <si>
-    <t>相邻对向车道有车</t>
-  </si>
-  <si>
-    <t>驾驶员接管</t>
-  </si>
-  <si>
-    <t>自车跟车距离远</t>
-  </si>
-  <si>
-    <t>后车跟车距离远</t>
-  </si>
-  <si>
-    <t>行人或非机动车横穿车辆前方</t>
-  </si>
-  <si>
-    <t>车内有婴儿</t>
-  </si>
-  <si>
-    <t>车内人员在睡觉</t>
-  </si>
-  <si>
-    <t>在低速行驶车辆前方/后方处于危险区域（约 1 辆车长）的人员</t>
-  </si>
-  <si>
-    <t>有乘客上下车</t>
-  </si>
-  <si>
-    <t>乘客失去自救能力</t>
-  </si>
-  <si>
-    <t>在低速行驶车辆前方/后方处于危险区域（约 1 辆车长）的易受伤害人员</t>
-  </si>
-  <si>
-    <t>道路旁边有行人</t>
-  </si>
-  <si>
-    <t>儿童单独坐在后排，无安全座椅</t>
-  </si>
-  <si>
-    <t>驾驶员未系安全带</t>
-  </si>
-  <si>
-    <t>行人或非机动车横穿车辆后方</t>
-  </si>
-  <si>
     <t>Hazard Analysis and Risk Assessment
  - Examples -</t>
   </si>
@@ -1197,7 +653,7 @@
   </si>
   <si>
     <t>FTTI</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>整车安全目标ID</t>
@@ -1257,7 +713,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1291,12 +747,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1399,62 +849,11 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1479,19 +878,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
@@ -1507,7 +893,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1546,18 +932,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1673,32 +1053,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -1779,14 +1133,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
@@ -1796,58 +1150,46 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="35" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1855,68 +1197,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
@@ -1931,43 +1261,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="13" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="13" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1979,23 +1273,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2005,139 +1299,134 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="12" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="12" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -7013,30 +6302,30 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" style="66" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="66" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="66" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="66" customWidth="1"/>
-    <col min="5" max="5" width="49.77734375" style="66" customWidth="1"/>
-    <col min="6" max="6" width="12" style="66" customWidth="1"/>
-    <col min="7" max="7" width="9" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="66"/>
+    <col min="1" max="1" width="9.88671875" style="46" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="46" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="46" customWidth="1"/>
+    <col min="5" max="5" width="49.77734375" style="46" customWidth="1"/>
+    <col min="6" max="6" width="12" style="46" customWidth="1"/>
+    <col min="7" max="7" width="9" style="46" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="45" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7048,786 +6337,11 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L65"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.6640625" style="74" customWidth="1"/>
-    <col min="2" max="3" width="20.6640625" style="74" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" style="74" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" style="74" customWidth="1"/>
-    <col min="6" max="8" width="10" style="74" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" style="74" customWidth="1"/>
-    <col min="10" max="254" width="10" style="74" customWidth="1"/>
-    <col min="255" max="259" width="15.44140625" style="74" customWidth="1"/>
-    <col min="260" max="264" width="10" style="74" customWidth="1"/>
-    <col min="265" max="265" width="13.33203125" style="74" customWidth="1"/>
-    <col min="266" max="510" width="10" style="74" customWidth="1"/>
-    <col min="511" max="515" width="15.44140625" style="74" customWidth="1"/>
-    <col min="516" max="520" width="10" style="74" customWidth="1"/>
-    <col min="521" max="521" width="13.33203125" style="74" customWidth="1"/>
-    <col min="522" max="766" width="10" style="74" customWidth="1"/>
-    <col min="767" max="771" width="15.44140625" style="74" customWidth="1"/>
-    <col min="772" max="776" width="10" style="74" customWidth="1"/>
-    <col min="777" max="777" width="13.33203125" style="74" customWidth="1"/>
-    <col min="778" max="1022" width="10" style="74" customWidth="1"/>
-    <col min="1023" max="1027" width="15.44140625" style="74" customWidth="1"/>
-    <col min="1028" max="1032" width="10" style="74" customWidth="1"/>
-    <col min="1033" max="1033" width="13.33203125" style="74" customWidth="1"/>
-    <col min="1034" max="1278" width="10" style="74" customWidth="1"/>
-    <col min="1279" max="1283" width="15.44140625" style="74" customWidth="1"/>
-    <col min="1284" max="1288" width="10" style="74" customWidth="1"/>
-    <col min="1289" max="1289" width="13.33203125" style="74" customWidth="1"/>
-    <col min="1290" max="1534" width="10" style="74" customWidth="1"/>
-    <col min="1535" max="1539" width="15.44140625" style="74" customWidth="1"/>
-    <col min="1540" max="1544" width="10" style="74" customWidth="1"/>
-    <col min="1545" max="1545" width="13.33203125" style="74" customWidth="1"/>
-    <col min="1546" max="1790" width="10" style="74" customWidth="1"/>
-    <col min="1791" max="1795" width="15.44140625" style="74" customWidth="1"/>
-    <col min="1796" max="1800" width="10" style="74" customWidth="1"/>
-    <col min="1801" max="1801" width="13.33203125" style="74" customWidth="1"/>
-    <col min="1802" max="2046" width="10" style="74" customWidth="1"/>
-    <col min="2047" max="2051" width="15.44140625" style="74" customWidth="1"/>
-    <col min="2052" max="2056" width="10" style="74" customWidth="1"/>
-    <col min="2057" max="2057" width="13.33203125" style="74" customWidth="1"/>
-    <col min="2058" max="2302" width="10" style="74" customWidth="1"/>
-    <col min="2303" max="2307" width="15.44140625" style="74" customWidth="1"/>
-    <col min="2308" max="2312" width="10" style="74" customWidth="1"/>
-    <col min="2313" max="2313" width="13.33203125" style="74" customWidth="1"/>
-    <col min="2314" max="2558" width="10" style="74" customWidth="1"/>
-    <col min="2559" max="2563" width="15.44140625" style="74" customWidth="1"/>
-    <col min="2564" max="2568" width="10" style="74" customWidth="1"/>
-    <col min="2569" max="2569" width="13.33203125" style="74" customWidth="1"/>
-    <col min="2570" max="2814" width="10" style="74" customWidth="1"/>
-    <col min="2815" max="2819" width="15.44140625" style="74" customWidth="1"/>
-    <col min="2820" max="2824" width="10" style="74" customWidth="1"/>
-    <col min="2825" max="2825" width="13.33203125" style="74" customWidth="1"/>
-    <col min="2826" max="3070" width="10" style="74" customWidth="1"/>
-    <col min="3071" max="3075" width="15.44140625" style="74" customWidth="1"/>
-    <col min="3076" max="3080" width="10" style="74" customWidth="1"/>
-    <col min="3081" max="3081" width="13.33203125" style="74" customWidth="1"/>
-    <col min="3082" max="3326" width="10" style="74" customWidth="1"/>
-    <col min="3327" max="3331" width="15.44140625" style="74" customWidth="1"/>
-    <col min="3332" max="3336" width="10" style="74" customWidth="1"/>
-    <col min="3337" max="3337" width="13.33203125" style="74" customWidth="1"/>
-    <col min="3338" max="3582" width="10" style="74" customWidth="1"/>
-    <col min="3583" max="3587" width="15.44140625" style="74" customWidth="1"/>
-    <col min="3588" max="3592" width="10" style="74" customWidth="1"/>
-    <col min="3593" max="3593" width="13.33203125" style="74" customWidth="1"/>
-    <col min="3594" max="3838" width="10" style="74" customWidth="1"/>
-    <col min="3839" max="3843" width="15.44140625" style="74" customWidth="1"/>
-    <col min="3844" max="3848" width="10" style="74" customWidth="1"/>
-    <col min="3849" max="3849" width="13.33203125" style="74" customWidth="1"/>
-    <col min="3850" max="4094" width="10" style="74" customWidth="1"/>
-    <col min="4095" max="4099" width="15.44140625" style="74" customWidth="1"/>
-    <col min="4100" max="4104" width="10" style="74" customWidth="1"/>
-    <col min="4105" max="4105" width="13.33203125" style="74" customWidth="1"/>
-    <col min="4106" max="4350" width="10" style="74" customWidth="1"/>
-    <col min="4351" max="4355" width="15.44140625" style="74" customWidth="1"/>
-    <col min="4356" max="4360" width="10" style="74" customWidth="1"/>
-    <col min="4361" max="4361" width="13.33203125" style="74" customWidth="1"/>
-    <col min="4362" max="4606" width="10" style="74" customWidth="1"/>
-    <col min="4607" max="4611" width="15.44140625" style="74" customWidth="1"/>
-    <col min="4612" max="4616" width="10" style="74" customWidth="1"/>
-    <col min="4617" max="4617" width="13.33203125" style="74" customWidth="1"/>
-    <col min="4618" max="4862" width="10" style="74" customWidth="1"/>
-    <col min="4863" max="4867" width="15.44140625" style="74" customWidth="1"/>
-    <col min="4868" max="4872" width="10" style="74" customWidth="1"/>
-    <col min="4873" max="4873" width="13.33203125" style="74" customWidth="1"/>
-    <col min="4874" max="5118" width="10" style="74" customWidth="1"/>
-    <col min="5119" max="5123" width="15.44140625" style="74" customWidth="1"/>
-    <col min="5124" max="5128" width="10" style="74" customWidth="1"/>
-    <col min="5129" max="5129" width="13.33203125" style="74" customWidth="1"/>
-    <col min="5130" max="5374" width="10" style="74" customWidth="1"/>
-    <col min="5375" max="5379" width="15.44140625" style="74" customWidth="1"/>
-    <col min="5380" max="5384" width="10" style="74" customWidth="1"/>
-    <col min="5385" max="5385" width="13.33203125" style="74" customWidth="1"/>
-    <col min="5386" max="5630" width="10" style="74" customWidth="1"/>
-    <col min="5631" max="5635" width="15.44140625" style="74" customWidth="1"/>
-    <col min="5636" max="5640" width="10" style="74" customWidth="1"/>
-    <col min="5641" max="5641" width="13.33203125" style="74" customWidth="1"/>
-    <col min="5642" max="5886" width="10" style="74" customWidth="1"/>
-    <col min="5887" max="5891" width="15.44140625" style="74" customWidth="1"/>
-    <col min="5892" max="5896" width="10" style="74" customWidth="1"/>
-    <col min="5897" max="5897" width="13.33203125" style="74" customWidth="1"/>
-    <col min="5898" max="6142" width="10" style="74" customWidth="1"/>
-    <col min="6143" max="6147" width="15.44140625" style="74" customWidth="1"/>
-    <col min="6148" max="6152" width="10" style="74" customWidth="1"/>
-    <col min="6153" max="6153" width="13.33203125" style="74" customWidth="1"/>
-    <col min="6154" max="6398" width="10" style="74" customWidth="1"/>
-    <col min="6399" max="6403" width="15.44140625" style="74" customWidth="1"/>
-    <col min="6404" max="6408" width="10" style="74" customWidth="1"/>
-    <col min="6409" max="6409" width="13.33203125" style="74" customWidth="1"/>
-    <col min="6410" max="6654" width="10" style="74" customWidth="1"/>
-    <col min="6655" max="6659" width="15.44140625" style="74" customWidth="1"/>
-    <col min="6660" max="6664" width="10" style="74" customWidth="1"/>
-    <col min="6665" max="6665" width="13.33203125" style="74" customWidth="1"/>
-    <col min="6666" max="6910" width="10" style="74" customWidth="1"/>
-    <col min="6911" max="6915" width="15.44140625" style="74" customWidth="1"/>
-    <col min="6916" max="6920" width="10" style="74" customWidth="1"/>
-    <col min="6921" max="6921" width="13.33203125" style="74" customWidth="1"/>
-    <col min="6922" max="7166" width="10" style="74" customWidth="1"/>
-    <col min="7167" max="7171" width="15.44140625" style="74" customWidth="1"/>
-    <col min="7172" max="7176" width="10" style="74" customWidth="1"/>
-    <col min="7177" max="7177" width="13.33203125" style="74" customWidth="1"/>
-    <col min="7178" max="7422" width="10" style="74" customWidth="1"/>
-    <col min="7423" max="7427" width="15.44140625" style="74" customWidth="1"/>
-    <col min="7428" max="7432" width="10" style="74" customWidth="1"/>
-    <col min="7433" max="7433" width="13.33203125" style="74" customWidth="1"/>
-    <col min="7434" max="7678" width="10" style="74" customWidth="1"/>
-    <col min="7679" max="7683" width="15.44140625" style="74" customWidth="1"/>
-    <col min="7684" max="7688" width="10" style="74" customWidth="1"/>
-    <col min="7689" max="7689" width="13.33203125" style="74" customWidth="1"/>
-    <col min="7690" max="7934" width="10" style="74" customWidth="1"/>
-    <col min="7935" max="7939" width="15.44140625" style="74" customWidth="1"/>
-    <col min="7940" max="7944" width="10" style="74" customWidth="1"/>
-    <col min="7945" max="7945" width="13.33203125" style="74" customWidth="1"/>
-    <col min="7946" max="8190" width="10" style="74" customWidth="1"/>
-    <col min="8191" max="8195" width="15.44140625" style="74" customWidth="1"/>
-    <col min="8196" max="8200" width="10" style="74" customWidth="1"/>
-    <col min="8201" max="8201" width="13.33203125" style="74" customWidth="1"/>
-    <col min="8202" max="8446" width="10" style="74" customWidth="1"/>
-    <col min="8447" max="8451" width="15.44140625" style="74" customWidth="1"/>
-    <col min="8452" max="8456" width="10" style="74" customWidth="1"/>
-    <col min="8457" max="8457" width="13.33203125" style="74" customWidth="1"/>
-    <col min="8458" max="8702" width="10" style="74" customWidth="1"/>
-    <col min="8703" max="8707" width="15.44140625" style="74" customWidth="1"/>
-    <col min="8708" max="8712" width="10" style="74" customWidth="1"/>
-    <col min="8713" max="8713" width="13.33203125" style="74" customWidth="1"/>
-    <col min="8714" max="8958" width="10" style="74" customWidth="1"/>
-    <col min="8959" max="8963" width="15.44140625" style="74" customWidth="1"/>
-    <col min="8964" max="8968" width="10" style="74" customWidth="1"/>
-    <col min="8969" max="8969" width="13.33203125" style="74" customWidth="1"/>
-    <col min="8970" max="9214" width="10" style="74" customWidth="1"/>
-    <col min="9215" max="9219" width="15.44140625" style="74" customWidth="1"/>
-    <col min="9220" max="9224" width="10" style="74" customWidth="1"/>
-    <col min="9225" max="9225" width="13.33203125" style="74" customWidth="1"/>
-    <col min="9226" max="9470" width="10" style="74" customWidth="1"/>
-    <col min="9471" max="9475" width="15.44140625" style="74" customWidth="1"/>
-    <col min="9476" max="9480" width="10" style="74" customWidth="1"/>
-    <col min="9481" max="9481" width="13.33203125" style="74" customWidth="1"/>
-    <col min="9482" max="9726" width="10" style="74" customWidth="1"/>
-    <col min="9727" max="9731" width="15.44140625" style="74" customWidth="1"/>
-    <col min="9732" max="9736" width="10" style="74" customWidth="1"/>
-    <col min="9737" max="9737" width="13.33203125" style="74" customWidth="1"/>
-    <col min="9738" max="9982" width="10" style="74" customWidth="1"/>
-    <col min="9983" max="9987" width="15.44140625" style="74" customWidth="1"/>
-    <col min="9988" max="9992" width="10" style="74" customWidth="1"/>
-    <col min="9993" max="9993" width="13.33203125" style="74" customWidth="1"/>
-    <col min="9994" max="10238" width="10" style="74" customWidth="1"/>
-    <col min="10239" max="10243" width="15.44140625" style="74" customWidth="1"/>
-    <col min="10244" max="10248" width="10" style="74" customWidth="1"/>
-    <col min="10249" max="10249" width="13.33203125" style="74" customWidth="1"/>
-    <col min="10250" max="10494" width="10" style="74" customWidth="1"/>
-    <col min="10495" max="10499" width="15.44140625" style="74" customWidth="1"/>
-    <col min="10500" max="10504" width="10" style="74" customWidth="1"/>
-    <col min="10505" max="10505" width="13.33203125" style="74" customWidth="1"/>
-    <col min="10506" max="10750" width="10" style="74" customWidth="1"/>
-    <col min="10751" max="10755" width="15.44140625" style="74" customWidth="1"/>
-    <col min="10756" max="10760" width="10" style="74" customWidth="1"/>
-    <col min="10761" max="10761" width="13.33203125" style="74" customWidth="1"/>
-    <col min="10762" max="11006" width="10" style="74" customWidth="1"/>
-    <col min="11007" max="11011" width="15.44140625" style="74" customWidth="1"/>
-    <col min="11012" max="11016" width="10" style="74" customWidth="1"/>
-    <col min="11017" max="11017" width="13.33203125" style="74" customWidth="1"/>
-    <col min="11018" max="11262" width="10" style="74" customWidth="1"/>
-    <col min="11263" max="11267" width="15.44140625" style="74" customWidth="1"/>
-    <col min="11268" max="11272" width="10" style="74" customWidth="1"/>
-    <col min="11273" max="11273" width="13.33203125" style="74" customWidth="1"/>
-    <col min="11274" max="11518" width="10" style="74" customWidth="1"/>
-    <col min="11519" max="11523" width="15.44140625" style="74" customWidth="1"/>
-    <col min="11524" max="11528" width="10" style="74" customWidth="1"/>
-    <col min="11529" max="11529" width="13.33203125" style="74" customWidth="1"/>
-    <col min="11530" max="11774" width="10" style="74" customWidth="1"/>
-    <col min="11775" max="11779" width="15.44140625" style="74" customWidth="1"/>
-    <col min="11780" max="11784" width="10" style="74" customWidth="1"/>
-    <col min="11785" max="11785" width="13.33203125" style="74" customWidth="1"/>
-    <col min="11786" max="12030" width="10" style="74" customWidth="1"/>
-    <col min="12031" max="12035" width="15.44140625" style="74" customWidth="1"/>
-    <col min="12036" max="12040" width="10" style="74" customWidth="1"/>
-    <col min="12041" max="12041" width="13.33203125" style="74" customWidth="1"/>
-    <col min="12042" max="12286" width="10" style="74" customWidth="1"/>
-    <col min="12287" max="12291" width="15.44140625" style="74" customWidth="1"/>
-    <col min="12292" max="12296" width="10" style="74" customWidth="1"/>
-    <col min="12297" max="12297" width="13.33203125" style="74" customWidth="1"/>
-    <col min="12298" max="12542" width="10" style="74" customWidth="1"/>
-    <col min="12543" max="12547" width="15.44140625" style="74" customWidth="1"/>
-    <col min="12548" max="12552" width="10" style="74" customWidth="1"/>
-    <col min="12553" max="12553" width="13.33203125" style="74" customWidth="1"/>
-    <col min="12554" max="12798" width="10" style="74" customWidth="1"/>
-    <col min="12799" max="12803" width="15.44140625" style="74" customWidth="1"/>
-    <col min="12804" max="12808" width="10" style="74" customWidth="1"/>
-    <col min="12809" max="12809" width="13.33203125" style="74" customWidth="1"/>
-    <col min="12810" max="13054" width="10" style="74" customWidth="1"/>
-    <col min="13055" max="13059" width="15.44140625" style="74" customWidth="1"/>
-    <col min="13060" max="13064" width="10" style="74" customWidth="1"/>
-    <col min="13065" max="13065" width="13.33203125" style="74" customWidth="1"/>
-    <col min="13066" max="13310" width="10" style="74" customWidth="1"/>
-    <col min="13311" max="13315" width="15.44140625" style="74" customWidth="1"/>
-    <col min="13316" max="13320" width="10" style="74" customWidth="1"/>
-    <col min="13321" max="13321" width="13.33203125" style="74" customWidth="1"/>
-    <col min="13322" max="13566" width="10" style="74" customWidth="1"/>
-    <col min="13567" max="13571" width="15.44140625" style="74" customWidth="1"/>
-    <col min="13572" max="13576" width="10" style="74" customWidth="1"/>
-    <col min="13577" max="13577" width="13.33203125" style="74" customWidth="1"/>
-    <col min="13578" max="13822" width="10" style="74" customWidth="1"/>
-    <col min="13823" max="13827" width="15.44140625" style="74" customWidth="1"/>
-    <col min="13828" max="13832" width="10" style="74" customWidth="1"/>
-    <col min="13833" max="13833" width="13.33203125" style="74" customWidth="1"/>
-    <col min="13834" max="14078" width="10" style="74" customWidth="1"/>
-    <col min="14079" max="14083" width="15.44140625" style="74" customWidth="1"/>
-    <col min="14084" max="14088" width="10" style="74" customWidth="1"/>
-    <col min="14089" max="14089" width="13.33203125" style="74" customWidth="1"/>
-    <col min="14090" max="14334" width="10" style="74" customWidth="1"/>
-    <col min="14335" max="14339" width="15.44140625" style="74" customWidth="1"/>
-    <col min="14340" max="14344" width="10" style="74" customWidth="1"/>
-    <col min="14345" max="14345" width="13.33203125" style="74" customWidth="1"/>
-    <col min="14346" max="14590" width="10" style="74" customWidth="1"/>
-    <col min="14591" max="14595" width="15.44140625" style="74" customWidth="1"/>
-    <col min="14596" max="14600" width="10" style="74" customWidth="1"/>
-    <col min="14601" max="14601" width="13.33203125" style="74" customWidth="1"/>
-    <col min="14602" max="14846" width="10" style="74" customWidth="1"/>
-    <col min="14847" max="14851" width="15.44140625" style="74" customWidth="1"/>
-    <col min="14852" max="14856" width="10" style="74" customWidth="1"/>
-    <col min="14857" max="14857" width="13.33203125" style="74" customWidth="1"/>
-    <col min="14858" max="15102" width="10" style="74" customWidth="1"/>
-    <col min="15103" max="15107" width="15.44140625" style="74" customWidth="1"/>
-    <col min="15108" max="15112" width="10" style="74" customWidth="1"/>
-    <col min="15113" max="15113" width="13.33203125" style="74" customWidth="1"/>
-    <col min="15114" max="15358" width="10" style="74" customWidth="1"/>
-    <col min="15359" max="15363" width="15.44140625" style="74" customWidth="1"/>
-    <col min="15364" max="15368" width="10" style="74" customWidth="1"/>
-    <col min="15369" max="15369" width="13.33203125" style="74" customWidth="1"/>
-    <col min="15370" max="15614" width="10" style="74" customWidth="1"/>
-    <col min="15615" max="15619" width="15.44140625" style="74" customWidth="1"/>
-    <col min="15620" max="15624" width="10" style="74" customWidth="1"/>
-    <col min="15625" max="15625" width="13.33203125" style="74" customWidth="1"/>
-    <col min="15626" max="15870" width="10" style="74" customWidth="1"/>
-    <col min="15871" max="15875" width="15.44140625" style="74" customWidth="1"/>
-    <col min="15876" max="15880" width="10" style="74" customWidth="1"/>
-    <col min="15881" max="15881" width="13.33203125" style="74" customWidth="1"/>
-    <col min="15882" max="16126" width="10" style="74" customWidth="1"/>
-    <col min="16127" max="16131" width="15.44140625" style="74" customWidth="1"/>
-    <col min="16132" max="16136" width="10" style="74" customWidth="1"/>
-    <col min="16137" max="16137" width="13.33203125" style="74" customWidth="1"/>
-    <col min="16138" max="16384" width="10" style="74" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="110"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-    </row>
-    <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="115" t="s">
-        <v>256</v>
-      </c>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="117"/>
-    </row>
-    <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
-      <c r="B11" s="75"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="75"/>
-      <c r="E11" s="75"/>
-    </row>
-    <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="76" t="s">
-        <v>257</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>258</v>
-      </c>
-      <c r="C12" s="76" t="s">
-        <v>259</v>
-      </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-    </row>
-    <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>261</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>262</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-    </row>
-    <row r="14" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-    </row>
-    <row r="15" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
-        <v>266</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-    </row>
-    <row r="16" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-    </row>
-    <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="120" t="s">
-        <v>269</v>
-      </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="117"/>
-    </row>
-    <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>271</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>281</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-    </row>
-    <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="120" t="s">
-        <v>285</v>
-      </c>
-      <c r="B23" s="116"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="117"/>
-    </row>
-    <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>271</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>289</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="73"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="123"/>
-      <c r="B30" s="77"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="119"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="119"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="119"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="119"/>
-      <c r="B34" s="77"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="77"/>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="77"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="77"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="73"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="73"/>
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="73"/>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="123"/>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="119"/>
-      <c r="B45" s="77"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="119"/>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="119"/>
-      <c r="B47" s="77"/>
-      <c r="C47" s="77"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="119"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="77"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="119"/>
-      <c r="B49" s="77"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="77"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="119"/>
-      <c r="B50" s="77"/>
-      <c r="C50" s="77"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="43"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="119"/>
-      <c r="B51" s="77"/>
-      <c r="C51" s="77"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="43"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="119"/>
-      <c r="B52" s="77"/>
-      <c r="C52" s="77"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="43"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="119"/>
-      <c r="B53" s="77"/>
-      <c r="C53" s="77"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="43"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="119"/>
-      <c r="B54" s="77"/>
-      <c r="C54" s="77"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="44"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="119"/>
-      <c r="B55" s="77"/>
-      <c r="C55" s="77"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="77"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="119"/>
-      <c r="B56" s="77"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="77"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="119"/>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="77"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="119"/>
-      <c r="B58" s="77"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="77"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="119"/>
-      <c r="B59" s="77"/>
-      <c r="C59" s="77"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="77"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="119"/>
-      <c r="B60" s="77"/>
-      <c r="C60" s="77"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="77"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="36" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="122" t="s">
-        <v>291</v>
-      </c>
-      <c r="B65" s="119"/>
-      <c r="C65" s="119"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="E30:E34"/>
-    <mergeCell ref="A44:A60"/>
-    <mergeCell ref="C30:C34"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="D30:D34"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A1:E3"/>
-    <mergeCell ref="A17:E17"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="66" customWidth="1"/>
-    <col min="11" max="11" width="7.44140625" style="66" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="46" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" style="46" customWidth="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7841,78 +6355,78 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="66" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="46" customWidth="1"/>
     <col min="2" max="2" width="60.21875" style="2" customWidth="1"/>
     <col min="3" max="3" width="24.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.77734375" style="66" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="66" customWidth="1"/>
-    <col min="8" max="8" width="35.33203125" style="66" customWidth="1"/>
+    <col min="4" max="4" width="41.77734375" style="46" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="35.33203125" style="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="63" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="69" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="90"/>
+      <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90"/>
+      <c r="D4" s="70"/>
     </row>
     <row r="5" spans="1:8" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="91"/>
+      <c r="D5" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7930,40 +6444,40 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" style="88" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" style="82" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" style="82" customWidth="1"/>
-    <col min="4" max="4" width="57.33203125" style="82" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="88" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="88" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" style="82" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" style="82" customWidth="1"/>
-    <col min="9" max="10" width="9" style="82" customWidth="1"/>
-    <col min="11" max="11" width="35.33203125" style="82" customWidth="1"/>
-    <col min="12" max="12" width="9" style="82" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="82"/>
+    <col min="1" max="1" width="15.88671875" style="68" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="62" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" style="62" customWidth="1"/>
+    <col min="4" max="4" width="57.33203125" style="62" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="68" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="68" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" style="62" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" style="62" customWidth="1"/>
+    <col min="9" max="10" width="9" style="62" customWidth="1"/>
+    <col min="11" max="11" width="35.33203125" style="62" customWidth="1"/>
+    <col min="12" max="12" width="9" style="62" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="62"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="87" t="s">
+      <c r="C1" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="87" t="s">
+      <c r="D1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="87" t="s">
+      <c r="E1" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="83" t="s">
+      <c r="G1" s="63" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7995,81 +6509,81 @@
   <dimension ref="A1:IM4"/>
   <sheetFormatPr defaultRowHeight="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="81" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="81" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="81" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="81" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" style="81" customWidth="1"/>
-    <col min="6" max="12" width="11.109375" style="81" customWidth="1"/>
-    <col min="13" max="13" width="12" style="81" customWidth="1"/>
-    <col min="14" max="14" width="44.44140625" style="81" customWidth="1"/>
-    <col min="15" max="247" width="30" style="81" customWidth="1"/>
-    <col min="248" max="16384" width="8.88671875" style="82"/>
+    <col min="1" max="1" width="15.33203125" style="61" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="61" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="61" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" style="61" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="61" customWidth="1"/>
+    <col min="6" max="12" width="11.109375" style="61" customWidth="1"/>
+    <col min="13" max="13" width="12" style="61" customWidth="1"/>
+    <col min="14" max="14" width="44.44140625" style="61" customWidth="1"/>
+    <col min="15" max="247" width="30" style="61" customWidth="1"/>
+    <col min="248" max="16384" width="8.88671875" style="62"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="92" t="s">
-        <v>303</v>
-      </c>
-      <c r="C1" s="92" t="s">
-        <v>306</v>
-      </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="93" t="s">
+      <c r="B1" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="81" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="79" t="s">
+    <row r="2" spans="1:14" s="61" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G2" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="79" t="s">
+      <c r="J2" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="80" t="s">
+      <c r="M2" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="93"/>
-    </row>
-    <row r="4" spans="1:14" s="81" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N2" s="73"/>
+    </row>
+    <row r="4" spans="1:14" s="61" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -8094,59 +6608,59 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.77734375" defaultRowHeight="29.4" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="21" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="22" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" style="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.77734375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="27.44140625" style="24" customWidth="1"/>
-    <col min="8" max="8" width="27.109375" style="24" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40" style="18" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.77734375" style="19" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" style="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-    </row>
-    <row r="2" spans="1:8" s="26" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+    </row>
+    <row r="2" spans="1:8" s="22" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="80" t="s">
+      <c r="G2" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="60" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="27" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:8" s="28" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:8" s="23" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:8" s="24" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:8" s="24" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:8" s="24" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:8" s="24" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -8165,119 +6679,119 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" style="59" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="59" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" style="60" customWidth="1"/>
-    <col min="5" max="7" width="30.5546875" style="61" customWidth="1"/>
-    <col min="8" max="8" width="13" style="59" customWidth="1"/>
-    <col min="9" max="9" width="34.21875" style="61" customWidth="1"/>
-    <col min="10" max="10" width="13" style="60" customWidth="1"/>
-    <col min="11" max="11" width="34.21875" style="61" customWidth="1"/>
-    <col min="12" max="12" width="13" style="60" customWidth="1"/>
-    <col min="13" max="13" width="11" style="60" customWidth="1"/>
-    <col min="14" max="14" width="34.21875" style="61" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" style="59" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="59" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.44140625" style="60" customWidth="1"/>
-    <col min="18" max="18" width="13" style="60" customWidth="1"/>
-    <col min="19" max="19" width="11.21875" style="59" customWidth="1"/>
-    <col min="20" max="20" width="16.109375" style="59" customWidth="1"/>
-    <col min="21" max="21" width="9" style="59" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="59"/>
+    <col min="1" max="1" width="13.77734375" style="39" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="39" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5546875" style="40" customWidth="1"/>
+    <col min="5" max="7" width="30.5546875" style="41" customWidth="1"/>
+    <col min="8" max="8" width="13" style="39" customWidth="1"/>
+    <col min="9" max="9" width="34.21875" style="41" customWidth="1"/>
+    <col min="10" max="10" width="13" style="40" customWidth="1"/>
+    <col min="11" max="11" width="34.21875" style="41" customWidth="1"/>
+    <col min="12" max="12" width="13" style="40" customWidth="1"/>
+    <col min="13" max="13" width="11" style="40" customWidth="1"/>
+    <col min="14" max="14" width="34.21875" style="41" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" style="39" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.44140625" style="40" customWidth="1"/>
+    <col min="18" max="18" width="13" style="40" customWidth="1"/>
+    <col min="19" max="19" width="11.21875" style="39" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" style="39" customWidth="1"/>
+    <col min="21" max="21" width="9" style="39" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="98" t="s">
-        <v>303</v>
-      </c>
-      <c r="C1" s="98" t="s">
-        <v>304</v>
-      </c>
-      <c r="D1" s="100" t="s">
+    <row r="1" spans="1:20" s="38" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="76" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="100" t="s">
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="92" t="s">
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="78" t="s">
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="38" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="77"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G2" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="79" t="s">
+      <c r="J2" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="M2" s="79" t="s">
+      <c r="M2" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="79" t="s">
+      <c r="N2" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="79" t="s">
+      <c r="O2" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="79" t="s">
+      <c r="P2" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="79" t="s">
+      <c r="Q2" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="78" t="s">
+      <c r="R2" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="78" t="s">
+      <c r="S2" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="92"/>
-    </row>
-    <row r="3" spans="1:20" s="58" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="T2" s="72"/>
+    </row>
+    <row r="3" spans="1:20" s="38" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="T1:T2"/>
@@ -8302,7 +6816,7 @@
   <dimension ref="A1:IT2"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.21875" style="25" customWidth="1"/>
+    <col min="1" max="2" width="20.21875" style="21" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" style="5" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" style="5" customWidth="1"/>
@@ -8315,56 +6829,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
-        <v>300</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103" t="s">
-        <v>299</v>
-      </c>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="104" t="s">
-        <v>298</v>
+      <c r="A1" s="83" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="B2" s="30" t="s">
+      <c r="A2" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="K2" s="104"/>
+      <c r="C2" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8380,3256 +6894,1079 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25.2" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.21875" style="57" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" style="57" customWidth="1"/>
-    <col min="3" max="3" width="75.44140625" style="57" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" style="57" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="57" customWidth="1"/>
-    <col min="6" max="6" width="9" style="57" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="57"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="105" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
-    </row>
-    <row r="2" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="8" customFormat="1" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-    </row>
-    <row r="4" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" s="7" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" spans="1:5" s="8" customFormat="1" ht="22.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-    </row>
-    <row r="20" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="10"/>
-    </row>
-    <row r="34" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="10"/>
-    </row>
-    <row r="35" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="10"/>
-    </row>
-    <row r="37" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="38" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="10"/>
-    </row>
-    <row r="39" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="10"/>
-    </row>
-    <row r="40" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="10"/>
-    </row>
-    <row r="41" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="10"/>
-    </row>
-    <row r="42" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E42" s="10"/>
-    </row>
-    <row r="43" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B43" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E43" s="10"/>
-    </row>
-    <row r="44" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E44" s="10"/>
-    </row>
-    <row r="45" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E45" s="10"/>
-    </row>
-    <row r="46" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B46" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="10"/>
-    </row>
-    <row r="47" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E47" s="10"/>
-    </row>
-    <row r="48" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B48" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E48" s="10"/>
-    </row>
-    <row r="49" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B49" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="10"/>
-    </row>
-    <row r="50" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E50" s="10"/>
-    </row>
-    <row r="51" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E51" s="10"/>
-    </row>
-    <row r="52" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" s="55" t="s">
-        <v>130</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E52" s="10"/>
-    </row>
-    <row r="53" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B53" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E53" s="10"/>
-    </row>
-    <row r="54" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E54" s="10"/>
-    </row>
-    <row r="55" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E55" s="10"/>
-    </row>
-    <row r="56" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E56" s="10"/>
-    </row>
-    <row r="57" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B57" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E57" s="10"/>
-    </row>
-    <row r="58" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" s="55" t="s">
-        <v>135</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E58" s="10"/>
-    </row>
-    <row r="59" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B59" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E59" s="10"/>
-    </row>
-    <row r="60" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B60" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C60" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E60" s="10"/>
-    </row>
-    <row r="61" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B61" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" s="10"/>
-    </row>
-    <row r="62" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B62" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E62" s="10"/>
-    </row>
-    <row r="63" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E63" s="10"/>
-    </row>
-    <row r="64" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B64" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C64" s="55" t="s">
-        <v>141</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E64" s="10"/>
-    </row>
-    <row r="65" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E65" s="10"/>
-    </row>
-    <row r="66" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="B66" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E66" s="10"/>
-    </row>
-    <row r="67" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="46"/>
-      <c r="B67" s="55"/>
-      <c r="C67" s="55"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-    </row>
-    <row r="68" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="B68" s="34"/>
-      <c r="C68" s="34"/>
-      <c r="D68" s="34"/>
-      <c r="E68" s="34"/>
-    </row>
-    <row r="69" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E69" s="10"/>
-    </row>
-    <row r="70" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E70" s="10"/>
-    </row>
-    <row r="71" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B71" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E71" s="10"/>
-    </row>
-    <row r="72" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B72" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E72" s="10"/>
-    </row>
-    <row r="73" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B73" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E73" s="10"/>
-    </row>
-    <row r="74" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B74" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E74" s="10"/>
-    </row>
-    <row r="75" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B75" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E75" s="10"/>
-    </row>
-    <row r="76" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E76" s="10"/>
-    </row>
-    <row r="77" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B77" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E77" s="10"/>
-    </row>
-    <row r="78" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B78" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E78" s="10"/>
-    </row>
-    <row r="79" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B79" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E79" s="10"/>
-    </row>
-    <row r="80" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B80" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E80" s="10"/>
-    </row>
-    <row r="81" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B81" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C81" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E81" s="10"/>
-    </row>
-    <row r="82" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C82" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E82" s="10"/>
-    </row>
-    <row r="83" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B83" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E83" s="10"/>
-    </row>
-    <row r="84" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B84" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E84" s="10"/>
-    </row>
-    <row r="85" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B85" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E85" s="10"/>
-    </row>
-    <row r="86" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B86" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E86" s="10"/>
-    </row>
-    <row r="87" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B87" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E87" s="10"/>
-    </row>
-    <row r="88" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B88" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C88" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E88" s="10"/>
-    </row>
-    <row r="89" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B89" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E89" s="10"/>
-    </row>
-    <row r="90" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B90" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E90" s="10"/>
-    </row>
-    <row r="91" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B91" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C91" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E91" s="10"/>
-    </row>
-    <row r="92" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B92" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E92" s="10"/>
-    </row>
-    <row r="93" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B93" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E93" s="10"/>
-    </row>
-    <row r="94" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B94" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E94" s="10"/>
-    </row>
-    <row r="95" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B95" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E95" s="10"/>
-    </row>
-    <row r="96" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B96" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E96" s="10"/>
-    </row>
-    <row r="97" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B97" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E97" s="10"/>
-    </row>
-    <row r="98" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B98" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E98" s="10"/>
-    </row>
-    <row r="99" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B99" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E99" s="10"/>
-    </row>
-    <row r="100" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B100" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E100" s="10"/>
-    </row>
-    <row r="101" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B101" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C101" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E101" s="10"/>
-    </row>
-    <row r="102" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B102" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E102" s="10"/>
-    </row>
-    <row r="103" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B103" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C103" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E103" s="10"/>
-    </row>
-    <row r="104" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B104" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C104" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E104" s="10"/>
-    </row>
-    <row r="105" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B105" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C105" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E105" s="10"/>
-    </row>
-    <row r="106" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B106" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C106" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E106" s="10"/>
-    </row>
-    <row r="107" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B107" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C107" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="D107" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E107" s="10"/>
-    </row>
-    <row r="108" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B108" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C108" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E108" s="10"/>
-    </row>
-    <row r="109" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B109" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C109" s="55" t="s">
-        <v>190</v>
-      </c>
-      <c r="D109" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E109" s="10"/>
-    </row>
-    <row r="110" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B110" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="C110" s="55" t="s">
-        <v>191</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E110" s="10"/>
-    </row>
-    <row r="111" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="B111" s="53" t="s">
-        <v>182</v>
-      </c>
-      <c r="C111" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E111" s="10"/>
-    </row>
-    <row r="112" spans="1:5" s="8" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="B112" s="34"/>
-      <c r="C112" s="34"/>
-      <c r="D112" s="34"/>
-      <c r="E112" s="34"/>
-    </row>
-    <row r="113" spans="1:5" s="7" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B113" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E113" s="10"/>
-    </row>
-    <row r="114" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B114" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C114" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B115" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C115" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="D115" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B116" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C116" s="55" t="s">
-        <v>201</v>
-      </c>
-      <c r="D116" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E116" s="10"/>
-    </row>
-    <row r="117" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B117" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="D117" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E117" s="10"/>
-    </row>
-    <row r="118" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B118" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E118" s="10"/>
-    </row>
-    <row r="119" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B119" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D119" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E119" s="10"/>
-    </row>
-    <row r="120" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B120" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E120" s="10"/>
-    </row>
-    <row r="121" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B121" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C121" s="55" t="s">
-        <v>206</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E121" s="10"/>
-    </row>
-    <row r="122" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B122" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C122" s="55" t="s">
-        <v>207</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E122" s="10"/>
-    </row>
-    <row r="123" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C123" s="55" t="s">
-        <v>208</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E123" s="10"/>
-    </row>
-    <row r="124" spans="1:5" s="7" customFormat="1" ht="45.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B124" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E124" s="10"/>
-    </row>
-    <row r="125" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B125" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C125" s="55" t="s">
-        <v>211</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E125" s="10"/>
-    </row>
-    <row r="126" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B126" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C126" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="D126" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E126" s="10"/>
-    </row>
-    <row r="127" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B127" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C127" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E127" s="10"/>
-    </row>
-    <row r="128" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B128" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C128" s="49" t="s">
-        <v>214</v>
-      </c>
-      <c r="D128" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B129" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C129" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B130" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E130" s="10"/>
-    </row>
-    <row r="131" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B131" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C131" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="D131" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E131" s="10"/>
-    </row>
-    <row r="132" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B132" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C132" s="49" t="s">
-        <v>219</v>
-      </c>
-      <c r="D132" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E132" s="10"/>
-    </row>
-    <row r="133" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B133" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C133" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E133" s="10"/>
-    </row>
-    <row r="134" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B134" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C134" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="D134" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E134" s="10"/>
-    </row>
-    <row r="135" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B135" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C135" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E135" s="10"/>
-    </row>
-    <row r="136" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B136" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C136" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E136" s="10"/>
-    </row>
-    <row r="137" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B137" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C137" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E137" s="10"/>
-    </row>
-    <row r="138" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B138" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="C138" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="D138" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E138" s="10"/>
-    </row>
-    <row r="139" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B139" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C139" s="55" t="s">
-        <v>226</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E139" s="10"/>
-    </row>
-    <row r="140" spans="1:5" s="7" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C140" s="55" t="s">
-        <v>227</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E140" s="10"/>
-    </row>
-    <row r="141" spans="1:5" s="7" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B141" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="D141" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E141" s="10"/>
-    </row>
-    <row r="142" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B142" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C142" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E142" s="10"/>
-    </row>
-    <row r="143" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B143" s="47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C143" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D143" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E143" s="56"/>
-    </row>
-    <row r="144" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B144" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C144" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="D144" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E144" s="56"/>
-    </row>
-    <row r="145" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="53" t="s">
-        <v>193</v>
-      </c>
-      <c r="B145" s="54" t="s">
-        <v>200</v>
-      </c>
-      <c r="C145" s="55" t="s">
-        <v>232</v>
-      </c>
-      <c r="D145" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E145" s="56"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L136"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="70" customWidth="1"/>
-    <col min="2" max="5" width="20.6640625" style="70" customWidth="1"/>
-    <col min="6" max="8" width="10" style="70" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" style="70" customWidth="1"/>
-    <col min="10" max="254" width="10" style="70" customWidth="1"/>
-    <col min="255" max="259" width="15.44140625" style="70" customWidth="1"/>
-    <col min="260" max="264" width="10" style="70" customWidth="1"/>
-    <col min="265" max="265" width="13.33203125" style="70" customWidth="1"/>
-    <col min="266" max="510" width="10" style="70" customWidth="1"/>
-    <col min="511" max="515" width="15.44140625" style="70" customWidth="1"/>
-    <col min="516" max="520" width="10" style="70" customWidth="1"/>
-    <col min="521" max="521" width="13.33203125" style="70" customWidth="1"/>
-    <col min="522" max="766" width="10" style="70" customWidth="1"/>
-    <col min="767" max="771" width="15.44140625" style="70" customWidth="1"/>
-    <col min="772" max="776" width="10" style="70" customWidth="1"/>
-    <col min="777" max="777" width="13.33203125" style="70" customWidth="1"/>
-    <col min="778" max="1022" width="10" style="70" customWidth="1"/>
-    <col min="1023" max="1027" width="15.44140625" style="70" customWidth="1"/>
-    <col min="1028" max="1032" width="10" style="70" customWidth="1"/>
-    <col min="1033" max="1033" width="13.33203125" style="70" customWidth="1"/>
-    <col min="1034" max="1278" width="10" style="70" customWidth="1"/>
-    <col min="1279" max="1283" width="15.44140625" style="70" customWidth="1"/>
-    <col min="1284" max="1288" width="10" style="70" customWidth="1"/>
-    <col min="1289" max="1289" width="13.33203125" style="70" customWidth="1"/>
-    <col min="1290" max="1534" width="10" style="70" customWidth="1"/>
-    <col min="1535" max="1539" width="15.44140625" style="70" customWidth="1"/>
-    <col min="1540" max="1544" width="10" style="70" customWidth="1"/>
-    <col min="1545" max="1545" width="13.33203125" style="70" customWidth="1"/>
-    <col min="1546" max="1790" width="10" style="70" customWidth="1"/>
-    <col min="1791" max="1795" width="15.44140625" style="70" customWidth="1"/>
-    <col min="1796" max="1800" width="10" style="70" customWidth="1"/>
-    <col min="1801" max="1801" width="13.33203125" style="70" customWidth="1"/>
-    <col min="1802" max="2046" width="10" style="70" customWidth="1"/>
-    <col min="2047" max="2051" width="15.44140625" style="70" customWidth="1"/>
-    <col min="2052" max="2056" width="10" style="70" customWidth="1"/>
-    <col min="2057" max="2057" width="13.33203125" style="70" customWidth="1"/>
-    <col min="2058" max="2302" width="10" style="70" customWidth="1"/>
-    <col min="2303" max="2307" width="15.44140625" style="70" customWidth="1"/>
-    <col min="2308" max="2312" width="10" style="70" customWidth="1"/>
-    <col min="2313" max="2313" width="13.33203125" style="70" customWidth="1"/>
-    <col min="2314" max="2558" width="10" style="70" customWidth="1"/>
-    <col min="2559" max="2563" width="15.44140625" style="70" customWidth="1"/>
-    <col min="2564" max="2568" width="10" style="70" customWidth="1"/>
-    <col min="2569" max="2569" width="13.33203125" style="70" customWidth="1"/>
-    <col min="2570" max="2814" width="10" style="70" customWidth="1"/>
-    <col min="2815" max="2819" width="15.44140625" style="70" customWidth="1"/>
-    <col min="2820" max="2824" width="10" style="70" customWidth="1"/>
-    <col min="2825" max="2825" width="13.33203125" style="70" customWidth="1"/>
-    <col min="2826" max="3070" width="10" style="70" customWidth="1"/>
-    <col min="3071" max="3075" width="15.44140625" style="70" customWidth="1"/>
-    <col min="3076" max="3080" width="10" style="70" customWidth="1"/>
-    <col min="3081" max="3081" width="13.33203125" style="70" customWidth="1"/>
-    <col min="3082" max="3326" width="10" style="70" customWidth="1"/>
-    <col min="3327" max="3331" width="15.44140625" style="70" customWidth="1"/>
-    <col min="3332" max="3336" width="10" style="70" customWidth="1"/>
-    <col min="3337" max="3337" width="13.33203125" style="70" customWidth="1"/>
-    <col min="3338" max="3582" width="10" style="70" customWidth="1"/>
-    <col min="3583" max="3587" width="15.44140625" style="70" customWidth="1"/>
-    <col min="3588" max="3592" width="10" style="70" customWidth="1"/>
-    <col min="3593" max="3593" width="13.33203125" style="70" customWidth="1"/>
-    <col min="3594" max="3838" width="10" style="70" customWidth="1"/>
-    <col min="3839" max="3843" width="15.44140625" style="70" customWidth="1"/>
-    <col min="3844" max="3848" width="10" style="70" customWidth="1"/>
-    <col min="3849" max="3849" width="13.33203125" style="70" customWidth="1"/>
-    <col min="3850" max="4094" width="10" style="70" customWidth="1"/>
-    <col min="4095" max="4099" width="15.44140625" style="70" customWidth="1"/>
-    <col min="4100" max="4104" width="10" style="70" customWidth="1"/>
-    <col min="4105" max="4105" width="13.33203125" style="70" customWidth="1"/>
-    <col min="4106" max="4350" width="10" style="70" customWidth="1"/>
-    <col min="4351" max="4355" width="15.44140625" style="70" customWidth="1"/>
-    <col min="4356" max="4360" width="10" style="70" customWidth="1"/>
-    <col min="4361" max="4361" width="13.33203125" style="70" customWidth="1"/>
-    <col min="4362" max="4606" width="10" style="70" customWidth="1"/>
-    <col min="4607" max="4611" width="15.44140625" style="70" customWidth="1"/>
-    <col min="4612" max="4616" width="10" style="70" customWidth="1"/>
-    <col min="4617" max="4617" width="13.33203125" style="70" customWidth="1"/>
-    <col min="4618" max="4862" width="10" style="70" customWidth="1"/>
-    <col min="4863" max="4867" width="15.44140625" style="70" customWidth="1"/>
-    <col min="4868" max="4872" width="10" style="70" customWidth="1"/>
-    <col min="4873" max="4873" width="13.33203125" style="70" customWidth="1"/>
-    <col min="4874" max="5118" width="10" style="70" customWidth="1"/>
-    <col min="5119" max="5123" width="15.44140625" style="70" customWidth="1"/>
-    <col min="5124" max="5128" width="10" style="70" customWidth="1"/>
-    <col min="5129" max="5129" width="13.33203125" style="70" customWidth="1"/>
-    <col min="5130" max="5374" width="10" style="70" customWidth="1"/>
-    <col min="5375" max="5379" width="15.44140625" style="70" customWidth="1"/>
-    <col min="5380" max="5384" width="10" style="70" customWidth="1"/>
-    <col min="5385" max="5385" width="13.33203125" style="70" customWidth="1"/>
-    <col min="5386" max="5630" width="10" style="70" customWidth="1"/>
-    <col min="5631" max="5635" width="15.44140625" style="70" customWidth="1"/>
-    <col min="5636" max="5640" width="10" style="70" customWidth="1"/>
-    <col min="5641" max="5641" width="13.33203125" style="70" customWidth="1"/>
-    <col min="5642" max="5886" width="10" style="70" customWidth="1"/>
-    <col min="5887" max="5891" width="15.44140625" style="70" customWidth="1"/>
-    <col min="5892" max="5896" width="10" style="70" customWidth="1"/>
-    <col min="5897" max="5897" width="13.33203125" style="70" customWidth="1"/>
-    <col min="5898" max="6142" width="10" style="70" customWidth="1"/>
-    <col min="6143" max="6147" width="15.44140625" style="70" customWidth="1"/>
-    <col min="6148" max="6152" width="10" style="70" customWidth="1"/>
-    <col min="6153" max="6153" width="13.33203125" style="70" customWidth="1"/>
-    <col min="6154" max="6398" width="10" style="70" customWidth="1"/>
-    <col min="6399" max="6403" width="15.44140625" style="70" customWidth="1"/>
-    <col min="6404" max="6408" width="10" style="70" customWidth="1"/>
-    <col min="6409" max="6409" width="13.33203125" style="70" customWidth="1"/>
-    <col min="6410" max="6654" width="10" style="70" customWidth="1"/>
-    <col min="6655" max="6659" width="15.44140625" style="70" customWidth="1"/>
-    <col min="6660" max="6664" width="10" style="70" customWidth="1"/>
-    <col min="6665" max="6665" width="13.33203125" style="70" customWidth="1"/>
-    <col min="6666" max="6910" width="10" style="70" customWidth="1"/>
-    <col min="6911" max="6915" width="15.44140625" style="70" customWidth="1"/>
-    <col min="6916" max="6920" width="10" style="70" customWidth="1"/>
-    <col min="6921" max="6921" width="13.33203125" style="70" customWidth="1"/>
-    <col min="6922" max="7166" width="10" style="70" customWidth="1"/>
-    <col min="7167" max="7171" width="15.44140625" style="70" customWidth="1"/>
-    <col min="7172" max="7176" width="10" style="70" customWidth="1"/>
-    <col min="7177" max="7177" width="13.33203125" style="70" customWidth="1"/>
-    <col min="7178" max="7422" width="10" style="70" customWidth="1"/>
-    <col min="7423" max="7427" width="15.44140625" style="70" customWidth="1"/>
-    <col min="7428" max="7432" width="10" style="70" customWidth="1"/>
-    <col min="7433" max="7433" width="13.33203125" style="70" customWidth="1"/>
-    <col min="7434" max="7678" width="10" style="70" customWidth="1"/>
-    <col min="7679" max="7683" width="15.44140625" style="70" customWidth="1"/>
-    <col min="7684" max="7688" width="10" style="70" customWidth="1"/>
-    <col min="7689" max="7689" width="13.33203125" style="70" customWidth="1"/>
-    <col min="7690" max="7934" width="10" style="70" customWidth="1"/>
-    <col min="7935" max="7939" width="15.44140625" style="70" customWidth="1"/>
-    <col min="7940" max="7944" width="10" style="70" customWidth="1"/>
-    <col min="7945" max="7945" width="13.33203125" style="70" customWidth="1"/>
-    <col min="7946" max="8190" width="10" style="70" customWidth="1"/>
-    <col min="8191" max="8195" width="15.44140625" style="70" customWidth="1"/>
-    <col min="8196" max="8200" width="10" style="70" customWidth="1"/>
-    <col min="8201" max="8201" width="13.33203125" style="70" customWidth="1"/>
-    <col min="8202" max="8446" width="10" style="70" customWidth="1"/>
-    <col min="8447" max="8451" width="15.44140625" style="70" customWidth="1"/>
-    <col min="8452" max="8456" width="10" style="70" customWidth="1"/>
-    <col min="8457" max="8457" width="13.33203125" style="70" customWidth="1"/>
-    <col min="8458" max="8702" width="10" style="70" customWidth="1"/>
-    <col min="8703" max="8707" width="15.44140625" style="70" customWidth="1"/>
-    <col min="8708" max="8712" width="10" style="70" customWidth="1"/>
-    <col min="8713" max="8713" width="13.33203125" style="70" customWidth="1"/>
-    <col min="8714" max="8958" width="10" style="70" customWidth="1"/>
-    <col min="8959" max="8963" width="15.44140625" style="70" customWidth="1"/>
-    <col min="8964" max="8968" width="10" style="70" customWidth="1"/>
-    <col min="8969" max="8969" width="13.33203125" style="70" customWidth="1"/>
-    <col min="8970" max="9214" width="10" style="70" customWidth="1"/>
-    <col min="9215" max="9219" width="15.44140625" style="70" customWidth="1"/>
-    <col min="9220" max="9224" width="10" style="70" customWidth="1"/>
-    <col min="9225" max="9225" width="13.33203125" style="70" customWidth="1"/>
-    <col min="9226" max="9470" width="10" style="70" customWidth="1"/>
-    <col min="9471" max="9475" width="15.44140625" style="70" customWidth="1"/>
-    <col min="9476" max="9480" width="10" style="70" customWidth="1"/>
-    <col min="9481" max="9481" width="13.33203125" style="70" customWidth="1"/>
-    <col min="9482" max="9726" width="10" style="70" customWidth="1"/>
-    <col min="9727" max="9731" width="15.44140625" style="70" customWidth="1"/>
-    <col min="9732" max="9736" width="10" style="70" customWidth="1"/>
-    <col min="9737" max="9737" width="13.33203125" style="70" customWidth="1"/>
-    <col min="9738" max="9982" width="10" style="70" customWidth="1"/>
-    <col min="9983" max="9987" width="15.44140625" style="70" customWidth="1"/>
-    <col min="9988" max="9992" width="10" style="70" customWidth="1"/>
-    <col min="9993" max="9993" width="13.33203125" style="70" customWidth="1"/>
-    <col min="9994" max="10238" width="10" style="70" customWidth="1"/>
-    <col min="10239" max="10243" width="15.44140625" style="70" customWidth="1"/>
-    <col min="10244" max="10248" width="10" style="70" customWidth="1"/>
-    <col min="10249" max="10249" width="13.33203125" style="70" customWidth="1"/>
-    <col min="10250" max="10494" width="10" style="70" customWidth="1"/>
-    <col min="10495" max="10499" width="15.44140625" style="70" customWidth="1"/>
-    <col min="10500" max="10504" width="10" style="70" customWidth="1"/>
-    <col min="10505" max="10505" width="13.33203125" style="70" customWidth="1"/>
-    <col min="10506" max="10750" width="10" style="70" customWidth="1"/>
-    <col min="10751" max="10755" width="15.44140625" style="70" customWidth="1"/>
-    <col min="10756" max="10760" width="10" style="70" customWidth="1"/>
-    <col min="10761" max="10761" width="13.33203125" style="70" customWidth="1"/>
-    <col min="10762" max="11006" width="10" style="70" customWidth="1"/>
-    <col min="11007" max="11011" width="15.44140625" style="70" customWidth="1"/>
-    <col min="11012" max="11016" width="10" style="70" customWidth="1"/>
-    <col min="11017" max="11017" width="13.33203125" style="70" customWidth="1"/>
-    <col min="11018" max="11262" width="10" style="70" customWidth="1"/>
-    <col min="11263" max="11267" width="15.44140625" style="70" customWidth="1"/>
-    <col min="11268" max="11272" width="10" style="70" customWidth="1"/>
-    <col min="11273" max="11273" width="13.33203125" style="70" customWidth="1"/>
-    <col min="11274" max="11518" width="10" style="70" customWidth="1"/>
-    <col min="11519" max="11523" width="15.44140625" style="70" customWidth="1"/>
-    <col min="11524" max="11528" width="10" style="70" customWidth="1"/>
-    <col min="11529" max="11529" width="13.33203125" style="70" customWidth="1"/>
-    <col min="11530" max="11774" width="10" style="70" customWidth="1"/>
-    <col min="11775" max="11779" width="15.44140625" style="70" customWidth="1"/>
-    <col min="11780" max="11784" width="10" style="70" customWidth="1"/>
-    <col min="11785" max="11785" width="13.33203125" style="70" customWidth="1"/>
-    <col min="11786" max="12030" width="10" style="70" customWidth="1"/>
-    <col min="12031" max="12035" width="15.44140625" style="70" customWidth="1"/>
-    <col min="12036" max="12040" width="10" style="70" customWidth="1"/>
-    <col min="12041" max="12041" width="13.33203125" style="70" customWidth="1"/>
-    <col min="12042" max="12286" width="10" style="70" customWidth="1"/>
-    <col min="12287" max="12291" width="15.44140625" style="70" customWidth="1"/>
-    <col min="12292" max="12296" width="10" style="70" customWidth="1"/>
-    <col min="12297" max="12297" width="13.33203125" style="70" customWidth="1"/>
-    <col min="12298" max="12542" width="10" style="70" customWidth="1"/>
-    <col min="12543" max="12547" width="15.44140625" style="70" customWidth="1"/>
-    <col min="12548" max="12552" width="10" style="70" customWidth="1"/>
-    <col min="12553" max="12553" width="13.33203125" style="70" customWidth="1"/>
-    <col min="12554" max="12798" width="10" style="70" customWidth="1"/>
-    <col min="12799" max="12803" width="15.44140625" style="70" customWidth="1"/>
-    <col min="12804" max="12808" width="10" style="70" customWidth="1"/>
-    <col min="12809" max="12809" width="13.33203125" style="70" customWidth="1"/>
-    <col min="12810" max="13054" width="10" style="70" customWidth="1"/>
-    <col min="13055" max="13059" width="15.44140625" style="70" customWidth="1"/>
-    <col min="13060" max="13064" width="10" style="70" customWidth="1"/>
-    <col min="13065" max="13065" width="13.33203125" style="70" customWidth="1"/>
-    <col min="13066" max="13310" width="10" style="70" customWidth="1"/>
-    <col min="13311" max="13315" width="15.44140625" style="70" customWidth="1"/>
-    <col min="13316" max="13320" width="10" style="70" customWidth="1"/>
-    <col min="13321" max="13321" width="13.33203125" style="70" customWidth="1"/>
-    <col min="13322" max="13566" width="10" style="70" customWidth="1"/>
-    <col min="13567" max="13571" width="15.44140625" style="70" customWidth="1"/>
-    <col min="13572" max="13576" width="10" style="70" customWidth="1"/>
-    <col min="13577" max="13577" width="13.33203125" style="70" customWidth="1"/>
-    <col min="13578" max="13822" width="10" style="70" customWidth="1"/>
-    <col min="13823" max="13827" width="15.44140625" style="70" customWidth="1"/>
-    <col min="13828" max="13832" width="10" style="70" customWidth="1"/>
-    <col min="13833" max="13833" width="13.33203125" style="70" customWidth="1"/>
-    <col min="13834" max="14078" width="10" style="70" customWidth="1"/>
-    <col min="14079" max="14083" width="15.44140625" style="70" customWidth="1"/>
-    <col min="14084" max="14088" width="10" style="70" customWidth="1"/>
-    <col min="14089" max="14089" width="13.33203125" style="70" customWidth="1"/>
-    <col min="14090" max="14334" width="10" style="70" customWidth="1"/>
-    <col min="14335" max="14339" width="15.44140625" style="70" customWidth="1"/>
-    <col min="14340" max="14344" width="10" style="70" customWidth="1"/>
-    <col min="14345" max="14345" width="13.33203125" style="70" customWidth="1"/>
-    <col min="14346" max="14590" width="10" style="70" customWidth="1"/>
-    <col min="14591" max="14595" width="15.44140625" style="70" customWidth="1"/>
-    <col min="14596" max="14600" width="10" style="70" customWidth="1"/>
-    <col min="14601" max="14601" width="13.33203125" style="70" customWidth="1"/>
-    <col min="14602" max="14846" width="10" style="70" customWidth="1"/>
-    <col min="14847" max="14851" width="15.44140625" style="70" customWidth="1"/>
-    <col min="14852" max="14856" width="10" style="70" customWidth="1"/>
-    <col min="14857" max="14857" width="13.33203125" style="70" customWidth="1"/>
-    <col min="14858" max="15102" width="10" style="70" customWidth="1"/>
-    <col min="15103" max="15107" width="15.44140625" style="70" customWidth="1"/>
-    <col min="15108" max="15112" width="10" style="70" customWidth="1"/>
-    <col min="15113" max="15113" width="13.33203125" style="70" customWidth="1"/>
-    <col min="15114" max="15358" width="10" style="70" customWidth="1"/>
-    <col min="15359" max="15363" width="15.44140625" style="70" customWidth="1"/>
-    <col min="15364" max="15368" width="10" style="70" customWidth="1"/>
-    <col min="15369" max="15369" width="13.33203125" style="70" customWidth="1"/>
-    <col min="15370" max="15614" width="10" style="70" customWidth="1"/>
-    <col min="15615" max="15619" width="15.44140625" style="70" customWidth="1"/>
-    <col min="15620" max="15624" width="10" style="70" customWidth="1"/>
-    <col min="15625" max="15625" width="13.33203125" style="70" customWidth="1"/>
-    <col min="15626" max="15870" width="10" style="70" customWidth="1"/>
-    <col min="15871" max="15875" width="15.44140625" style="70" customWidth="1"/>
-    <col min="15876" max="15880" width="10" style="70" customWidth="1"/>
-    <col min="15881" max="15881" width="13.33203125" style="70" customWidth="1"/>
-    <col min="15882" max="16126" width="10" style="70" customWidth="1"/>
-    <col min="16127" max="16131" width="15.44140625" style="70" customWidth="1"/>
-    <col min="16132" max="16136" width="10" style="70" customWidth="1"/>
-    <col min="16137" max="16137" width="13.33203125" style="70" customWidth="1"/>
-    <col min="16138" max="16384" width="10" style="70" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="50" customWidth="1"/>
+    <col min="2" max="5" width="20.6640625" style="50" customWidth="1"/>
+    <col min="6" max="8" width="10" style="50" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" style="50" customWidth="1"/>
+    <col min="10" max="254" width="10" style="50" customWidth="1"/>
+    <col min="255" max="259" width="15.44140625" style="50" customWidth="1"/>
+    <col min="260" max="264" width="10" style="50" customWidth="1"/>
+    <col min="265" max="265" width="13.33203125" style="50" customWidth="1"/>
+    <col min="266" max="510" width="10" style="50" customWidth="1"/>
+    <col min="511" max="515" width="15.44140625" style="50" customWidth="1"/>
+    <col min="516" max="520" width="10" style="50" customWidth="1"/>
+    <col min="521" max="521" width="13.33203125" style="50" customWidth="1"/>
+    <col min="522" max="766" width="10" style="50" customWidth="1"/>
+    <col min="767" max="771" width="15.44140625" style="50" customWidth="1"/>
+    <col min="772" max="776" width="10" style="50" customWidth="1"/>
+    <col min="777" max="777" width="13.33203125" style="50" customWidth="1"/>
+    <col min="778" max="1022" width="10" style="50" customWidth="1"/>
+    <col min="1023" max="1027" width="15.44140625" style="50" customWidth="1"/>
+    <col min="1028" max="1032" width="10" style="50" customWidth="1"/>
+    <col min="1033" max="1033" width="13.33203125" style="50" customWidth="1"/>
+    <col min="1034" max="1278" width="10" style="50" customWidth="1"/>
+    <col min="1279" max="1283" width="15.44140625" style="50" customWidth="1"/>
+    <col min="1284" max="1288" width="10" style="50" customWidth="1"/>
+    <col min="1289" max="1289" width="13.33203125" style="50" customWidth="1"/>
+    <col min="1290" max="1534" width="10" style="50" customWidth="1"/>
+    <col min="1535" max="1539" width="15.44140625" style="50" customWidth="1"/>
+    <col min="1540" max="1544" width="10" style="50" customWidth="1"/>
+    <col min="1545" max="1545" width="13.33203125" style="50" customWidth="1"/>
+    <col min="1546" max="1790" width="10" style="50" customWidth="1"/>
+    <col min="1791" max="1795" width="15.44140625" style="50" customWidth="1"/>
+    <col min="1796" max="1800" width="10" style="50" customWidth="1"/>
+    <col min="1801" max="1801" width="13.33203125" style="50" customWidth="1"/>
+    <col min="1802" max="2046" width="10" style="50" customWidth="1"/>
+    <col min="2047" max="2051" width="15.44140625" style="50" customWidth="1"/>
+    <col min="2052" max="2056" width="10" style="50" customWidth="1"/>
+    <col min="2057" max="2057" width="13.33203125" style="50" customWidth="1"/>
+    <col min="2058" max="2302" width="10" style="50" customWidth="1"/>
+    <col min="2303" max="2307" width="15.44140625" style="50" customWidth="1"/>
+    <col min="2308" max="2312" width="10" style="50" customWidth="1"/>
+    <col min="2313" max="2313" width="13.33203125" style="50" customWidth="1"/>
+    <col min="2314" max="2558" width="10" style="50" customWidth="1"/>
+    <col min="2559" max="2563" width="15.44140625" style="50" customWidth="1"/>
+    <col min="2564" max="2568" width="10" style="50" customWidth="1"/>
+    <col min="2569" max="2569" width="13.33203125" style="50" customWidth="1"/>
+    <col min="2570" max="2814" width="10" style="50" customWidth="1"/>
+    <col min="2815" max="2819" width="15.44140625" style="50" customWidth="1"/>
+    <col min="2820" max="2824" width="10" style="50" customWidth="1"/>
+    <col min="2825" max="2825" width="13.33203125" style="50" customWidth="1"/>
+    <col min="2826" max="3070" width="10" style="50" customWidth="1"/>
+    <col min="3071" max="3075" width="15.44140625" style="50" customWidth="1"/>
+    <col min="3076" max="3080" width="10" style="50" customWidth="1"/>
+    <col min="3081" max="3081" width="13.33203125" style="50" customWidth="1"/>
+    <col min="3082" max="3326" width="10" style="50" customWidth="1"/>
+    <col min="3327" max="3331" width="15.44140625" style="50" customWidth="1"/>
+    <col min="3332" max="3336" width="10" style="50" customWidth="1"/>
+    <col min="3337" max="3337" width="13.33203125" style="50" customWidth="1"/>
+    <col min="3338" max="3582" width="10" style="50" customWidth="1"/>
+    <col min="3583" max="3587" width="15.44140625" style="50" customWidth="1"/>
+    <col min="3588" max="3592" width="10" style="50" customWidth="1"/>
+    <col min="3593" max="3593" width="13.33203125" style="50" customWidth="1"/>
+    <col min="3594" max="3838" width="10" style="50" customWidth="1"/>
+    <col min="3839" max="3843" width="15.44140625" style="50" customWidth="1"/>
+    <col min="3844" max="3848" width="10" style="50" customWidth="1"/>
+    <col min="3849" max="3849" width="13.33203125" style="50" customWidth="1"/>
+    <col min="3850" max="4094" width="10" style="50" customWidth="1"/>
+    <col min="4095" max="4099" width="15.44140625" style="50" customWidth="1"/>
+    <col min="4100" max="4104" width="10" style="50" customWidth="1"/>
+    <col min="4105" max="4105" width="13.33203125" style="50" customWidth="1"/>
+    <col min="4106" max="4350" width="10" style="50" customWidth="1"/>
+    <col min="4351" max="4355" width="15.44140625" style="50" customWidth="1"/>
+    <col min="4356" max="4360" width="10" style="50" customWidth="1"/>
+    <col min="4361" max="4361" width="13.33203125" style="50" customWidth="1"/>
+    <col min="4362" max="4606" width="10" style="50" customWidth="1"/>
+    <col min="4607" max="4611" width="15.44140625" style="50" customWidth="1"/>
+    <col min="4612" max="4616" width="10" style="50" customWidth="1"/>
+    <col min="4617" max="4617" width="13.33203125" style="50" customWidth="1"/>
+    <col min="4618" max="4862" width="10" style="50" customWidth="1"/>
+    <col min="4863" max="4867" width="15.44140625" style="50" customWidth="1"/>
+    <col min="4868" max="4872" width="10" style="50" customWidth="1"/>
+    <col min="4873" max="4873" width="13.33203125" style="50" customWidth="1"/>
+    <col min="4874" max="5118" width="10" style="50" customWidth="1"/>
+    <col min="5119" max="5123" width="15.44140625" style="50" customWidth="1"/>
+    <col min="5124" max="5128" width="10" style="50" customWidth="1"/>
+    <col min="5129" max="5129" width="13.33203125" style="50" customWidth="1"/>
+    <col min="5130" max="5374" width="10" style="50" customWidth="1"/>
+    <col min="5375" max="5379" width="15.44140625" style="50" customWidth="1"/>
+    <col min="5380" max="5384" width="10" style="50" customWidth="1"/>
+    <col min="5385" max="5385" width="13.33203125" style="50" customWidth="1"/>
+    <col min="5386" max="5630" width="10" style="50" customWidth="1"/>
+    <col min="5631" max="5635" width="15.44140625" style="50" customWidth="1"/>
+    <col min="5636" max="5640" width="10" style="50" customWidth="1"/>
+    <col min="5641" max="5641" width="13.33203125" style="50" customWidth="1"/>
+    <col min="5642" max="5886" width="10" style="50" customWidth="1"/>
+    <col min="5887" max="5891" width="15.44140625" style="50" customWidth="1"/>
+    <col min="5892" max="5896" width="10" style="50" customWidth="1"/>
+    <col min="5897" max="5897" width="13.33203125" style="50" customWidth="1"/>
+    <col min="5898" max="6142" width="10" style="50" customWidth="1"/>
+    <col min="6143" max="6147" width="15.44140625" style="50" customWidth="1"/>
+    <col min="6148" max="6152" width="10" style="50" customWidth="1"/>
+    <col min="6153" max="6153" width="13.33203125" style="50" customWidth="1"/>
+    <col min="6154" max="6398" width="10" style="50" customWidth="1"/>
+    <col min="6399" max="6403" width="15.44140625" style="50" customWidth="1"/>
+    <col min="6404" max="6408" width="10" style="50" customWidth="1"/>
+    <col min="6409" max="6409" width="13.33203125" style="50" customWidth="1"/>
+    <col min="6410" max="6654" width="10" style="50" customWidth="1"/>
+    <col min="6655" max="6659" width="15.44140625" style="50" customWidth="1"/>
+    <col min="6660" max="6664" width="10" style="50" customWidth="1"/>
+    <col min="6665" max="6665" width="13.33203125" style="50" customWidth="1"/>
+    <col min="6666" max="6910" width="10" style="50" customWidth="1"/>
+    <col min="6911" max="6915" width="15.44140625" style="50" customWidth="1"/>
+    <col min="6916" max="6920" width="10" style="50" customWidth="1"/>
+    <col min="6921" max="6921" width="13.33203125" style="50" customWidth="1"/>
+    <col min="6922" max="7166" width="10" style="50" customWidth="1"/>
+    <col min="7167" max="7171" width="15.44140625" style="50" customWidth="1"/>
+    <col min="7172" max="7176" width="10" style="50" customWidth="1"/>
+    <col min="7177" max="7177" width="13.33203125" style="50" customWidth="1"/>
+    <col min="7178" max="7422" width="10" style="50" customWidth="1"/>
+    <col min="7423" max="7427" width="15.44140625" style="50" customWidth="1"/>
+    <col min="7428" max="7432" width="10" style="50" customWidth="1"/>
+    <col min="7433" max="7433" width="13.33203125" style="50" customWidth="1"/>
+    <col min="7434" max="7678" width="10" style="50" customWidth="1"/>
+    <col min="7679" max="7683" width="15.44140625" style="50" customWidth="1"/>
+    <col min="7684" max="7688" width="10" style="50" customWidth="1"/>
+    <col min="7689" max="7689" width="13.33203125" style="50" customWidth="1"/>
+    <col min="7690" max="7934" width="10" style="50" customWidth="1"/>
+    <col min="7935" max="7939" width="15.44140625" style="50" customWidth="1"/>
+    <col min="7940" max="7944" width="10" style="50" customWidth="1"/>
+    <col min="7945" max="7945" width="13.33203125" style="50" customWidth="1"/>
+    <col min="7946" max="8190" width="10" style="50" customWidth="1"/>
+    <col min="8191" max="8195" width="15.44140625" style="50" customWidth="1"/>
+    <col min="8196" max="8200" width="10" style="50" customWidth="1"/>
+    <col min="8201" max="8201" width="13.33203125" style="50" customWidth="1"/>
+    <col min="8202" max="8446" width="10" style="50" customWidth="1"/>
+    <col min="8447" max="8451" width="15.44140625" style="50" customWidth="1"/>
+    <col min="8452" max="8456" width="10" style="50" customWidth="1"/>
+    <col min="8457" max="8457" width="13.33203125" style="50" customWidth="1"/>
+    <col min="8458" max="8702" width="10" style="50" customWidth="1"/>
+    <col min="8703" max="8707" width="15.44140625" style="50" customWidth="1"/>
+    <col min="8708" max="8712" width="10" style="50" customWidth="1"/>
+    <col min="8713" max="8713" width="13.33203125" style="50" customWidth="1"/>
+    <col min="8714" max="8958" width="10" style="50" customWidth="1"/>
+    <col min="8959" max="8963" width="15.44140625" style="50" customWidth="1"/>
+    <col min="8964" max="8968" width="10" style="50" customWidth="1"/>
+    <col min="8969" max="8969" width="13.33203125" style="50" customWidth="1"/>
+    <col min="8970" max="9214" width="10" style="50" customWidth="1"/>
+    <col min="9215" max="9219" width="15.44140625" style="50" customWidth="1"/>
+    <col min="9220" max="9224" width="10" style="50" customWidth="1"/>
+    <col min="9225" max="9225" width="13.33203125" style="50" customWidth="1"/>
+    <col min="9226" max="9470" width="10" style="50" customWidth="1"/>
+    <col min="9471" max="9475" width="15.44140625" style="50" customWidth="1"/>
+    <col min="9476" max="9480" width="10" style="50" customWidth="1"/>
+    <col min="9481" max="9481" width="13.33203125" style="50" customWidth="1"/>
+    <col min="9482" max="9726" width="10" style="50" customWidth="1"/>
+    <col min="9727" max="9731" width="15.44140625" style="50" customWidth="1"/>
+    <col min="9732" max="9736" width="10" style="50" customWidth="1"/>
+    <col min="9737" max="9737" width="13.33203125" style="50" customWidth="1"/>
+    <col min="9738" max="9982" width="10" style="50" customWidth="1"/>
+    <col min="9983" max="9987" width="15.44140625" style="50" customWidth="1"/>
+    <col min="9988" max="9992" width="10" style="50" customWidth="1"/>
+    <col min="9993" max="9993" width="13.33203125" style="50" customWidth="1"/>
+    <col min="9994" max="10238" width="10" style="50" customWidth="1"/>
+    <col min="10239" max="10243" width="15.44140625" style="50" customWidth="1"/>
+    <col min="10244" max="10248" width="10" style="50" customWidth="1"/>
+    <col min="10249" max="10249" width="13.33203125" style="50" customWidth="1"/>
+    <col min="10250" max="10494" width="10" style="50" customWidth="1"/>
+    <col min="10495" max="10499" width="15.44140625" style="50" customWidth="1"/>
+    <col min="10500" max="10504" width="10" style="50" customWidth="1"/>
+    <col min="10505" max="10505" width="13.33203125" style="50" customWidth="1"/>
+    <col min="10506" max="10750" width="10" style="50" customWidth="1"/>
+    <col min="10751" max="10755" width="15.44140625" style="50" customWidth="1"/>
+    <col min="10756" max="10760" width="10" style="50" customWidth="1"/>
+    <col min="10761" max="10761" width="13.33203125" style="50" customWidth="1"/>
+    <col min="10762" max="11006" width="10" style="50" customWidth="1"/>
+    <col min="11007" max="11011" width="15.44140625" style="50" customWidth="1"/>
+    <col min="11012" max="11016" width="10" style="50" customWidth="1"/>
+    <col min="11017" max="11017" width="13.33203125" style="50" customWidth="1"/>
+    <col min="11018" max="11262" width="10" style="50" customWidth="1"/>
+    <col min="11263" max="11267" width="15.44140625" style="50" customWidth="1"/>
+    <col min="11268" max="11272" width="10" style="50" customWidth="1"/>
+    <col min="11273" max="11273" width="13.33203125" style="50" customWidth="1"/>
+    <col min="11274" max="11518" width="10" style="50" customWidth="1"/>
+    <col min="11519" max="11523" width="15.44140625" style="50" customWidth="1"/>
+    <col min="11524" max="11528" width="10" style="50" customWidth="1"/>
+    <col min="11529" max="11529" width="13.33203125" style="50" customWidth="1"/>
+    <col min="11530" max="11774" width="10" style="50" customWidth="1"/>
+    <col min="11775" max="11779" width="15.44140625" style="50" customWidth="1"/>
+    <col min="11780" max="11784" width="10" style="50" customWidth="1"/>
+    <col min="11785" max="11785" width="13.33203125" style="50" customWidth="1"/>
+    <col min="11786" max="12030" width="10" style="50" customWidth="1"/>
+    <col min="12031" max="12035" width="15.44140625" style="50" customWidth="1"/>
+    <col min="12036" max="12040" width="10" style="50" customWidth="1"/>
+    <col min="12041" max="12041" width="13.33203125" style="50" customWidth="1"/>
+    <col min="12042" max="12286" width="10" style="50" customWidth="1"/>
+    <col min="12287" max="12291" width="15.44140625" style="50" customWidth="1"/>
+    <col min="12292" max="12296" width="10" style="50" customWidth="1"/>
+    <col min="12297" max="12297" width="13.33203125" style="50" customWidth="1"/>
+    <col min="12298" max="12542" width="10" style="50" customWidth="1"/>
+    <col min="12543" max="12547" width="15.44140625" style="50" customWidth="1"/>
+    <col min="12548" max="12552" width="10" style="50" customWidth="1"/>
+    <col min="12553" max="12553" width="13.33203125" style="50" customWidth="1"/>
+    <col min="12554" max="12798" width="10" style="50" customWidth="1"/>
+    <col min="12799" max="12803" width="15.44140625" style="50" customWidth="1"/>
+    <col min="12804" max="12808" width="10" style="50" customWidth="1"/>
+    <col min="12809" max="12809" width="13.33203125" style="50" customWidth="1"/>
+    <col min="12810" max="13054" width="10" style="50" customWidth="1"/>
+    <col min="13055" max="13059" width="15.44140625" style="50" customWidth="1"/>
+    <col min="13060" max="13064" width="10" style="50" customWidth="1"/>
+    <col min="13065" max="13065" width="13.33203125" style="50" customWidth="1"/>
+    <col min="13066" max="13310" width="10" style="50" customWidth="1"/>
+    <col min="13311" max="13315" width="15.44140625" style="50" customWidth="1"/>
+    <col min="13316" max="13320" width="10" style="50" customWidth="1"/>
+    <col min="13321" max="13321" width="13.33203125" style="50" customWidth="1"/>
+    <col min="13322" max="13566" width="10" style="50" customWidth="1"/>
+    <col min="13567" max="13571" width="15.44140625" style="50" customWidth="1"/>
+    <col min="13572" max="13576" width="10" style="50" customWidth="1"/>
+    <col min="13577" max="13577" width="13.33203125" style="50" customWidth="1"/>
+    <col min="13578" max="13822" width="10" style="50" customWidth="1"/>
+    <col min="13823" max="13827" width="15.44140625" style="50" customWidth="1"/>
+    <col min="13828" max="13832" width="10" style="50" customWidth="1"/>
+    <col min="13833" max="13833" width="13.33203125" style="50" customWidth="1"/>
+    <col min="13834" max="14078" width="10" style="50" customWidth="1"/>
+    <col min="14079" max="14083" width="15.44140625" style="50" customWidth="1"/>
+    <col min="14084" max="14088" width="10" style="50" customWidth="1"/>
+    <col min="14089" max="14089" width="13.33203125" style="50" customWidth="1"/>
+    <col min="14090" max="14334" width="10" style="50" customWidth="1"/>
+    <col min="14335" max="14339" width="15.44140625" style="50" customWidth="1"/>
+    <col min="14340" max="14344" width="10" style="50" customWidth="1"/>
+    <col min="14345" max="14345" width="13.33203125" style="50" customWidth="1"/>
+    <col min="14346" max="14590" width="10" style="50" customWidth="1"/>
+    <col min="14591" max="14595" width="15.44140625" style="50" customWidth="1"/>
+    <col min="14596" max="14600" width="10" style="50" customWidth="1"/>
+    <col min="14601" max="14601" width="13.33203125" style="50" customWidth="1"/>
+    <col min="14602" max="14846" width="10" style="50" customWidth="1"/>
+    <col min="14847" max="14851" width="15.44140625" style="50" customWidth="1"/>
+    <col min="14852" max="14856" width="10" style="50" customWidth="1"/>
+    <col min="14857" max="14857" width="13.33203125" style="50" customWidth="1"/>
+    <col min="14858" max="15102" width="10" style="50" customWidth="1"/>
+    <col min="15103" max="15107" width="15.44140625" style="50" customWidth="1"/>
+    <col min="15108" max="15112" width="10" style="50" customWidth="1"/>
+    <col min="15113" max="15113" width="13.33203125" style="50" customWidth="1"/>
+    <col min="15114" max="15358" width="10" style="50" customWidth="1"/>
+    <col min="15359" max="15363" width="15.44140625" style="50" customWidth="1"/>
+    <col min="15364" max="15368" width="10" style="50" customWidth="1"/>
+    <col min="15369" max="15369" width="13.33203125" style="50" customWidth="1"/>
+    <col min="15370" max="15614" width="10" style="50" customWidth="1"/>
+    <col min="15615" max="15619" width="15.44140625" style="50" customWidth="1"/>
+    <col min="15620" max="15624" width="10" style="50" customWidth="1"/>
+    <col min="15625" max="15625" width="13.33203125" style="50" customWidth="1"/>
+    <col min="15626" max="15870" width="10" style="50" customWidth="1"/>
+    <col min="15871" max="15875" width="15.44140625" style="50" customWidth="1"/>
+    <col min="15876" max="15880" width="10" style="50" customWidth="1"/>
+    <col min="15881" max="15881" width="13.33203125" style="50" customWidth="1"/>
+    <col min="15882" max="16126" width="10" style="50" customWidth="1"/>
+    <col min="16127" max="16131" width="15.44140625" style="50" customWidth="1"/>
+    <col min="16132" max="16136" width="10" style="50" customWidth="1"/>
+    <col min="16137" max="16137" width="13.33203125" style="50" customWidth="1"/>
+    <col min="16138" max="16384" width="10" style="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="108" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
+      <c r="A1" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="110"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="110"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>234</v>
+      <c r="A5" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>235</v>
+      <c r="A8" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
+      <c r="A9" s="8"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
+      <c r="A10" s="8"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+      <c r="A11" s="8"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
+      <c r="A12" s="8"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
+      <c r="A13" s="8"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
+      <c r="A14" s="8"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
+      <c r="A15" s="8"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+      <c r="A17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+      <c r="A18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
+      <c r="A19" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+      <c r="A20" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
+      <c r="A21" s="8"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+      <c r="A22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
+      <c r="A23" s="8"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
+      <c r="A24" s="8"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
+      <c r="A25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="67"/>
+      <c r="A26" s="47"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="72"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="68"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
+      <c r="A28" s="48"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="68"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="113"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
+      <c r="A30" s="87"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="109"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
+      <c r="A31" s="86"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="109"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="109"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
+      <c r="A33" s="86"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="86"/>
+      <c r="D33" s="86"/>
+      <c r="E33" s="86"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="109"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="109"/>
+      <c r="A34" s="86"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="86"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="69"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="69"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="69"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="69"/>
-      <c r="B38" s="69"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="69"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="69"/>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="69"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="69"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="69"/>
-      <c r="B43" s="69"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="69"/>
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="69"/>
-      <c r="B45" s="69"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="69"/>
-      <c r="B46" s="69"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="72" t="s">
-        <v>236</v>
+      <c r="A48" s="52" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="112" t="s">
-        <v>237</v>
-      </c>
-      <c r="B49" s="109"/>
-      <c r="C49" s="109"/>
-      <c r="D49" s="109"/>
-      <c r="E49" s="109"/>
+      <c r="A49" s="88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="86"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>238</v>
+      <c r="A50" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B52" s="109" t="s">
-        <v>240</v>
-      </c>
-      <c r="C52" s="109"/>
-      <c r="D52" s="109"/>
-      <c r="E52" s="109"/>
+      <c r="A52" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="86"/>
+      <c r="D52" s="86"/>
+      <c r="E52" s="86"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="B53" s="109" t="s">
-        <v>242</v>
-      </c>
-      <c r="C53" s="109"/>
-      <c r="D53" s="109"/>
-      <c r="E53" s="109"/>
+      <c r="A53" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B54" s="112" t="s">
-        <v>244</v>
-      </c>
-      <c r="C54" s="109"/>
-      <c r="D54" s="109"/>
-      <c r="E54" s="109"/>
+      <c r="A54" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="86"/>
+      <c r="D54" s="86"/>
+      <c r="E54" s="86"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B55" s="112" t="s">
-        <v>246</v>
-      </c>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
+      <c r="A55" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="88" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="86"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="B56" s="112" t="s">
-        <v>248</v>
-      </c>
-      <c r="C56" s="109"/>
-      <c r="D56" s="109"/>
-      <c r="E56" s="109"/>
+      <c r="A56" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="88" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="86"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="B57" s="112" t="s">
-        <v>250</v>
-      </c>
-      <c r="C57" s="109"/>
-      <c r="D57" s="109"/>
-      <c r="E57" s="109"/>
+      <c r="A57" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="88" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="B58" s="112" t="s">
-        <v>252</v>
-      </c>
-      <c r="C58" s="109"/>
-      <c r="D58" s="109"/>
-      <c r="E58" s="109"/>
+      <c r="A58" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="88" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="86"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="86"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
-        <v>253</v>
+      <c r="A60" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="68"/>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
-      <c r="D62" s="68"/>
-      <c r="E62" s="68"/>
+      <c r="A62" s="48"/>
+      <c r="B62" s="48"/>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="68"/>
-      <c r="B63" s="69"/>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
+      <c r="A63" s="48"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="68"/>
-      <c r="B64" s="69"/>
-      <c r="C64" s="69"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
+      <c r="A64" s="48"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="113"/>
-      <c r="B65" s="69"/>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
+      <c r="A65" s="87"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="109"/>
-      <c r="B66" s="69"/>
-      <c r="C66" s="69"/>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
+      <c r="A66" s="86"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="49"/>
+      <c r="E66" s="49"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="109"/>
-      <c r="B67" s="69"/>
-      <c r="C67" s="69"/>
-      <c r="D67" s="69"/>
-      <c r="E67" s="69"/>
+      <c r="A67" s="86"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="109"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="69"/>
-      <c r="E68" s="69"/>
+      <c r="A68" s="86"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="109"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="69"/>
-      <c r="E69" s="69"/>
+      <c r="A69" s="86"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="109"/>
-      <c r="B70" s="69"/>
-      <c r="C70" s="69"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="69"/>
+      <c r="A70" s="86"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="49"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="109"/>
-      <c r="B71" s="69"/>
-      <c r="C71" s="69"/>
-      <c r="D71" s="67"/>
-      <c r="E71" s="16"/>
+      <c r="A71" s="86"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="12"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="109"/>
-      <c r="B72" s="69"/>
-      <c r="C72" s="69"/>
-      <c r="D72" s="71"/>
-      <c r="E72" s="16"/>
+      <c r="A72" s="86"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="12"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="109"/>
-      <c r="B73" s="69"/>
-      <c r="C73" s="69"/>
-      <c r="D73" s="71"/>
-      <c r="E73" s="16"/>
+      <c r="A73" s="86"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="51"/>
+      <c r="E73" s="12"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="109"/>
-      <c r="B74" s="69"/>
-      <c r="C74" s="69"/>
-      <c r="D74" s="71"/>
-      <c r="E74" s="16"/>
+      <c r="A74" s="86"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="12"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="109"/>
-      <c r="B75" s="69"/>
-      <c r="C75" s="69"/>
-      <c r="D75" s="71"/>
-      <c r="E75" s="67"/>
+      <c r="A75" s="86"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="47"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="109"/>
-      <c r="B76" s="69"/>
-      <c r="C76" s="69"/>
-      <c r="D76" s="71"/>
-      <c r="E76" s="69"/>
+      <c r="A76" s="86"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="49"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="109"/>
-      <c r="B77" s="69"/>
-      <c r="C77" s="69"/>
-      <c r="D77" s="71"/>
-      <c r="E77" s="69"/>
+      <c r="A77" s="86"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="49"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="109"/>
-      <c r="B78" s="69"/>
-      <c r="C78" s="69"/>
-      <c r="D78" s="71"/>
-      <c r="E78" s="69"/>
+      <c r="A78" s="86"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="51"/>
+      <c r="E78" s="49"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="109"/>
-      <c r="B79" s="69"/>
-      <c r="C79" s="69"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="69"/>
+      <c r="A79" s="86"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="49"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="109"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="69"/>
+      <c r="A80" s="86"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="49"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="109"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="71"/>
-      <c r="E81" s="69"/>
+      <c r="A81" s="86"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="51"/>
+      <c r="E81" s="49"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="109"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="71"/>
-      <c r="E82" s="69"/>
+      <c r="A82" s="86"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="51"/>
+      <c r="E82" s="49"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="109"/>
-      <c r="B83" s="69"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="71"/>
-      <c r="E83" s="69"/>
+      <c r="A83" s="86"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="51"/>
+      <c r="E83" s="49"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="109"/>
-      <c r="B84" s="69"/>
-      <c r="C84" s="67"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
+      <c r="A84" s="86"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="47"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="68"/>
+      <c r="A86" s="48"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="114"/>
-      <c r="B87" s="109"/>
-      <c r="C87" s="109"/>
-      <c r="D87" s="109"/>
-      <c r="E87" s="109"/>
+      <c r="A87" s="85"/>
+      <c r="B87" s="86"/>
+      <c r="C87" s="86"/>
+      <c r="D87" s="86"/>
+      <c r="E87" s="86"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="69"/>
-      <c r="B88" s="71"/>
-      <c r="C88" s="71"/>
-      <c r="D88" s="71"/>
-      <c r="E88" s="71"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="69"/>
-      <c r="B89" s="71"/>
-      <c r="C89" s="71"/>
-      <c r="D89" s="71"/>
-      <c r="E89" s="71"/>
+      <c r="A89" s="49"/>
+      <c r="B89" s="51"/>
+      <c r="C89" s="51"/>
+      <c r="D89" s="51"/>
+      <c r="E89" s="51"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="17"/>
+      <c r="A90" s="13"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="12"/>
+      <c r="A91" s="8"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="18"/>
-      <c r="B93" s="72"/>
-      <c r="C93" s="72"/>
-      <c r="D93" s="72"/>
-      <c r="E93" s="72"/>
+      <c r="A93" s="14"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="72"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
+      <c r="A94" s="52"/>
+      <c r="B94" s="41"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="41"/>
+      <c r="E94" s="41"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="19"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
+      <c r="A95" s="15"/>
+      <c r="B95" s="41"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="41"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="111"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
+      <c r="A96" s="91"/>
+      <c r="B96" s="41"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="41"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="109"/>
-      <c r="B97" s="61"/>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
-      <c r="E97" s="61"/>
+      <c r="A97" s="86"/>
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="109"/>
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
+      <c r="A98" s="86"/>
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="109"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
+      <c r="A99" s="86"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="41"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="109"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
+      <c r="A100" s="86"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="41"/>
+      <c r="E100" s="41"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="109"/>
-      <c r="B101" s="20"/>
-      <c r="C101" s="20"/>
-      <c r="D101" s="61"/>
-      <c r="E101" s="61"/>
+      <c r="A101" s="86"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="41"/>
+      <c r="E101" s="41"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="109"/>
-      <c r="B102" s="20"/>
-      <c r="C102" s="20"/>
-      <c r="D102" s="61"/>
-      <c r="E102" s="61"/>
+      <c r="A102" s="86"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="41"/>
+      <c r="E102" s="41"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="109"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="20"/>
-      <c r="D103" s="61"/>
-      <c r="E103" s="61"/>
+      <c r="A103" s="86"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="41"/>
+      <c r="E103" s="41"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="109"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="20"/>
-      <c r="D104" s="61"/>
-      <c r="E104" s="61"/>
+      <c r="A104" s="86"/>
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="41"/>
+      <c r="E104" s="41"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="109"/>
-      <c r="B105" s="20"/>
-      <c r="C105" s="20"/>
-      <c r="D105" s="61"/>
-      <c r="E105" s="61"/>
+      <c r="A105" s="86"/>
+      <c r="B105" s="16"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="41"/>
+      <c r="E105" s="41"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="109"/>
-      <c r="B106" s="20"/>
-      <c r="C106" s="20"/>
-      <c r="D106" s="61"/>
-      <c r="E106" s="61"/>
+      <c r="A106" s="86"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="41"/>
+      <c r="E106" s="41"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="109"/>
-      <c r="B107" s="20"/>
-      <c r="C107" s="20"/>
-      <c r="D107" s="61"/>
-      <c r="E107" s="61"/>
+      <c r="A107" s="86"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="41"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="109"/>
-      <c r="B108" s="20"/>
-      <c r="C108" s="20"/>
-      <c r="D108" s="61"/>
-      <c r="E108" s="61"/>
+      <c r="A108" s="86"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="41"/>
+      <c r="E108" s="41"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="109"/>
-      <c r="B109" s="20"/>
-      <c r="C109" s="20"/>
-      <c r="D109" s="61"/>
-      <c r="E109" s="61"/>
+      <c r="A109" s="86"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="41"/>
+      <c r="E109" s="41"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="109"/>
-      <c r="B110" s="20"/>
-      <c r="C110" s="20"/>
-      <c r="D110" s="61"/>
-      <c r="E110" s="61"/>
+      <c r="A110" s="86"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="41"/>
+      <c r="E110" s="41"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="109"/>
-      <c r="B111" s="20"/>
-      <c r="C111" s="20"/>
-      <c r="D111" s="61"/>
-      <c r="E111" s="61"/>
+      <c r="A111" s="86"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="41"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="109"/>
-      <c r="B112" s="20"/>
-      <c r="C112" s="20"/>
-      <c r="D112" s="61"/>
-      <c r="E112" s="61"/>
+      <c r="A112" s="86"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="41"/>
+      <c r="E112" s="41"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="109"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="20"/>
-      <c r="D113" s="61"/>
-      <c r="E113" s="61"/>
+      <c r="A113" s="86"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="41"/>
+      <c r="E113" s="41"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="109"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="20"/>
-      <c r="D114" s="61"/>
-      <c r="E114" s="61"/>
+      <c r="A114" s="86"/>
+      <c r="B114" s="16"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="41"/>
+      <c r="E114" s="41"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="109"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="20"/>
-      <c r="D115" s="61"/>
-      <c r="E115" s="61"/>
+      <c r="A115" s="86"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="41"/>
+      <c r="E115" s="41"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="109"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="20"/>
-      <c r="D116" s="61"/>
-      <c r="E116" s="61"/>
+      <c r="A116" s="86"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="16"/>
+      <c r="D116" s="41"/>
+      <c r="E116" s="41"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="109"/>
-      <c r="B117" s="20"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="61"/>
-      <c r="E117" s="61"/>
+      <c r="A117" s="86"/>
+      <c r="B117" s="16"/>
+      <c r="C117" s="16"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="109"/>
-      <c r="B118" s="20"/>
-      <c r="C118" s="20"/>
-      <c r="D118" s="61"/>
-      <c r="E118" s="61"/>
+      <c r="A118" s="86"/>
+      <c r="B118" s="16"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="41"/>
+      <c r="E118" s="41"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="109"/>
-      <c r="B119" s="20"/>
-      <c r="C119" s="20"/>
-      <c r="D119" s="61"/>
-      <c r="E119" s="61"/>
+      <c r="A119" s="86"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="16"/>
+      <c r="D119" s="41"/>
+      <c r="E119" s="41"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="109"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="20"/>
-      <c r="D120" s="61"/>
-      <c r="E120" s="61"/>
+      <c r="A120" s="86"/>
+      <c r="B120" s="16"/>
+      <c r="C120" s="16"/>
+      <c r="D120" s="41"/>
+      <c r="E120" s="41"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="109"/>
-      <c r="B121" s="20"/>
-      <c r="C121" s="20"/>
-      <c r="D121" s="61"/>
-      <c r="E121" s="61"/>
+      <c r="A121" s="86"/>
+      <c r="B121" s="16"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="41"/>
+      <c r="E121" s="41"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="109"/>
-      <c r="B122" s="20"/>
-      <c r="C122" s="20"/>
-      <c r="D122" s="61"/>
-      <c r="E122" s="61"/>
+      <c r="A122" s="86"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="16"/>
+      <c r="D122" s="41"/>
+      <c r="E122" s="41"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="109"/>
-      <c r="B123" s="20"/>
-      <c r="C123" s="20"/>
-      <c r="D123" s="61"/>
-      <c r="E123" s="61"/>
+      <c r="A123" s="86"/>
+      <c r="B123" s="16"/>
+      <c r="C123" s="16"/>
+      <c r="D123" s="41"/>
+      <c r="E123" s="41"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="109"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
-      <c r="D124" s="61"/>
-      <c r="E124" s="61"/>
+      <c r="A124" s="86"/>
+      <c r="B124" s="16"/>
+      <c r="C124" s="16"/>
+      <c r="D124" s="41"/>
+      <c r="E124" s="41"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="109"/>
-      <c r="B125" s="20"/>
-      <c r="C125" s="20"/>
-      <c r="D125" s="61"/>
-      <c r="E125" s="61"/>
+      <c r="A125" s="86"/>
+      <c r="B125" s="16"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="41"/>
+      <c r="E125" s="41"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="109"/>
-      <c r="B126" s="20"/>
-      <c r="C126" s="20"/>
-      <c r="D126" s="61"/>
-      <c r="E126" s="61"/>
+      <c r="A126" s="86"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="16"/>
+      <c r="D126" s="41"/>
+      <c r="E126" s="41"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="109"/>
-      <c r="B127" s="20"/>
-      <c r="C127" s="20"/>
-      <c r="D127" s="61"/>
-      <c r="E127" s="61"/>
+      <c r="A127" s="86"/>
+      <c r="B127" s="16"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="41"/>
+      <c r="E127" s="41"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="109"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="20"/>
-      <c r="D128" s="61"/>
-      <c r="E128" s="61"/>
+      <c r="A128" s="86"/>
+      <c r="B128" s="16"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="41"/>
+      <c r="E128" s="41"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="109"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="20"/>
-      <c r="D129" s="61"/>
-      <c r="E129" s="61"/>
+      <c r="A129" s="86"/>
+      <c r="B129" s="16"/>
+      <c r="C129" s="16"/>
+      <c r="D129" s="41"/>
+      <c r="E129" s="41"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="109"/>
-      <c r="B130" s="20"/>
-      <c r="C130" s="20"/>
-      <c r="D130" s="61"/>
-      <c r="E130" s="61"/>
+      <c r="A130" s="86"/>
+      <c r="B130" s="16"/>
+      <c r="C130" s="16"/>
+      <c r="D130" s="41"/>
+      <c r="E130" s="41"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="68"/>
+      <c r="A132" s="48"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="114"/>
-      <c r="B133" s="109"/>
-      <c r="C133" s="109"/>
-      <c r="D133" s="109"/>
-      <c r="E133" s="109"/>
+      <c r="A133" s="85"/>
+      <c r="B133" s="86"/>
+      <c r="C133" s="86"/>
+      <c r="D133" s="86"/>
+      <c r="E133" s="86"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="11" t="s">
-        <v>254</v>
+      <c r="A136" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="A65:A84"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A87:E87"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
     <mergeCell ref="A1:E3"/>
     <mergeCell ref="A96:A130"/>
     <mergeCell ref="B54:E54"/>
@@ -11641,6 +7978,787 @@
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="D30:D34"/>
     <mergeCell ref="B52:E52"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="A65:A84"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" style="54" customWidth="1"/>
+    <col min="2" max="3" width="20.6640625" style="54" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" style="54" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" style="54" customWidth="1"/>
+    <col min="6" max="8" width="10" style="54" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" style="54" customWidth="1"/>
+    <col min="10" max="254" width="10" style="54" customWidth="1"/>
+    <col min="255" max="259" width="15.44140625" style="54" customWidth="1"/>
+    <col min="260" max="264" width="10" style="54" customWidth="1"/>
+    <col min="265" max="265" width="13.33203125" style="54" customWidth="1"/>
+    <col min="266" max="510" width="10" style="54" customWidth="1"/>
+    <col min="511" max="515" width="15.44140625" style="54" customWidth="1"/>
+    <col min="516" max="520" width="10" style="54" customWidth="1"/>
+    <col min="521" max="521" width="13.33203125" style="54" customWidth="1"/>
+    <col min="522" max="766" width="10" style="54" customWidth="1"/>
+    <col min="767" max="771" width="15.44140625" style="54" customWidth="1"/>
+    <col min="772" max="776" width="10" style="54" customWidth="1"/>
+    <col min="777" max="777" width="13.33203125" style="54" customWidth="1"/>
+    <col min="778" max="1022" width="10" style="54" customWidth="1"/>
+    <col min="1023" max="1027" width="15.44140625" style="54" customWidth="1"/>
+    <col min="1028" max="1032" width="10" style="54" customWidth="1"/>
+    <col min="1033" max="1033" width="13.33203125" style="54" customWidth="1"/>
+    <col min="1034" max="1278" width="10" style="54" customWidth="1"/>
+    <col min="1279" max="1283" width="15.44140625" style="54" customWidth="1"/>
+    <col min="1284" max="1288" width="10" style="54" customWidth="1"/>
+    <col min="1289" max="1289" width="13.33203125" style="54" customWidth="1"/>
+    <col min="1290" max="1534" width="10" style="54" customWidth="1"/>
+    <col min="1535" max="1539" width="15.44140625" style="54" customWidth="1"/>
+    <col min="1540" max="1544" width="10" style="54" customWidth="1"/>
+    <col min="1545" max="1545" width="13.33203125" style="54" customWidth="1"/>
+    <col min="1546" max="1790" width="10" style="54" customWidth="1"/>
+    <col min="1791" max="1795" width="15.44140625" style="54" customWidth="1"/>
+    <col min="1796" max="1800" width="10" style="54" customWidth="1"/>
+    <col min="1801" max="1801" width="13.33203125" style="54" customWidth="1"/>
+    <col min="1802" max="2046" width="10" style="54" customWidth="1"/>
+    <col min="2047" max="2051" width="15.44140625" style="54" customWidth="1"/>
+    <col min="2052" max="2056" width="10" style="54" customWidth="1"/>
+    <col min="2057" max="2057" width="13.33203125" style="54" customWidth="1"/>
+    <col min="2058" max="2302" width="10" style="54" customWidth="1"/>
+    <col min="2303" max="2307" width="15.44140625" style="54" customWidth="1"/>
+    <col min="2308" max="2312" width="10" style="54" customWidth="1"/>
+    <col min="2313" max="2313" width="13.33203125" style="54" customWidth="1"/>
+    <col min="2314" max="2558" width="10" style="54" customWidth="1"/>
+    <col min="2559" max="2563" width="15.44140625" style="54" customWidth="1"/>
+    <col min="2564" max="2568" width="10" style="54" customWidth="1"/>
+    <col min="2569" max="2569" width="13.33203125" style="54" customWidth="1"/>
+    <col min="2570" max="2814" width="10" style="54" customWidth="1"/>
+    <col min="2815" max="2819" width="15.44140625" style="54" customWidth="1"/>
+    <col min="2820" max="2824" width="10" style="54" customWidth="1"/>
+    <col min="2825" max="2825" width="13.33203125" style="54" customWidth="1"/>
+    <col min="2826" max="3070" width="10" style="54" customWidth="1"/>
+    <col min="3071" max="3075" width="15.44140625" style="54" customWidth="1"/>
+    <col min="3076" max="3080" width="10" style="54" customWidth="1"/>
+    <col min="3081" max="3081" width="13.33203125" style="54" customWidth="1"/>
+    <col min="3082" max="3326" width="10" style="54" customWidth="1"/>
+    <col min="3327" max="3331" width="15.44140625" style="54" customWidth="1"/>
+    <col min="3332" max="3336" width="10" style="54" customWidth="1"/>
+    <col min="3337" max="3337" width="13.33203125" style="54" customWidth="1"/>
+    <col min="3338" max="3582" width="10" style="54" customWidth="1"/>
+    <col min="3583" max="3587" width="15.44140625" style="54" customWidth="1"/>
+    <col min="3588" max="3592" width="10" style="54" customWidth="1"/>
+    <col min="3593" max="3593" width="13.33203125" style="54" customWidth="1"/>
+    <col min="3594" max="3838" width="10" style="54" customWidth="1"/>
+    <col min="3839" max="3843" width="15.44140625" style="54" customWidth="1"/>
+    <col min="3844" max="3848" width="10" style="54" customWidth="1"/>
+    <col min="3849" max="3849" width="13.33203125" style="54" customWidth="1"/>
+    <col min="3850" max="4094" width="10" style="54" customWidth="1"/>
+    <col min="4095" max="4099" width="15.44140625" style="54" customWidth="1"/>
+    <col min="4100" max="4104" width="10" style="54" customWidth="1"/>
+    <col min="4105" max="4105" width="13.33203125" style="54" customWidth="1"/>
+    <col min="4106" max="4350" width="10" style="54" customWidth="1"/>
+    <col min="4351" max="4355" width="15.44140625" style="54" customWidth="1"/>
+    <col min="4356" max="4360" width="10" style="54" customWidth="1"/>
+    <col min="4361" max="4361" width="13.33203125" style="54" customWidth="1"/>
+    <col min="4362" max="4606" width="10" style="54" customWidth="1"/>
+    <col min="4607" max="4611" width="15.44140625" style="54" customWidth="1"/>
+    <col min="4612" max="4616" width="10" style="54" customWidth="1"/>
+    <col min="4617" max="4617" width="13.33203125" style="54" customWidth="1"/>
+    <col min="4618" max="4862" width="10" style="54" customWidth="1"/>
+    <col min="4863" max="4867" width="15.44140625" style="54" customWidth="1"/>
+    <col min="4868" max="4872" width="10" style="54" customWidth="1"/>
+    <col min="4873" max="4873" width="13.33203125" style="54" customWidth="1"/>
+    <col min="4874" max="5118" width="10" style="54" customWidth="1"/>
+    <col min="5119" max="5123" width="15.44140625" style="54" customWidth="1"/>
+    <col min="5124" max="5128" width="10" style="54" customWidth="1"/>
+    <col min="5129" max="5129" width="13.33203125" style="54" customWidth="1"/>
+    <col min="5130" max="5374" width="10" style="54" customWidth="1"/>
+    <col min="5375" max="5379" width="15.44140625" style="54" customWidth="1"/>
+    <col min="5380" max="5384" width="10" style="54" customWidth="1"/>
+    <col min="5385" max="5385" width="13.33203125" style="54" customWidth="1"/>
+    <col min="5386" max="5630" width="10" style="54" customWidth="1"/>
+    <col min="5631" max="5635" width="15.44140625" style="54" customWidth="1"/>
+    <col min="5636" max="5640" width="10" style="54" customWidth="1"/>
+    <col min="5641" max="5641" width="13.33203125" style="54" customWidth="1"/>
+    <col min="5642" max="5886" width="10" style="54" customWidth="1"/>
+    <col min="5887" max="5891" width="15.44140625" style="54" customWidth="1"/>
+    <col min="5892" max="5896" width="10" style="54" customWidth="1"/>
+    <col min="5897" max="5897" width="13.33203125" style="54" customWidth="1"/>
+    <col min="5898" max="6142" width="10" style="54" customWidth="1"/>
+    <col min="6143" max="6147" width="15.44140625" style="54" customWidth="1"/>
+    <col min="6148" max="6152" width="10" style="54" customWidth="1"/>
+    <col min="6153" max="6153" width="13.33203125" style="54" customWidth="1"/>
+    <col min="6154" max="6398" width="10" style="54" customWidth="1"/>
+    <col min="6399" max="6403" width="15.44140625" style="54" customWidth="1"/>
+    <col min="6404" max="6408" width="10" style="54" customWidth="1"/>
+    <col min="6409" max="6409" width="13.33203125" style="54" customWidth="1"/>
+    <col min="6410" max="6654" width="10" style="54" customWidth="1"/>
+    <col min="6655" max="6659" width="15.44140625" style="54" customWidth="1"/>
+    <col min="6660" max="6664" width="10" style="54" customWidth="1"/>
+    <col min="6665" max="6665" width="13.33203125" style="54" customWidth="1"/>
+    <col min="6666" max="6910" width="10" style="54" customWidth="1"/>
+    <col min="6911" max="6915" width="15.44140625" style="54" customWidth="1"/>
+    <col min="6916" max="6920" width="10" style="54" customWidth="1"/>
+    <col min="6921" max="6921" width="13.33203125" style="54" customWidth="1"/>
+    <col min="6922" max="7166" width="10" style="54" customWidth="1"/>
+    <col min="7167" max="7171" width="15.44140625" style="54" customWidth="1"/>
+    <col min="7172" max="7176" width="10" style="54" customWidth="1"/>
+    <col min="7177" max="7177" width="13.33203125" style="54" customWidth="1"/>
+    <col min="7178" max="7422" width="10" style="54" customWidth="1"/>
+    <col min="7423" max="7427" width="15.44140625" style="54" customWidth="1"/>
+    <col min="7428" max="7432" width="10" style="54" customWidth="1"/>
+    <col min="7433" max="7433" width="13.33203125" style="54" customWidth="1"/>
+    <col min="7434" max="7678" width="10" style="54" customWidth="1"/>
+    <col min="7679" max="7683" width="15.44140625" style="54" customWidth="1"/>
+    <col min="7684" max="7688" width="10" style="54" customWidth="1"/>
+    <col min="7689" max="7689" width="13.33203125" style="54" customWidth="1"/>
+    <col min="7690" max="7934" width="10" style="54" customWidth="1"/>
+    <col min="7935" max="7939" width="15.44140625" style="54" customWidth="1"/>
+    <col min="7940" max="7944" width="10" style="54" customWidth="1"/>
+    <col min="7945" max="7945" width="13.33203125" style="54" customWidth="1"/>
+    <col min="7946" max="8190" width="10" style="54" customWidth="1"/>
+    <col min="8191" max="8195" width="15.44140625" style="54" customWidth="1"/>
+    <col min="8196" max="8200" width="10" style="54" customWidth="1"/>
+    <col min="8201" max="8201" width="13.33203125" style="54" customWidth="1"/>
+    <col min="8202" max="8446" width="10" style="54" customWidth="1"/>
+    <col min="8447" max="8451" width="15.44140625" style="54" customWidth="1"/>
+    <col min="8452" max="8456" width="10" style="54" customWidth="1"/>
+    <col min="8457" max="8457" width="13.33203125" style="54" customWidth="1"/>
+    <col min="8458" max="8702" width="10" style="54" customWidth="1"/>
+    <col min="8703" max="8707" width="15.44140625" style="54" customWidth="1"/>
+    <col min="8708" max="8712" width="10" style="54" customWidth="1"/>
+    <col min="8713" max="8713" width="13.33203125" style="54" customWidth="1"/>
+    <col min="8714" max="8958" width="10" style="54" customWidth="1"/>
+    <col min="8959" max="8963" width="15.44140625" style="54" customWidth="1"/>
+    <col min="8964" max="8968" width="10" style="54" customWidth="1"/>
+    <col min="8969" max="8969" width="13.33203125" style="54" customWidth="1"/>
+    <col min="8970" max="9214" width="10" style="54" customWidth="1"/>
+    <col min="9215" max="9219" width="15.44140625" style="54" customWidth="1"/>
+    <col min="9220" max="9224" width="10" style="54" customWidth="1"/>
+    <col min="9225" max="9225" width="13.33203125" style="54" customWidth="1"/>
+    <col min="9226" max="9470" width="10" style="54" customWidth="1"/>
+    <col min="9471" max="9475" width="15.44140625" style="54" customWidth="1"/>
+    <col min="9476" max="9480" width="10" style="54" customWidth="1"/>
+    <col min="9481" max="9481" width="13.33203125" style="54" customWidth="1"/>
+    <col min="9482" max="9726" width="10" style="54" customWidth="1"/>
+    <col min="9727" max="9731" width="15.44140625" style="54" customWidth="1"/>
+    <col min="9732" max="9736" width="10" style="54" customWidth="1"/>
+    <col min="9737" max="9737" width="13.33203125" style="54" customWidth="1"/>
+    <col min="9738" max="9982" width="10" style="54" customWidth="1"/>
+    <col min="9983" max="9987" width="15.44140625" style="54" customWidth="1"/>
+    <col min="9988" max="9992" width="10" style="54" customWidth="1"/>
+    <col min="9993" max="9993" width="13.33203125" style="54" customWidth="1"/>
+    <col min="9994" max="10238" width="10" style="54" customWidth="1"/>
+    <col min="10239" max="10243" width="15.44140625" style="54" customWidth="1"/>
+    <col min="10244" max="10248" width="10" style="54" customWidth="1"/>
+    <col min="10249" max="10249" width="13.33203125" style="54" customWidth="1"/>
+    <col min="10250" max="10494" width="10" style="54" customWidth="1"/>
+    <col min="10495" max="10499" width="15.44140625" style="54" customWidth="1"/>
+    <col min="10500" max="10504" width="10" style="54" customWidth="1"/>
+    <col min="10505" max="10505" width="13.33203125" style="54" customWidth="1"/>
+    <col min="10506" max="10750" width="10" style="54" customWidth="1"/>
+    <col min="10751" max="10755" width="15.44140625" style="54" customWidth="1"/>
+    <col min="10756" max="10760" width="10" style="54" customWidth="1"/>
+    <col min="10761" max="10761" width="13.33203125" style="54" customWidth="1"/>
+    <col min="10762" max="11006" width="10" style="54" customWidth="1"/>
+    <col min="11007" max="11011" width="15.44140625" style="54" customWidth="1"/>
+    <col min="11012" max="11016" width="10" style="54" customWidth="1"/>
+    <col min="11017" max="11017" width="13.33203125" style="54" customWidth="1"/>
+    <col min="11018" max="11262" width="10" style="54" customWidth="1"/>
+    <col min="11263" max="11267" width="15.44140625" style="54" customWidth="1"/>
+    <col min="11268" max="11272" width="10" style="54" customWidth="1"/>
+    <col min="11273" max="11273" width="13.33203125" style="54" customWidth="1"/>
+    <col min="11274" max="11518" width="10" style="54" customWidth="1"/>
+    <col min="11519" max="11523" width="15.44140625" style="54" customWidth="1"/>
+    <col min="11524" max="11528" width="10" style="54" customWidth="1"/>
+    <col min="11529" max="11529" width="13.33203125" style="54" customWidth="1"/>
+    <col min="11530" max="11774" width="10" style="54" customWidth="1"/>
+    <col min="11775" max="11779" width="15.44140625" style="54" customWidth="1"/>
+    <col min="11780" max="11784" width="10" style="54" customWidth="1"/>
+    <col min="11785" max="11785" width="13.33203125" style="54" customWidth="1"/>
+    <col min="11786" max="12030" width="10" style="54" customWidth="1"/>
+    <col min="12031" max="12035" width="15.44140625" style="54" customWidth="1"/>
+    <col min="12036" max="12040" width="10" style="54" customWidth="1"/>
+    <col min="12041" max="12041" width="13.33203125" style="54" customWidth="1"/>
+    <col min="12042" max="12286" width="10" style="54" customWidth="1"/>
+    <col min="12287" max="12291" width="15.44140625" style="54" customWidth="1"/>
+    <col min="12292" max="12296" width="10" style="54" customWidth="1"/>
+    <col min="12297" max="12297" width="13.33203125" style="54" customWidth="1"/>
+    <col min="12298" max="12542" width="10" style="54" customWidth="1"/>
+    <col min="12543" max="12547" width="15.44140625" style="54" customWidth="1"/>
+    <col min="12548" max="12552" width="10" style="54" customWidth="1"/>
+    <col min="12553" max="12553" width="13.33203125" style="54" customWidth="1"/>
+    <col min="12554" max="12798" width="10" style="54" customWidth="1"/>
+    <col min="12799" max="12803" width="15.44140625" style="54" customWidth="1"/>
+    <col min="12804" max="12808" width="10" style="54" customWidth="1"/>
+    <col min="12809" max="12809" width="13.33203125" style="54" customWidth="1"/>
+    <col min="12810" max="13054" width="10" style="54" customWidth="1"/>
+    <col min="13055" max="13059" width="15.44140625" style="54" customWidth="1"/>
+    <col min="13060" max="13064" width="10" style="54" customWidth="1"/>
+    <col min="13065" max="13065" width="13.33203125" style="54" customWidth="1"/>
+    <col min="13066" max="13310" width="10" style="54" customWidth="1"/>
+    <col min="13311" max="13315" width="15.44140625" style="54" customWidth="1"/>
+    <col min="13316" max="13320" width="10" style="54" customWidth="1"/>
+    <col min="13321" max="13321" width="13.33203125" style="54" customWidth="1"/>
+    <col min="13322" max="13566" width="10" style="54" customWidth="1"/>
+    <col min="13567" max="13571" width="15.44140625" style="54" customWidth="1"/>
+    <col min="13572" max="13576" width="10" style="54" customWidth="1"/>
+    <col min="13577" max="13577" width="13.33203125" style="54" customWidth="1"/>
+    <col min="13578" max="13822" width="10" style="54" customWidth="1"/>
+    <col min="13823" max="13827" width="15.44140625" style="54" customWidth="1"/>
+    <col min="13828" max="13832" width="10" style="54" customWidth="1"/>
+    <col min="13833" max="13833" width="13.33203125" style="54" customWidth="1"/>
+    <col min="13834" max="14078" width="10" style="54" customWidth="1"/>
+    <col min="14079" max="14083" width="15.44140625" style="54" customWidth="1"/>
+    <col min="14084" max="14088" width="10" style="54" customWidth="1"/>
+    <col min="14089" max="14089" width="13.33203125" style="54" customWidth="1"/>
+    <col min="14090" max="14334" width="10" style="54" customWidth="1"/>
+    <col min="14335" max="14339" width="15.44140625" style="54" customWidth="1"/>
+    <col min="14340" max="14344" width="10" style="54" customWidth="1"/>
+    <col min="14345" max="14345" width="13.33203125" style="54" customWidth="1"/>
+    <col min="14346" max="14590" width="10" style="54" customWidth="1"/>
+    <col min="14591" max="14595" width="15.44140625" style="54" customWidth="1"/>
+    <col min="14596" max="14600" width="10" style="54" customWidth="1"/>
+    <col min="14601" max="14601" width="13.33203125" style="54" customWidth="1"/>
+    <col min="14602" max="14846" width="10" style="54" customWidth="1"/>
+    <col min="14847" max="14851" width="15.44140625" style="54" customWidth="1"/>
+    <col min="14852" max="14856" width="10" style="54" customWidth="1"/>
+    <col min="14857" max="14857" width="13.33203125" style="54" customWidth="1"/>
+    <col min="14858" max="15102" width="10" style="54" customWidth="1"/>
+    <col min="15103" max="15107" width="15.44140625" style="54" customWidth="1"/>
+    <col min="15108" max="15112" width="10" style="54" customWidth="1"/>
+    <col min="15113" max="15113" width="13.33203125" style="54" customWidth="1"/>
+    <col min="15114" max="15358" width="10" style="54" customWidth="1"/>
+    <col min="15359" max="15363" width="15.44140625" style="54" customWidth="1"/>
+    <col min="15364" max="15368" width="10" style="54" customWidth="1"/>
+    <col min="15369" max="15369" width="13.33203125" style="54" customWidth="1"/>
+    <col min="15370" max="15614" width="10" style="54" customWidth="1"/>
+    <col min="15615" max="15619" width="15.44140625" style="54" customWidth="1"/>
+    <col min="15620" max="15624" width="10" style="54" customWidth="1"/>
+    <col min="15625" max="15625" width="13.33203125" style="54" customWidth="1"/>
+    <col min="15626" max="15870" width="10" style="54" customWidth="1"/>
+    <col min="15871" max="15875" width="15.44140625" style="54" customWidth="1"/>
+    <col min="15876" max="15880" width="10" style="54" customWidth="1"/>
+    <col min="15881" max="15881" width="13.33203125" style="54" customWidth="1"/>
+    <col min="15882" max="16126" width="10" style="54" customWidth="1"/>
+    <col min="16127" max="16131" width="15.44140625" style="54" customWidth="1"/>
+    <col min="16132" max="16136" width="10" style="54" customWidth="1"/>
+    <col min="16137" max="16137" width="13.33203125" style="54" customWidth="1"/>
+    <col min="16138" max="16384" width="10" style="54" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="90"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="90"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="29"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="96" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="98"/>
+    </row>
+    <row r="11" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+    </row>
+    <row r="12" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+    </row>
+    <row r="13" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+    </row>
+    <row r="14" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+    </row>
+    <row r="15" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+    </row>
+    <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="97"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="98"/>
+    </row>
+    <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+    </row>
+    <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="97"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="98"/>
+    </row>
+    <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="33"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="53"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="53"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="94"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="93"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="93"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="93"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="93"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="57"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="53"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="53"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="94"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="93"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="93"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="93"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="93"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="93"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="57"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="93"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="35"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="93"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="35"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="93"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="35"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="93"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="35"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="93"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="36"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="93"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="57"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="93"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="57"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="93"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="57"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="93"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="57"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="93"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="57"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="93"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="57"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" s="93"/>
+      <c r="C65" s="93"/>
+      <c r="D65" s="93"/>
+      <c r="E65" s="93"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="D30:D34"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="E30:E34"/>
+    <mergeCell ref="A44:A60"/>
+    <mergeCell ref="C30:C34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
